--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="95">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,51 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>EC Vitoria Salvador</t>
+  </si>
+  <si>
+    <t>Sportivo San Lorenzo</t>
+  </si>
+  <si>
+    <t>CA Platense</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>SE Palmeiras</t>
+  </si>
+  <si>
+    <t>Guarani (Par)</t>
+  </si>
+  <si>
+    <t>2026-07-28 01:56:17</t>
   </si>
 </sst>
 </file>
@@ -585,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +873,974 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2">
+        <v>2.08</v>
+      </c>
+      <c r="G2">
+        <v>2.24</v>
+      </c>
+      <c r="H2">
+        <v>4.4</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>3.05</v>
+      </c>
+      <c r="K2">
+        <v>3.25</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.15</v>
+      </c>
+      <c r="N2">
+        <v>2.3</v>
+      </c>
+      <c r="O2">
+        <v>1.66</v>
+      </c>
+      <c r="P2">
+        <v>1.42</v>
+      </c>
+      <c r="Q2">
+        <v>3</v>
+      </c>
+      <c r="R2">
+        <v>1.14</v>
+      </c>
+      <c r="S2">
+        <v>6.8</v>
+      </c>
+      <c r="T2">
+        <v>2.34</v>
+      </c>
+      <c r="U2">
+        <v>1.61</v>
+      </c>
+      <c r="V2">
+        <v>1.25</v>
+      </c>
+      <c r="W2">
+        <v>1.8</v>
+      </c>
+      <c r="X2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y2">
+        <v>13</v>
+      </c>
+      <c r="Z2">
+        <v>40</v>
+      </c>
+      <c r="AA2">
+        <v>170</v>
+      </c>
+      <c r="AB2">
+        <v>6.4</v>
+      </c>
+      <c r="AC2">
+        <v>7.8</v>
+      </c>
+      <c r="AD2">
+        <v>26</v>
+      </c>
+      <c r="AE2">
+        <v>120</v>
+      </c>
+      <c r="AF2">
+        <v>14</v>
+      </c>
+      <c r="AG2">
+        <v>15</v>
+      </c>
+      <c r="AH2">
+        <v>36</v>
+      </c>
+      <c r="AI2">
+        <v>160</v>
+      </c>
+      <c r="AJ2">
+        <v>38</v>
+      </c>
+      <c r="AK2">
+        <v>44</v>
+      </c>
+      <c r="AL2">
+        <v>95</v>
+      </c>
+      <c r="AM2">
+        <v>350</v>
+      </c>
+      <c r="AN2">
+        <v>44</v>
+      </c>
+      <c r="AO2">
+        <v>220</v>
+      </c>
+      <c r="AP2">
+        <v>6.4</v>
+      </c>
+      <c r="AQ2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>4.7</v>
+      </c>
+      <c r="AS2">
+        <v>5.2</v>
+      </c>
+      <c r="AT2">
+        <v>5.4</v>
+      </c>
+      <c r="AU2">
+        <v>6.4</v>
+      </c>
+      <c r="AV2">
+        <v>18</v>
+      </c>
+      <c r="AW2">
+        <v>5.1</v>
+      </c>
+      <c r="AX2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY2">
+        <v>10.5</v>
+      </c>
+      <c r="AZ2">
+        <v>4.6</v>
+      </c>
+      <c r="BA2">
+        <v>5.2</v>
+      </c>
+      <c r="BB2">
+        <v>4.7</v>
+      </c>
+      <c r="BC2">
+        <v>4.8</v>
+      </c>
+      <c r="BD2">
+        <v>5.1</v>
+      </c>
+      <c r="BE2">
+        <v>5.3</v>
+      </c>
+      <c r="BF2">
+        <v>4.8</v>
+      </c>
+      <c r="BG2">
+        <v>5.2</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.61</v>
+      </c>
+      <c r="BJ2">
+        <v>18.5</v>
+      </c>
+      <c r="BK2">
+        <v>1.48</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.61</v>
+      </c>
+      <c r="BN2">
+        <v>6.4</v>
+      </c>
+      <c r="BO2">
+        <v>3.1</v>
+      </c>
+      <c r="BP2">
+        <v>28</v>
+      </c>
+      <c r="BQ2">
+        <v>1.52</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.57</v>
+      </c>
+      <c r="BT2">
+        <v>11</v>
+      </c>
+      <c r="BU2">
+        <v>4.9</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.57</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.61</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.58</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3">
+        <v>1.81</v>
+      </c>
+      <c r="G3">
+        <v>1.88</v>
+      </c>
+      <c r="H3">
+        <v>4.7</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>3.8</v>
+      </c>
+      <c r="K3">
+        <v>4.1</v>
+      </c>
+      <c r="L3">
+        <v>1.35</v>
+      </c>
+      <c r="M3">
+        <v>1.06</v>
+      </c>
+      <c r="N3">
+        <v>3.9</v>
+      </c>
+      <c r="O3">
+        <v>1.3</v>
+      </c>
+      <c r="P3">
+        <v>2.02</v>
+      </c>
+      <c r="Q3">
+        <v>1.89</v>
+      </c>
+      <c r="R3">
+        <v>1.39</v>
+      </c>
+      <c r="S3">
+        <v>3.25</v>
+      </c>
+      <c r="T3">
+        <v>1.8</v>
+      </c>
+      <c r="U3">
+        <v>2.1</v>
+      </c>
+      <c r="V3">
+        <v>1.25</v>
+      </c>
+      <c r="W3">
+        <v>2.12</v>
+      </c>
+      <c r="X3">
+        <v>19</v>
+      </c>
+      <c r="Y3">
+        <v>18</v>
+      </c>
+      <c r="Z3">
+        <v>46</v>
+      </c>
+      <c r="AA3">
+        <v>140</v>
+      </c>
+      <c r="AB3">
+        <v>9.6</v>
+      </c>
+      <c r="AC3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3">
+        <v>23</v>
+      </c>
+      <c r="AE3">
+        <v>75</v>
+      </c>
+      <c r="AF3">
+        <v>12.5</v>
+      </c>
+      <c r="AG3">
+        <v>12.5</v>
+      </c>
+      <c r="AH3">
+        <v>23</v>
+      </c>
+      <c r="AI3">
+        <v>65</v>
+      </c>
+      <c r="AJ3">
+        <v>25</v>
+      </c>
+      <c r="AK3">
+        <v>24</v>
+      </c>
+      <c r="AL3">
+        <v>42</v>
+      </c>
+      <c r="AM3">
+        <v>120</v>
+      </c>
+      <c r="AN3">
+        <v>12</v>
+      </c>
+      <c r="AO3">
+        <v>85</v>
+      </c>
+      <c r="AP3">
+        <v>4.6</v>
+      </c>
+      <c r="AQ3">
+        <v>15</v>
+      </c>
+      <c r="AR3">
+        <v>5.4</v>
+      </c>
+      <c r="AS3">
+        <v>5.9</v>
+      </c>
+      <c r="AT3">
+        <v>8</v>
+      </c>
+      <c r="AU3">
+        <v>7.8</v>
+      </c>
+      <c r="AV3">
+        <v>15</v>
+      </c>
+      <c r="AW3">
+        <v>5.7</v>
+      </c>
+      <c r="AX3">
+        <v>10</v>
+      </c>
+      <c r="AY3">
+        <v>9</v>
+      </c>
+      <c r="AZ3">
+        <v>15</v>
+      </c>
+      <c r="BA3">
+        <v>5.6</v>
+      </c>
+      <c r="BB3">
+        <v>17.5</v>
+      </c>
+      <c r="BC3">
+        <v>15</v>
+      </c>
+      <c r="BD3">
+        <v>5.4</v>
+      </c>
+      <c r="BE3">
+        <v>5.9</v>
+      </c>
+      <c r="BF3">
+        <v>8.6</v>
+      </c>
+      <c r="BG3">
+        <v>5.8</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.86</v>
+      </c>
+      <c r="BJ3">
+        <v>13.5</v>
+      </c>
+      <c r="BK3">
+        <v>1.63</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.86</v>
+      </c>
+      <c r="BN3">
+        <v>6.4</v>
+      </c>
+      <c r="BO3">
+        <v>3.1</v>
+      </c>
+      <c r="BP3">
+        <v>18.5</v>
+      </c>
+      <c r="BQ3">
+        <v>1.69</v>
+      </c>
+      <c r="BR3">
+        <v>38</v>
+      </c>
+      <c r="BS3">
+        <v>1.77</v>
+      </c>
+      <c r="BT3">
+        <v>11.5</v>
+      </c>
+      <c r="BU3">
+        <v>5.1</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.8</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.81</v>
+      </c>
+      <c r="BZ3">
+        <v>32</v>
+      </c>
+      <c r="CA3">
+        <v>1.76</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4">
+        <v>4.3</v>
+      </c>
+      <c r="G4">
+        <v>4.6</v>
+      </c>
+      <c r="H4">
+        <v>2.02</v>
+      </c>
+      <c r="I4">
+        <v>2.08</v>
+      </c>
+      <c r="J4">
+        <v>3.5</v>
+      </c>
+      <c r="K4">
+        <v>3.6</v>
+      </c>
+      <c r="L4">
+        <v>1.4</v>
+      </c>
+      <c r="M4">
+        <v>1.08</v>
+      </c>
+      <c r="N4">
+        <v>3.2</v>
+      </c>
+      <c r="O4">
+        <v>1.38</v>
+      </c>
+      <c r="P4">
+        <v>1.76</v>
+      </c>
+      <c r="Q4">
+        <v>2.12</v>
+      </c>
+      <c r="R4">
+        <v>1.29</v>
+      </c>
+      <c r="S4">
+        <v>3.9</v>
+      </c>
+      <c r="T4">
+        <v>1.9</v>
+      </c>
+      <c r="U4">
+        <v>1.96</v>
+      </c>
+      <c r="V4">
+        <v>1.94</v>
+      </c>
+      <c r="W4">
+        <v>1.28</v>
+      </c>
+      <c r="X4">
+        <v>15</v>
+      </c>
+      <c r="Y4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z4">
+        <v>12.5</v>
+      </c>
+      <c r="AA4">
+        <v>25</v>
+      </c>
+      <c r="AB4">
+        <v>14.5</v>
+      </c>
+      <c r="AC4">
+        <v>8</v>
+      </c>
+      <c r="AD4">
+        <v>11</v>
+      </c>
+      <c r="AE4">
+        <v>24</v>
+      </c>
+      <c r="AF4">
+        <v>32</v>
+      </c>
+      <c r="AG4">
+        <v>970</v>
+      </c>
+      <c r="AH4">
+        <v>20</v>
+      </c>
+      <c r="AI4">
+        <v>42</v>
+      </c>
+      <c r="AJ4">
+        <v>120</v>
+      </c>
+      <c r="AK4">
+        <v>65</v>
+      </c>
+      <c r="AL4">
+        <v>90</v>
+      </c>
+      <c r="AM4">
+        <v>150</v>
+      </c>
+      <c r="AN4">
+        <v>95</v>
+      </c>
+      <c r="AO4">
+        <v>21</v>
+      </c>
+      <c r="AP4">
+        <v>10.5</v>
+      </c>
+      <c r="AQ4">
+        <v>7.2</v>
+      </c>
+      <c r="AR4">
+        <v>10.5</v>
+      </c>
+      <c r="AS4">
+        <v>21</v>
+      </c>
+      <c r="AT4">
+        <v>12</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW4">
+        <v>20</v>
+      </c>
+      <c r="AX4">
+        <v>7.2</v>
+      </c>
+      <c r="AY4">
+        <v>15.5</v>
+      </c>
+      <c r="AZ4">
+        <v>15.5</v>
+      </c>
+      <c r="BA4">
+        <v>7.6</v>
+      </c>
+      <c r="BB4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD4">
+        <v>8.6</v>
+      </c>
+      <c r="BE4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF4">
+        <v>8.6</v>
+      </c>
+      <c r="BG4">
+        <v>13</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.78</v>
+      </c>
+      <c r="BJ4">
+        <v>15</v>
+      </c>
+      <c r="BK4">
+        <v>1.59</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.78</v>
+      </c>
+      <c r="BN4">
+        <v>10.5</v>
+      </c>
+      <c r="BO4">
+        <v>4.8</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.72</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.74</v>
+      </c>
+      <c r="BT4">
+        <v>6.4</v>
+      </c>
+      <c r="BU4">
+        <v>3.15</v>
+      </c>
+      <c r="BV4">
+        <v>22</v>
+      </c>
+      <c r="BW4">
+        <v>1.65</v>
+      </c>
+      <c r="BX4">
+        <v>48</v>
+      </c>
+      <c r="BY4">
+        <v>1.72</v>
+      </c>
+      <c r="BZ4">
+        <v>46</v>
+      </c>
+      <c r="CA4">
+        <v>1.71</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.24</v>
+      </c>
+      <c r="Q5">
+        <v>1.01</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -298,7 +298,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 01:56:17</t>
+    <t>2026-07-28 03:58:18</t>
   </si>
 </sst>
 </file>
@@ -892,7 +892,7 @@
         <v>90</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G2">
         <v>2.24</v>
@@ -916,7 +916,7 @@
         <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O2">
         <v>1.66</v>
@@ -985,7 +985,7 @@
         <v>38</v>
       </c>
       <c r="AK2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL2">
         <v>95</v>
@@ -1030,7 +1030,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA2">
         <v>5.2</v>
@@ -1057,19 +1057,19 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BJ2">
         <v>18.5</v>
       </c>
       <c r="BK2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BN2">
         <v>6.4</v>
@@ -1081,7 +1081,7 @@
         <v>28</v>
       </c>
       <c r="BQ2">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1105,13 +1105,13 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CB2" t="s">
         <v>94</v>
@@ -1134,7 +1134,7 @@
         <v>91</v>
       </c>
       <c r="F3">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G3">
         <v>1.88</v>
@@ -1146,10 +1146,10 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L3">
         <v>1.35</v>
@@ -1179,7 +1179,7 @@
         <v>1.8</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V3">
         <v>1.25</v>
@@ -1299,19 +1299,19 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BJ3">
         <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BN3">
         <v>6.4</v>
@@ -1320,7 +1320,7 @@
         <v>3.1</v>
       </c>
       <c r="BP3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ3">
         <v>1.69</v>
@@ -1329,7 +1329,7 @@
         <v>38</v>
       </c>
       <c r="BS3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BT3">
         <v>11.5</v>
@@ -1341,16 +1341,16 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BZ3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA3">
         <v>1.76</v>
@@ -1385,13 +1385,13 @@
         <v>2.02</v>
       </c>
       <c r="I4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J4">
         <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
         <v>1.4</v>
@@ -1400,13 +1400,13 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
         <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
         <v>2.12</v>
@@ -1433,46 +1433,46 @@
         <v>15</v>
       </c>
       <c r="Y4">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA4">
+        <v>30</v>
+      </c>
+      <c r="AB4">
+        <v>17</v>
+      </c>
+      <c r="AC4">
+        <v>9.6</v>
+      </c>
+      <c r="AD4">
+        <v>13</v>
+      </c>
+      <c r="AE4">
+        <v>29</v>
+      </c>
+      <c r="AF4">
+        <v>40</v>
+      </c>
+      <c r="AG4">
+        <v>22</v>
+      </c>
+      <c r="AH4">
         <v>25</v>
       </c>
-      <c r="AB4">
-        <v>14.5</v>
-      </c>
-      <c r="AC4">
-        <v>8</v>
-      </c>
-      <c r="AD4">
-        <v>11</v>
-      </c>
-      <c r="AE4">
-        <v>24</v>
-      </c>
-      <c r="AF4">
-        <v>32</v>
-      </c>
-      <c r="AG4">
-        <v>970</v>
-      </c>
-      <c r="AH4">
-        <v>20</v>
-      </c>
       <c r="AI4">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
         <v>120</v>
       </c>
       <c r="AK4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AL4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM4">
         <v>150</v>
@@ -1481,7 +1481,7 @@
         <v>95</v>
       </c>
       <c r="AO4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
@@ -1508,7 +1508,7 @@
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="AY4">
         <v>15.5</v>
@@ -1517,22 +1517,22 @@
         <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="BB4">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BC4">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="BD4">
-        <v>8.6</v>
+        <v>4.1</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BF4">
-        <v>8.6</v>
+        <v>4.1</v>
       </c>
       <c r="BG4">
         <v>13</v>
@@ -1541,61 +1541,61 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
         <v>94</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -298,7 +298,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 03:58:18</t>
+    <t>2026-07-28 06:05:36</t>
   </si>
 </sst>
 </file>
@@ -892,7 +892,7 @@
         <v>90</v>
       </c>
       <c r="F2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
         <v>2.24</v>
@@ -907,10 +907,10 @@
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="M2">
         <v>1.15</v>
@@ -931,31 +931,31 @@
         <v>1.14</v>
       </c>
       <c r="S2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="T2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V2">
         <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X2">
         <v>8.800000000000001</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA2">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB2">
         <v>6.4</v>
@@ -964,10 +964,10 @@
         <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF2">
         <v>14</v>
@@ -979,7 +979,7 @@
         <v>36</v>
       </c>
       <c r="AI2">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ2">
         <v>38</v>
@@ -991,25 +991,25 @@
         <v>95</v>
       </c>
       <c r="AM2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AN2">
         <v>44</v>
       </c>
       <c r="AO2">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AP2">
         <v>6.4</v>
       </c>
       <c r="AQ2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS2">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AT2">
         <v>5.4</v>
@@ -1021,7 +1021,7 @@
         <v>18</v>
       </c>
       <c r="AW2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
@@ -1030,88 +1030,88 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BB2">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BC2">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BD2">
+        <v>4.9</v>
+      </c>
+      <c r="BE2">
         <v>5.1</v>
       </c>
-      <c r="BE2">
-        <v>5.3</v>
-      </c>
       <c r="BF2">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BG2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="BI2">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="BJ2">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>1.47</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BO2">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BP2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
-        <v>1.51</v>
+        <v>7</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS2">
-        <v>1.57</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW2">
-        <v>1.57</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.57</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
         <v>94</v>
@@ -1134,13 +1134,13 @@
         <v>91</v>
       </c>
       <c r="F3">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G3">
         <v>1.88</v>
       </c>
       <c r="H3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I3">
         <v>5</v>
@@ -1191,7 +1191,7 @@
         <v>19</v>
       </c>
       <c r="Y3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Z3">
         <v>46</v>
@@ -1200,10 +1200,10 @@
         <v>140</v>
       </c>
       <c r="AB3">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
         <v>23</v>
@@ -1212,7 +1212,7 @@
         <v>75</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
@@ -1242,16 +1242,16 @@
         <v>85</v>
       </c>
       <c r="AP3">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AQ3">
         <v>15</v>
       </c>
       <c r="AR3">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS3">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="AT3">
         <v>8</v>
@@ -1263,7 +1263,7 @@
         <v>15</v>
       </c>
       <c r="AW3">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX3">
         <v>10</v>
@@ -1275,7 +1275,7 @@
         <v>15</v>
       </c>
       <c r="BA3">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB3">
         <v>17.5</v>
@@ -1284,16 +1284,16 @@
         <v>15</v>
       </c>
       <c r="BD3">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE3">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BF3">
         <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1302,10 +1302,10 @@
         <v>1.87</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1314,10 +1314,10 @@
         <v>1.87</v>
       </c>
       <c r="BN3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP3">
         <v>18</v>
@@ -1382,7 +1382,7 @@
         <v>4.6</v>
       </c>
       <c r="H4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>2.06</v>
@@ -1421,181 +1421,181 @@
         <v>1.9</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V4">
         <v>1.94</v>
       </c>
       <c r="W4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y4">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z4">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA4">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AB4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC4">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AF4">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG4">
+        <v>18.5</v>
+      </c>
+      <c r="AH4">
         <v>22</v>
       </c>
-      <c r="AH4">
-        <v>25</v>
-      </c>
       <c r="AI4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AJ4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK4">
+        <v>65</v>
+      </c>
+      <c r="AL4">
         <v>75</v>
       </c>
-      <c r="AL4">
+      <c r="AM4">
+        <v>140</v>
+      </c>
+      <c r="AN4">
         <v>85</v>
       </c>
-      <c r="AM4">
-        <v>150</v>
-      </c>
-      <c r="AN4">
-        <v>95</v>
-      </c>
       <c r="AO4">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS4">
         <v>21</v>
       </c>
       <c r="AT4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW4">
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>3.9</v>
+        <v>27</v>
       </c>
       <c r="AY4">
+        <v>16</v>
+      </c>
+      <c r="AZ4">
+        <v>18</v>
+      </c>
+      <c r="BA4">
+        <v>36</v>
+      </c>
+      <c r="BB4">
+        <v>7</v>
+      </c>
+      <c r="BC4">
+        <v>50</v>
+      </c>
+      <c r="BD4">
+        <v>6.8</v>
+      </c>
+      <c r="BE4">
+        <v>7</v>
+      </c>
+      <c r="BF4">
+        <v>55</v>
+      </c>
+      <c r="BG4">
         <v>15.5</v>
-      </c>
-      <c r="AZ4">
-        <v>15.5</v>
-      </c>
-      <c r="BA4">
-        <v>4</v>
-      </c>
-      <c r="BB4">
-        <v>4.1</v>
-      </c>
-      <c r="BC4">
-        <v>4.1</v>
-      </c>
-      <c r="BD4">
-        <v>4.1</v>
-      </c>
-      <c r="BE4">
-        <v>4.2</v>
-      </c>
-      <c r="BF4">
-        <v>4.1</v>
-      </c>
-      <c r="BG4">
-        <v>13</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="CB4" t="s">
         <v>94</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -298,7 +298,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 06:05:36</t>
+    <t>2026-07-28 08:12:31</t>
   </si>
 </sst>
 </file>
@@ -898,16 +898,16 @@
         <v>2.24</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J2">
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
         <v>1.66</v>
@@ -916,7 +916,7 @@
         <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
         <v>1.66</v>
@@ -931,16 +931,16 @@
         <v>1.14</v>
       </c>
       <c r="S2">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="T2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U2">
         <v>1.6</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W2">
         <v>1.81</v>
@@ -982,16 +982,16 @@
         <v>170</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK2">
         <v>42</v>
       </c>
       <c r="AL2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AN2">
         <v>44</v>
@@ -1003,13 +1003,13 @@
         <v>6.4</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT2">
         <v>5.4</v>
@@ -1030,25 +1030,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BA2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB2">
         <v>21</v>
       </c>
       <c r="BC2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD2">
         <v>4.9</v>
       </c>
       <c r="BE2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG2">
         <v>5.1</v>
@@ -1057,22 +1057,22 @@
         <v>2.56</v>
       </c>
       <c r="BI2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BJ2">
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
         <v>3.55</v>
@@ -1081,37 +1081,37 @@
         <v>20</v>
       </c>
       <c r="BQ2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
         <v>8.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BV2">
         <v>60</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>94</v>
@@ -1137,7 +1137,7 @@
         <v>1.84</v>
       </c>
       <c r="G3">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H3">
         <v>4.8</v>
@@ -1146,13 +1146,13 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
         <v>3.95</v>
       </c>
       <c r="L3">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
         <v>1.06</v>
@@ -1161,37 +1161,37 @@
         <v>3.9</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P3">
         <v>2.02</v>
       </c>
       <c r="Q3">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R3">
         <v>1.39</v>
       </c>
       <c r="S3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U3">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V3">
         <v>1.25</v>
       </c>
       <c r="W3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X3">
         <v>19</v>
       </c>
       <c r="Y3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Z3">
         <v>46</v>
@@ -1200,7 +1200,7 @@
         <v>140</v>
       </c>
       <c r="AB3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
         <v>10.5</v>
@@ -1212,7 +1212,7 @@
         <v>75</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
@@ -1224,7 +1224,7 @@
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK3">
         <v>24</v>
@@ -1242,16 +1242,16 @@
         <v>85</v>
       </c>
       <c r="AP3">
-        <v>4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3">
         <v>15</v>
       </c>
       <c r="AR3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AS3">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT3">
         <v>8</v>
@@ -1263,7 +1263,7 @@
         <v>15</v>
       </c>
       <c r="AW3">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AX3">
         <v>10</v>
@@ -1275,7 +1275,7 @@
         <v>15</v>
       </c>
       <c r="BA3">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB3">
         <v>17.5</v>
@@ -1284,76 +1284,76 @@
         <v>15</v>
       </c>
       <c r="BD3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE3">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF3">
         <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI3">
-        <v>1.87</v>
+        <v>2.92</v>
       </c>
       <c r="BJ3">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BK3">
-        <v>1.66</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.87</v>
+        <v>14</v>
       </c>
       <c r="BN3">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BO3">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BQ3">
-        <v>1.69</v>
+        <v>7.6</v>
       </c>
       <c r="BR3">
         <v>38</v>
       </c>
       <c r="BS3">
-        <v>1.78</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3">
+        <v>8.4</v>
+      </c>
+      <c r="BU3">
+        <v>5.4</v>
+      </c>
+      <c r="BV3">
+        <v>55</v>
+      </c>
+      <c r="BW3">
+        <v>11</v>
+      </c>
+      <c r="BX3">
+        <v>70</v>
+      </c>
+      <c r="BY3">
         <v>11.5</v>
       </c>
-      <c r="BU3">
-        <v>5.1</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>1.81</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>1.82</v>
-      </c>
       <c r="BZ3">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="CA3">
-        <v>1.76</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>94</v>
@@ -1385,19 +1385,19 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J4">
         <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
         <v>3.25</v>
@@ -1409,49 +1409,49 @@
         <v>1.77</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
         <v>3.9</v>
       </c>
       <c r="T4">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V4">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W4">
         <v>1.27</v>
       </c>
       <c r="X4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y4">
         <v>8.6</v>
       </c>
       <c r="Z4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AF4">
         <v>34</v>
@@ -1481,13 +1481,13 @@
         <v>85</v>
       </c>
       <c r="AO4">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR4">
         <v>10</v>
@@ -1508,7 +1508,7 @@
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY4">
         <v>16</v>
@@ -1520,82 +1520,82 @@
         <v>36</v>
       </c>
       <c r="BB4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC4">
         <v>50</v>
       </c>
       <c r="BD4">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE4">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BF4">
         <v>55</v>
       </c>
       <c r="BG4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>1.78</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>1.59</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.78</v>
+        <v>14.5</v>
       </c>
       <c r="BN4">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.72</v>
+        <v>11</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.74</v>
+        <v>12</v>
       </c>
       <c r="BT4">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BU4">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BV4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BW4">
-        <v>1.65</v>
+        <v>7.6</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.72</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.71</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>94</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -298,7 +298,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 08:12:31</t>
+    <t>2026-07-28 10:20:43</t>
   </si>
 </sst>
 </file>
@@ -892,64 +892,64 @@
         <v>90</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G2">
         <v>2.24</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
         <v>1.66</v>
       </c>
       <c r="M2">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R2">
         <v>1.14</v>
       </c>
       <c r="S2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T2">
         <v>2.34</v>
       </c>
       <c r="U2">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
         <v>42</v>
@@ -958,7 +958,7 @@
         <v>180</v>
       </c>
       <c r="AB2">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
@@ -976,142 +976,142 @@
         <v>15</v>
       </c>
       <c r="AH2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI2">
         <v>170</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AM2">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="AN2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO2">
         <v>230</v>
       </c>
       <c r="AP2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR2">
+        <v>4.3</v>
+      </c>
+      <c r="AS2">
         <v>4.7</v>
       </c>
-      <c r="AS2">
-        <v>5.1</v>
-      </c>
       <c r="AT2">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV2">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AX2">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY2">
         <v>10.5</v>
       </c>
       <c r="AZ2">
+        <v>21</v>
+      </c>
+      <c r="BA2">
+        <v>4.7</v>
+      </c>
+      <c r="BB2">
+        <v>4.3</v>
+      </c>
+      <c r="BC2">
+        <v>4.4</v>
+      </c>
+      <c r="BD2">
         <v>4.6</v>
       </c>
-      <c r="BA2">
-        <v>5.1</v>
-      </c>
-      <c r="BB2">
-        <v>21</v>
-      </c>
-      <c r="BC2">
+      <c r="BE2">
+        <v>4.8</v>
+      </c>
+      <c r="BF2">
+        <v>4.3</v>
+      </c>
+      <c r="BG2">
         <v>4.7</v>
       </c>
-      <c r="BD2">
-        <v>4.9</v>
-      </c>
-      <c r="BE2">
-        <v>5.2</v>
-      </c>
-      <c r="BF2">
-        <v>4.7</v>
-      </c>
-      <c r="BG2">
-        <v>5.1</v>
-      </c>
       <c r="BH2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BI2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="BJ2">
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO2">
         <v>3.55</v>
       </c>
       <c r="BP2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
         <v>8.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
         <v>60</v>
       </c>
       <c r="BW2">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
         <v>94</v>
@@ -1134,13 +1134,13 @@
         <v>91</v>
       </c>
       <c r="F3">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G3">
         <v>1.87</v>
       </c>
       <c r="H3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I3">
         <v>5</v>
@@ -1155,7 +1155,7 @@
         <v>1.39</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
         <v>3.9</v>
@@ -1170,16 +1170,16 @@
         <v>1.91</v>
       </c>
       <c r="R3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U3">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
         <v>1.25</v>
@@ -1188,40 +1188,40 @@
         <v>2.14</v>
       </c>
       <c r="X3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Z3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA3">
         <v>140</v>
       </c>
       <c r="AB3">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3">
+        <v>24</v>
+      </c>
+      <c r="AE3">
+        <v>80</v>
+      </c>
+      <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
         <v>10.5</v>
-      </c>
-      <c r="AD3">
-        <v>23</v>
-      </c>
-      <c r="AE3">
-        <v>75</v>
-      </c>
-      <c r="AF3">
-        <v>12</v>
-      </c>
-      <c r="AG3">
-        <v>12.5</v>
       </c>
       <c r="AH3">
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
         <v>24</v>
@@ -1230,28 +1230,28 @@
         <v>24</v>
       </c>
       <c r="AL3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM3">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN3">
         <v>12</v>
       </c>
       <c r="AO3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP3">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3">
         <v>15</v>
       </c>
       <c r="AR3">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AS3">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT3">
         <v>8</v>
@@ -1260,40 +1260,40 @@
         <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW3">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AX3">
         <v>10</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BE3">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BF3">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BG3">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH3">
         <v>3.6</v>
@@ -1317,16 +1317,16 @@
         <v>4.5</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BP3">
         <v>12.5</v>
       </c>
       <c r="BQ3">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
         <v>9.800000000000001</v>
@@ -1338,13 +1338,13 @@
         <v>5.4</v>
       </c>
       <c r="BV3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
         <v>11</v>
       </c>
       <c r="BX3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
         <v>11.5</v>
@@ -1376,16 +1376,16 @@
         <v>92</v>
       </c>
       <c r="F4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G4">
         <v>4.6</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J4">
         <v>3.5</v>
@@ -1397,16 +1397,16 @@
         <v>1.45</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
         <v>2.14</v>
@@ -1418,49 +1418,49 @@
         <v>3.9</v>
       </c>
       <c r="T4">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V4">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X4">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Y4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z4">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AA4">
         <v>24</v>
       </c>
       <c r="AB4">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AC4">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AD4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE4">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AF4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI4">
         <v>44</v>
@@ -1475,22 +1475,22 @@
         <v>75</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS4">
         <v>21</v>
@@ -1502,13 +1502,13 @@
         <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW4">
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AY4">
         <v>16</v>
@@ -1520,40 +1520,40 @@
         <v>36</v>
       </c>
       <c r="BB4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BC4">
         <v>50</v>
       </c>
       <c r="BD4">
-        <v>9.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="BE4">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BF4">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH4">
         <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN4">
         <v>7.6</v>
@@ -1565,37 +1565,37 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV4">
         <v>15</v>
       </c>
       <c r="BW4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>94</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -298,7 +298,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 10:20:43</t>
+    <t>2026-07-28 12:28:20</t>
   </si>
 </sst>
 </file>
@@ -892,7 +892,7 @@
         <v>90</v>
       </c>
       <c r="F2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
         <v>2.24</v>
@@ -913,52 +913,52 @@
         <v>1.66</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P2">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V2">
         <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X2">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z2">
         <v>42</v>
       </c>
       <c r="AA2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB2">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
@@ -970,13 +970,13 @@
         <v>130</v>
       </c>
       <c r="AF2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI2">
         <v>170</v>
@@ -985,79 +985,79 @@
         <v>38</v>
       </c>
       <c r="AK2">
+        <v>42</v>
+      </c>
+      <c r="AL2">
+        <v>95</v>
+      </c>
+      <c r="AM2">
+        <v>350</v>
+      </c>
+      <c r="AN2">
         <v>44</v>
-      </c>
-      <c r="AL2">
-        <v>100</v>
-      </c>
-      <c r="AM2">
-        <v>370</v>
-      </c>
-      <c r="AN2">
-        <v>40</v>
       </c>
       <c r="AO2">
         <v>230</v>
       </c>
       <c r="AP2">
+        <v>6.4</v>
+      </c>
+      <c r="AQ2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR2">
         <v>6.2</v>
       </c>
-      <c r="AQ2">
-        <v>8</v>
-      </c>
-      <c r="AR2">
-        <v>4.3</v>
-      </c>
       <c r="AS2">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AT2">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV2">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AW2">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AX2">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2">
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BA2">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BB2">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC2">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD2">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG2">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BH2">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BI2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BJ2">
         <v>13.5</v>
@@ -1078,7 +1078,7 @@
         <v>3.55</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
         <v>7.2</v>
@@ -1099,7 +1099,7 @@
         <v>60</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1108,7 +1108,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
         <v>9.4</v>
@@ -1134,13 +1134,13 @@
         <v>91</v>
       </c>
       <c r="F3">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G3">
         <v>1.87</v>
       </c>
       <c r="H3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I3">
         <v>5</v>
@@ -1167,13 +1167,13 @@
         <v>2.02</v>
       </c>
       <c r="Q3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R3">
         <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
         <v>1.84</v>
@@ -1188,19 +1188,19 @@
         <v>2.14</v>
       </c>
       <c r="X3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y3">
         <v>22</v>
       </c>
       <c r="Z3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA3">
         <v>140</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3">
         <v>8.800000000000001</v>
@@ -1212,7 +1212,7 @@
         <v>80</v>
       </c>
       <c r="AF3">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
@@ -1221,79 +1221,79 @@
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK3">
         <v>24</v>
       </c>
       <c r="AL3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM3">
         <v>130</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AO3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP3">
         <v>13.5</v>
       </c>
       <c r="AQ3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AS3">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
         <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AW3">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="AX3">
         <v>10</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BD3">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE3">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
         <v>3.6</v>
@@ -1302,7 +1302,7 @@
         <v>2.92</v>
       </c>
       <c r="BJ3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3">
         <v>6</v>
@@ -1314,16 +1314,16 @@
         <v>14</v>
       </c>
       <c r="BN3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP3">
         <v>12.5</v>
       </c>
       <c r="BQ3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR3">
         <v>1000</v>
@@ -1332,10 +1332,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1388,49 +1388,49 @@
         <v>2.06</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
         <v>1.45</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
         <v>2.14</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T4">
         <v>1.92</v>
       </c>
       <c r="U4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V4">
         <v>1.94</v>
       </c>
       <c r="W4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y4">
         <v>8.4</v>
@@ -1442,10 +1442,10 @@
         <v>24</v>
       </c>
       <c r="AB4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD4">
         <v>11</v>
@@ -1460,31 +1460,31 @@
         <v>18</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI4">
         <v>44</v>
       </c>
       <c r="AJ4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK4">
         <v>65</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
         <v>80</v>
       </c>
       <c r="AO4">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
         <v>7.6</v>
@@ -1496,7 +1496,7 @@
         <v>21</v>
       </c>
       <c r="AT4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU4">
         <v>7.2</v>
@@ -1508,19 +1508,19 @@
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="AY4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4">
         <v>18</v>
       </c>
       <c r="BA4">
+        <v>25</v>
+      </c>
+      <c r="BB4">
         <v>36</v>
-      </c>
-      <c r="BB4">
-        <v>12</v>
       </c>
       <c r="BC4">
         <v>50</v>
@@ -1529,16 +1529,16 @@
         <v>60</v>
       </c>
       <c r="BE4">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="BF4">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="BG4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI4">
         <v>2.62</v>
@@ -1547,13 +1547,13 @@
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN4">
         <v>7.6</v>
@@ -1565,37 +1565,37 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT4">
         <v>4.7</v>
       </c>
       <c r="BU4">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV4">
         <v>15</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>94</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -298,7 +298,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 12:28:20</t>
+    <t>2026-07-28 14:35:52</t>
   </si>
 </sst>
 </file>
@@ -892,16 +892,16 @@
         <v>90</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G2">
         <v>2.24</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -913,37 +913,37 @@
         <v>1.66</v>
       </c>
       <c r="M2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P2">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Q2">
         <v>3</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S2">
         <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V2">
         <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
         <v>7.4</v>
@@ -952,7 +952,7 @@
         <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA2">
         <v>170</v>
@@ -964,10 +964,10 @@
         <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF2">
         <v>12</v>
@@ -979,7 +979,7 @@
         <v>36</v>
       </c>
       <c r="AI2">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ2">
         <v>38</v>
@@ -991,13 +991,13 @@
         <v>95</v>
       </c>
       <c r="AM2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AN2">
         <v>44</v>
       </c>
       <c r="AO2">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AP2">
         <v>6.4</v>
@@ -1006,10 +1006,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
         <v>5.4</v>
@@ -1021,7 +1021,7 @@
         <v>18</v>
       </c>
       <c r="AW2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
@@ -1030,25 +1030,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB2">
         <v>6.2</v>
       </c>
       <c r="BC2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG2">
         <v>7.2</v>
@@ -1140,10 +1140,10 @@
         <v>1.87</v>
       </c>
       <c r="H3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J3">
         <v>3.8</v>
@@ -1167,7 +1167,7 @@
         <v>2.02</v>
       </c>
       <c r="Q3">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R3">
         <v>1.4</v>
@@ -1176,19 +1176,19 @@
         <v>3.3</v>
       </c>
       <c r="T3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W3">
         <v>2.14</v>
       </c>
       <c r="X3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y3">
         <v>22</v>
@@ -1203,7 +1203,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
         <v>24</v>
@@ -1233,7 +1233,7 @@
         <v>44</v>
       </c>
       <c r="AM3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN3">
         <v>14.5</v>
@@ -1245,13 +1245,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR3">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS3">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT3">
         <v>8.199999999999999</v>
@@ -1260,40 +1260,40 @@
         <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW3">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX3">
         <v>10</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB3">
         <v>17.5</v>
       </c>
       <c r="BC3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE3">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF3">
         <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH3">
         <v>3.6</v>
@@ -1406,7 +1406,7 @@
         <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
         <v>2.14</v>
@@ -1418,13 +1418,13 @@
         <v>3.95</v>
       </c>
       <c r="T4">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V4">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W4">
         <v>1.27</v>
@@ -1442,7 +1442,7 @@
         <v>24</v>
       </c>
       <c r="AB4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
@@ -1466,7 +1466,7 @@
         <v>44</v>
       </c>
       <c r="AJ4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
         <v>65</v>
@@ -1478,7 +1478,7 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
         <v>17.5</v>
@@ -1508,10 +1508,10 @@
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AY4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ4">
         <v>18</v>
@@ -1535,25 +1535,25 @@
         <v>55</v>
       </c>
       <c r="BG4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH4">
         <v>3.15</v>
       </c>
       <c r="BI4">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN4">
         <v>7.6</v>
@@ -1565,16 +1565,16 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU4">
         <v>4.1</v>
@@ -1583,19 +1583,19 @@
         <v>15</v>
       </c>
       <c r="BW4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="s">
         <v>94</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -298,7 +298,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 14:35:52</t>
+    <t>2026-07-28 16:43:34</t>
   </si>
 </sst>
 </file>
@@ -895,13 +895,13 @@
         <v>2.14</v>
       </c>
       <c r="G2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H2">
         <v>4.5</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -910,82 +910,82 @@
         <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="M2">
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="O2">
         <v>1.67</v>
       </c>
       <c r="P2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U2">
         <v>1.62</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y2">
+        <v>11</v>
+      </c>
+      <c r="Z2">
+        <v>32</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>6.2</v>
+      </c>
+      <c r="AC2">
+        <v>7.6</v>
+      </c>
+      <c r="AD2">
+        <v>22</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
         <v>11.5</v>
-      </c>
-      <c r="Z2">
-        <v>40</v>
-      </c>
-      <c r="AA2">
-        <v>170</v>
-      </c>
-      <c r="AB2">
-        <v>6.4</v>
-      </c>
-      <c r="AC2">
-        <v>7.8</v>
-      </c>
-      <c r="AD2">
-        <v>26</v>
-      </c>
-      <c r="AE2">
-        <v>120</v>
-      </c>
-      <c r="AF2">
-        <v>12</v>
       </c>
       <c r="AG2">
         <v>13</v>
       </c>
       <c r="AH2">
+        <v>32</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
         <v>36</v>
       </c>
-      <c r="AI2">
-        <v>160</v>
-      </c>
-      <c r="AJ2">
-        <v>38</v>
-      </c>
       <c r="AK2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL2">
         <v>95</v>
@@ -994,64 +994,64 @@
         <v>340</v>
       </c>
       <c r="AN2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO2">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR2">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AS2">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="AT2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
       </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="BA2">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BB2">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="BC2">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BE2">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BG2">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BH2">
         <v>2.56</v>
@@ -1134,7 +1134,7 @@
         <v>91</v>
       </c>
       <c r="F3">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G3">
         <v>1.87</v>
@@ -1149,7 +1149,7 @@
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
         <v>1.39</v>
@@ -1245,7 +1245,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3">
         <v>5.4</v>
@@ -1260,10 +1260,10 @@
         <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AW3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX3">
         <v>10</v>
@@ -1379,13 +1379,13 @@
         <v>4.4</v>
       </c>
       <c r="G4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H4">
         <v>2.02</v>
       </c>
       <c r="I4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J4">
         <v>3.45</v>
@@ -1400,37 +1400,37 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P4">
         <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
         <v>1.31</v>
       </c>
       <c r="S4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T4">
         <v>1.93</v>
       </c>
       <c r="U4">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W4">
         <v>1.27</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y4">
         <v>8.4</v>
@@ -1466,7 +1466,7 @@
         <v>44</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK4">
         <v>65</v>
@@ -1478,10 +1478,10 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO4">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AP4">
         <v>11</v>
@@ -1517,7 +1517,7 @@
         <v>18</v>
       </c>
       <c r="BA4">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BB4">
         <v>36</v>
@@ -1636,202 +1636,202 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P5">
         <v>1.24</v>
       </c>
       <c r="Q5">
+        <v>1.47</v>
+      </c>
+      <c r="R5">
+        <v>1.18</v>
+      </c>
+      <c r="S5">
+        <v>1.47</v>
+      </c>
+      <c r="T5">
+        <v>1.11</v>
+      </c>
+      <c r="U5">
+        <v>1.11</v>
+      </c>
+      <c r="V5">
         <v>1.01</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -298,7 +298,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 16:43:34</t>
+    <t>2026-07-28 18:50:29</t>
   </si>
 </sst>
 </file>
@@ -895,7 +895,7 @@
         <v>2.14</v>
       </c>
       <c r="G2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H2">
         <v>4.5</v>
@@ -907,10 +907,10 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="M2">
         <v>1.16</v>
@@ -925,7 +925,7 @@
         <v>1.44</v>
       </c>
       <c r="Q2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R2">
         <v>1.15</v>
@@ -1006,19 +1006,19 @@
         <v>9.6</v>
       </c>
       <c r="AR2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS2">
         <v>40</v>
       </c>
       <c r="AT2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW2">
         <v>36</v>
@@ -1030,7 +1030,7 @@
         <v>11</v>
       </c>
       <c r="AZ2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA2">
         <v>44</v>
@@ -1134,7 +1134,7 @@
         <v>91</v>
       </c>
       <c r="F3">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G3">
         <v>1.87</v>
@@ -1143,7 +1143,7 @@
         <v>4.9</v>
       </c>
       <c r="I3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>3.8</v>
@@ -1158,16 +1158,16 @@
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
         <v>1.31</v>
       </c>
       <c r="P3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q3">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R3">
         <v>1.4</v>
@@ -1179,25 +1179,25 @@
         <v>1.83</v>
       </c>
       <c r="U3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
         <v>2.14</v>
       </c>
       <c r="X3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
         <v>9.199999999999999</v>
@@ -1206,76 +1206,76 @@
         <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
       </c>
       <c r="AH3">
+        <v>21</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
         <v>23</v>
       </c>
-      <c r="AI3">
-        <v>80</v>
-      </c>
-      <c r="AJ3">
-        <v>25</v>
-      </c>
       <c r="AK3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AL3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
+        <v>14</v>
+      </c>
+      <c r="AQ3">
         <v>13.5</v>
       </c>
-      <c r="AQ3">
-        <v>14</v>
-      </c>
       <c r="AR3">
-        <v>5.4</v>
+        <v>27</v>
       </c>
       <c r="AS3">
-        <v>5.7</v>
+        <v>38</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU3">
         <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW3">
-        <v>5.7</v>
+        <v>42</v>
       </c>
       <c r="AX3">
         <v>10</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA3">
-        <v>5.7</v>
+        <v>42</v>
       </c>
       <c r="BB3">
         <v>17.5</v>
@@ -1284,16 +1284,16 @@
         <v>16.5</v>
       </c>
       <c r="BD3">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="BE3">
-        <v>5.9</v>
+        <v>38</v>
       </c>
       <c r="BF3">
         <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="BH3">
         <v>3.6</v>
@@ -1382,7 +1382,7 @@
         <v>4.7</v>
       </c>
       <c r="H4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>2.04</v>
@@ -1418,10 +1418,10 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V4">
         <v>1.96</v>
@@ -1466,7 +1466,7 @@
         <v>44</v>
       </c>
       <c r="AJ4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
         <v>65</v>
@@ -1478,7 +1478,7 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
         <v>21</v>
@@ -1642,13 +1642,13 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O5">
         <v>1.47</v>
       </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
         <v>1.47</v>
@@ -1726,52 +1726,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1783,55 +1783,55 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -298,7 +298,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 18:50:29</t>
+    <t>2026-07-28 20:57:49</t>
   </si>
 </sst>
 </file>
@@ -901,7 +901,7 @@
         <v>4.5</v>
       </c>
       <c r="I2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -940,7 +940,7 @@
         <v>1.62</v>
       </c>
       <c r="V2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
         <v>1.81</v>
@@ -952,7 +952,7 @@
         <v>11</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1152,7 +1152,7 @@
         <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M3">
         <v>1.07</v>
@@ -1191,7 +1191,7 @@
         <v>18</v>
       </c>
       <c r="Y3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z3">
         <v>44</v>
@@ -1206,7 +1206,7 @@
         <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE3">
         <v>75</v>
@@ -1218,13 +1218,13 @@
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI3">
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK3">
         <v>20</v>
@@ -1248,7 +1248,7 @@
         <v>13.5</v>
       </c>
       <c r="AR3">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AS3">
         <v>38</v>
@@ -1284,7 +1284,7 @@
         <v>16.5</v>
       </c>
       <c r="BD3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BE3">
         <v>38</v>
@@ -1379,7 +1379,7 @@
         <v>4.4</v>
       </c>
       <c r="G4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -1388,7 +1388,7 @@
         <v>2.04</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
         <v>3.55</v>
@@ -1397,19 +1397,19 @@
         <v>1.45</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
         <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
         <v>1.31</v>
@@ -1418,16 +1418,16 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V4">
         <v>1.96</v>
       </c>
       <c r="W4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X4">
         <v>12.5</v>
@@ -1436,10 +1436,10 @@
         <v>8.4</v>
       </c>
       <c r="Z4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB4">
         <v>14.5</v>
@@ -1451,7 +1451,7 @@
         <v>11</v>
       </c>
       <c r="AE4">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AF4">
         <v>32</v>
@@ -1463,10 +1463,10 @@
         <v>26</v>
       </c>
       <c r="AI4">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK4">
         <v>65</v>
@@ -1478,10 +1478,10 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AP4">
         <v>11</v>
@@ -1490,7 +1490,7 @@
         <v>7.6</v>
       </c>
       <c r="AR4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS4">
         <v>21</v>
@@ -1511,7 +1511,7 @@
         <v>23</v>
       </c>
       <c r="AY4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4">
         <v>18</v>
@@ -1535,7 +1535,7 @@
         <v>55</v>
       </c>
       <c r="BG4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH4">
         <v>3.15</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -298,7 +298,7 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 20:57:49</t>
+    <t>2026-07-28 23:04:14</t>
   </si>
 </sst>
 </file>
@@ -895,13 +895,13 @@
         <v>2.14</v>
       </c>
       <c r="G2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H2">
         <v>4.5</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -925,7 +925,7 @@
         <v>1.44</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
         <v>1.15</v>
@@ -952,7 +952,7 @@
         <v>11</v>
       </c>
       <c r="Z2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -985,7 +985,7 @@
         <v>36</v>
       </c>
       <c r="AK2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL2">
         <v>95</v>
@@ -994,7 +994,7 @@
         <v>340</v>
       </c>
       <c r="AN2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1012,7 +1012,7 @@
         <v>40</v>
       </c>
       <c r="AT2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1054,7 +1054,7 @@
         <v>44</v>
       </c>
       <c r="BH2">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BI2">
         <v>2.08</v>
@@ -1081,7 +1081,7 @@
         <v>20</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR2">
         <v>55</v>
@@ -1096,10 +1096,10 @@
         <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1111,7 +1111,7 @@
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>94</v>
@@ -1161,25 +1161,25 @@
         <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
         <v>2.04</v>
       </c>
       <c r="Q3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S3">
         <v>3.3</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V3">
         <v>1.25</v>
@@ -1191,7 +1191,7 @@
         <v>18</v>
       </c>
       <c r="Y3">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Z3">
         <v>44</v>
@@ -1203,10 +1203,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE3">
         <v>75</v>
@@ -1221,10 +1221,10 @@
         <v>19.5</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK3">
         <v>20</v>
@@ -1239,16 +1239,16 @@
         <v>11.5</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP3">
         <v>14</v>
       </c>
       <c r="AQ3">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AR3">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AS3">
         <v>38</v>
@@ -1257,13 +1257,13 @@
         <v>8.4</v>
       </c>
       <c r="AU3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
         <v>16.5</v>
       </c>
       <c r="AW3">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AX3">
         <v>10</v>
@@ -1275,7 +1275,7 @@
         <v>16</v>
       </c>
       <c r="BA3">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BB3">
         <v>17.5</v>
@@ -1284,7 +1284,7 @@
         <v>16.5</v>
       </c>
       <c r="BD3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BE3">
         <v>38</v>
@@ -1299,7 +1299,7 @@
         <v>3.6</v>
       </c>
       <c r="BI3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ3">
         <v>9.800000000000001</v>
@@ -1341,7 +1341,7 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1388,7 +1388,7 @@
         <v>2.04</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>3.55</v>
@@ -1397,49 +1397,49 @@
         <v>1.45</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V4">
         <v>1.96</v>
       </c>
       <c r="W4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB4">
         <v>14.5</v>
@@ -1451,19 +1451,19 @@
         <v>11</v>
       </c>
       <c r="AE4">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AF4">
         <v>32</v>
       </c>
       <c r="AG4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AJ4">
         <v>110</v>
@@ -1475,7 +1475,7 @@
         <v>1000</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN4">
         <v>80</v>
@@ -1502,7 +1502,7 @@
         <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW4">
         <v>20</v>
@@ -1520,10 +1520,10 @@
         <v>36</v>
       </c>
       <c r="BB4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BD4">
         <v>60</v>
@@ -1532,7 +1532,7 @@
         <v>40</v>
       </c>
       <c r="BF4">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BG4">
         <v>14.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="106">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,15 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>Instituto</t>
   </si>
   <si>
@@ -286,6 +295,18 @@
     <t>Sportivo San Lorenzo</t>
   </si>
   <si>
+    <t>Libertad</t>
+  </si>
+  <si>
+    <t>Talleres</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
     <t>CA Platense</t>
   </si>
   <si>
@@ -298,7 +319,19 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
-    <t>2026-07-28 23:04:14</t>
+    <t>Deportivo Recoleta</t>
+  </si>
+  <si>
+    <t>Velez Sarsfield</t>
+  </si>
+  <si>
+    <t>CA Huracan</t>
+  </si>
+  <si>
+    <t>Athletico-PR</t>
+  </si>
+  <si>
+    <t>2026-07-29 01:11:05</t>
   </si>
 </sst>
 </file>
@@ -630,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -886,43 +919,43 @@
         <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F2">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G2">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M2">
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="O2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q2">
         <v>3.05</v>
@@ -931,19 +964,19 @@
         <v>1.15</v>
       </c>
       <c r="S2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T2">
         <v>2.44</v>
       </c>
       <c r="U2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X2">
         <v>7.2</v>
@@ -964,7 +997,7 @@
         <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE2">
         <v>1000</v>
@@ -976,25 +1009,25 @@
         <v>13</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AK2">
         <v>36</v>
       </c>
       <c r="AL2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AN2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1003,10 +1036,10 @@
         <v>6.6</v>
       </c>
       <c r="AQ2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS2">
         <v>40</v>
@@ -1024,7 +1057,7 @@
         <v>36</v>
       </c>
       <c r="AX2">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2">
         <v>11</v>
@@ -1039,7 +1072,7 @@
         <v>18.5</v>
       </c>
       <c r="BC2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD2">
         <v>36</v>
@@ -1054,13 +1087,13 @@
         <v>44</v>
       </c>
       <c r="BH2">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BI2">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BJ2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK2">
         <v>6</v>
@@ -1069,7 +1102,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
         <v>4.8</v>
@@ -1078,43 +1111,43 @@
         <v>3.55</v>
       </c>
       <c r="BP2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BS2">
         <v>9.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU2">
         <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1128,10 +1161,10 @@
         <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F3">
         <v>1.85</v>
@@ -1152,34 +1185,34 @@
         <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
         <v>1.9</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S3">
         <v>3.3</v>
       </c>
       <c r="T3">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V3">
         <v>1.25</v>
@@ -1188,7 +1221,7 @@
         <v>2.14</v>
       </c>
       <c r="X3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y3">
         <v>19.5</v>
@@ -1209,7 +1242,7 @@
         <v>21</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF3">
         <v>12</v>
@@ -1239,7 +1272,7 @@
         <v>11.5</v>
       </c>
       <c r="AO3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
         <v>14</v>
@@ -1257,7 +1290,7 @@
         <v>8.4</v>
       </c>
       <c r="AU3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
         <v>16.5</v>
@@ -1269,13 +1302,13 @@
         <v>10</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
         <v>16</v>
       </c>
       <c r="BA3">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BB3">
         <v>17.5</v>
@@ -1284,7 +1317,7 @@
         <v>16.5</v>
       </c>
       <c r="BD3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE3">
         <v>38</v>
@@ -1350,13 +1383,13 @@
         <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
         <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1370,10 +1403,10 @@
         <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F4">
         <v>4.4</v>
@@ -1388,40 +1421,40 @@
         <v>2.04</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R4">
         <v>1.29</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U4">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V4">
         <v>1.96</v>
@@ -1430,7 +1463,7 @@
         <v>1.27</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
         <v>8.199999999999999</v>
@@ -1445,7 +1478,7 @@
         <v>14.5</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
         <v>11</v>
@@ -1457,10 +1490,10 @@
         <v>32</v>
       </c>
       <c r="AG4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4">
         <v>44</v>
@@ -1469,25 +1502,25 @@
         <v>110</v>
       </c>
       <c r="AK4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR4">
         <v>10</v>
@@ -1499,7 +1532,7 @@
         <v>13</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV4">
         <v>10</v>
@@ -1508,13 +1541,13 @@
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AY4">
         <v>16.5</v>
       </c>
       <c r="AZ4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA4">
         <v>36</v>
@@ -1523,19 +1556,19 @@
         <v>38</v>
       </c>
       <c r="BC4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD4">
         <v>60</v>
       </c>
       <c r="BE4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF4">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="BG4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH4">
         <v>3.15</v>
@@ -1559,16 +1592,16 @@
         <v>7.6</v>
       </c>
       <c r="BO4">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ4">
         <v>12</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS4">
         <v>13</v>
@@ -1598,7 +1631,7 @@
         <v>11</v>
       </c>
       <c r="CB4" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1612,10 +1645,10 @@
         <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1840,7 +1873,975 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6">
+        <v>1.83</v>
+      </c>
+      <c r="G6">
+        <v>2.04</v>
+      </c>
+      <c r="H6">
+        <v>4.3</v>
+      </c>
+      <c r="I6">
+        <v>5.5</v>
+      </c>
+      <c r="J6">
+        <v>3.5</v>
+      </c>
+      <c r="K6">
+        <v>3.75</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.07</v>
+      </c>
+      <c r="N6">
+        <v>3.15</v>
+      </c>
+      <c r="O6">
+        <v>1.32</v>
+      </c>
+      <c r="P6">
+        <v>1.85</v>
+      </c>
+      <c r="Q6">
+        <v>1.97</v>
+      </c>
+      <c r="R6">
+        <v>1.3</v>
+      </c>
+      <c r="S6">
+        <v>2.72</v>
+      </c>
+      <c r="T6">
+        <v>1.11</v>
+      </c>
+      <c r="U6">
+        <v>1.11</v>
+      </c>
+      <c r="V6">
+        <v>1.21</v>
+      </c>
+      <c r="W6">
+        <v>1.96</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>19</v>
+      </c>
+      <c r="Z6">
+        <v>42</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>80</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>85</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.11</v>
+      </c>
+      <c r="AQ6">
+        <v>1.05</v>
+      </c>
+      <c r="AR6">
+        <v>1.09</v>
+      </c>
+      <c r="AS6">
+        <v>1.11</v>
+      </c>
+      <c r="AT6">
+        <v>1.11</v>
+      </c>
+      <c r="AU6">
+        <v>1.11</v>
+      </c>
+      <c r="AV6">
+        <v>1.11</v>
+      </c>
+      <c r="AW6">
+        <v>1.1</v>
+      </c>
+      <c r="AX6">
+        <v>1.11</v>
+      </c>
+      <c r="AY6">
+        <v>1.11</v>
+      </c>
+      <c r="AZ6">
+        <v>1.11</v>
+      </c>
+      <c r="BA6">
+        <v>1.1</v>
+      </c>
+      <c r="BB6">
+        <v>1.11</v>
+      </c>
+      <c r="BC6">
+        <v>1.11</v>
+      </c>
+      <c r="BD6">
+        <v>1.11</v>
+      </c>
+      <c r="BE6">
+        <v>1.11</v>
+      </c>
+      <c r="BF6">
+        <v>1.11</v>
+      </c>
+      <c r="BG6">
+        <v>1.11</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.91</v>
+      </c>
+      <c r="BJ6">
+        <v>13.5</v>
+      </c>
+      <c r="BK6">
+        <v>1.68</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.91</v>
+      </c>
+      <c r="BN6">
+        <v>6</v>
+      </c>
+      <c r="BO6">
+        <v>3.2</v>
+      </c>
+      <c r="BP6">
+        <v>18.5</v>
+      </c>
+      <c r="BQ6">
+        <v>1.73</v>
+      </c>
+      <c r="BR6">
+        <v>40</v>
+      </c>
+      <c r="BS6">
+        <v>1.83</v>
+      </c>
+      <c r="BT6">
+        <v>10.5</v>
+      </c>
+      <c r="BU6">
+        <v>5.3</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.85</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.86</v>
+      </c>
+      <c r="BZ6">
+        <v>34</v>
+      </c>
+      <c r="CA6">
+        <v>1.81</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
         <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7">
+        <v>2.44</v>
+      </c>
+      <c r="G7">
+        <v>2.6</v>
+      </c>
+      <c r="H7">
+        <v>3.65</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>2.82</v>
+      </c>
+      <c r="K7">
+        <v>3.05</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.14</v>
+      </c>
+      <c r="N7">
+        <v>2.42</v>
+      </c>
+      <c r="O7">
+        <v>1.6</v>
+      </c>
+      <c r="P7">
+        <v>1.48</v>
+      </c>
+      <c r="Q7">
+        <v>2.78</v>
+      </c>
+      <c r="R7">
+        <v>1.17</v>
+      </c>
+      <c r="S7">
+        <v>6</v>
+      </c>
+      <c r="T7">
+        <v>2.14</v>
+      </c>
+      <c r="U7">
+        <v>1.74</v>
+      </c>
+      <c r="V7">
+        <v>1.33</v>
+      </c>
+      <c r="W7">
+        <v>1.62</v>
+      </c>
+      <c r="X7">
+        <v>8</v>
+      </c>
+      <c r="Y7">
+        <v>10.5</v>
+      </c>
+      <c r="Z7">
+        <v>26</v>
+      </c>
+      <c r="AA7">
+        <v>100</v>
+      </c>
+      <c r="AB7">
+        <v>7.6</v>
+      </c>
+      <c r="AC7">
+        <v>7.2</v>
+      </c>
+      <c r="AD7">
+        <v>18</v>
+      </c>
+      <c r="AE7">
+        <v>70</v>
+      </c>
+      <c r="AF7">
+        <v>15</v>
+      </c>
+      <c r="AG7">
+        <v>13.5</v>
+      </c>
+      <c r="AH7">
+        <v>25</v>
+      </c>
+      <c r="AI7">
+        <v>110</v>
+      </c>
+      <c r="AJ7">
+        <v>42</v>
+      </c>
+      <c r="AK7">
+        <v>40</v>
+      </c>
+      <c r="AL7">
+        <v>75</v>
+      </c>
+      <c r="AM7">
+        <v>270</v>
+      </c>
+      <c r="AN7">
+        <v>44</v>
+      </c>
+      <c r="AO7">
+        <v>110</v>
+      </c>
+      <c r="AP7">
+        <v>6.8</v>
+      </c>
+      <c r="AQ7">
+        <v>7.2</v>
+      </c>
+      <c r="AR7">
+        <v>20</v>
+      </c>
+      <c r="AS7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT7">
+        <v>6.4</v>
+      </c>
+      <c r="AU7">
+        <v>6</v>
+      </c>
+      <c r="AV7">
+        <v>14</v>
+      </c>
+      <c r="AW7">
+        <v>8.4</v>
+      </c>
+      <c r="AX7">
+        <v>12</v>
+      </c>
+      <c r="AY7">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7">
+        <v>19.5</v>
+      </c>
+      <c r="BA7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB7">
+        <v>7.8</v>
+      </c>
+      <c r="BC7">
+        <v>7.6</v>
+      </c>
+      <c r="BD7">
+        <v>8.4</v>
+      </c>
+      <c r="BE7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF7">
+        <v>7.8</v>
+      </c>
+      <c r="BG7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.67</v>
+      </c>
+      <c r="BJ7">
+        <v>17</v>
+      </c>
+      <c r="BK7">
+        <v>1.52</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.67</v>
+      </c>
+      <c r="BN7">
+        <v>7</v>
+      </c>
+      <c r="BO7">
+        <v>3.5</v>
+      </c>
+      <c r="BP7">
+        <v>32</v>
+      </c>
+      <c r="BQ7">
+        <v>1.59</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.63</v>
+      </c>
+      <c r="BT7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU7">
+        <v>4.3</v>
+      </c>
+      <c r="BV7">
+        <v>50</v>
+      </c>
+      <c r="BW7">
+        <v>1.61</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.64</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.63</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8">
+        <v>2.24</v>
+      </c>
+      <c r="G8">
+        <v>2.42</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>4.6</v>
+      </c>
+      <c r="J8">
+        <v>2.98</v>
+      </c>
+      <c r="K8">
+        <v>3.1</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>2.22</v>
+      </c>
+      <c r="O8">
+        <v>1.01</v>
+      </c>
+      <c r="P8">
+        <v>1.42</v>
+      </c>
+      <c r="Q8">
+        <v>3</v>
+      </c>
+      <c r="R8">
+        <v>1.11</v>
+      </c>
+      <c r="S8">
+        <v>6.4</v>
+      </c>
+      <c r="T8">
+        <v>2.28</v>
+      </c>
+      <c r="U8">
+        <v>1.61</v>
+      </c>
+      <c r="V8">
+        <v>1.28</v>
+      </c>
+      <c r="W8">
+        <v>1.7</v>
+      </c>
+      <c r="X8">
+        <v>7.4</v>
+      </c>
+      <c r="Y8">
+        <v>12.5</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>25</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>16</v>
+      </c>
+      <c r="AG8">
+        <v>16</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>46</v>
+      </c>
+      <c r="AK8">
+        <v>48</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.4</v>
+      </c>
+      <c r="AQ8">
+        <v>1.52</v>
+      </c>
+      <c r="AR8">
+        <v>1.74</v>
+      </c>
+      <c r="AS8">
+        <v>1.74</v>
+      </c>
+      <c r="AT8">
+        <v>1.73</v>
+      </c>
+      <c r="AU8">
+        <v>1.73</v>
+      </c>
+      <c r="AV8">
+        <v>1.62</v>
+      </c>
+      <c r="AW8">
+        <v>1.74</v>
+      </c>
+      <c r="AX8">
+        <v>1.57</v>
+      </c>
+      <c r="AY8">
+        <v>1.57</v>
+      </c>
+      <c r="AZ8">
+        <v>1.73</v>
+      </c>
+      <c r="BA8">
+        <v>1.74</v>
+      </c>
+      <c r="BB8">
+        <v>1.67</v>
+      </c>
+      <c r="BC8">
+        <v>1.68</v>
+      </c>
+      <c r="BD8">
+        <v>1.74</v>
+      </c>
+      <c r="BE8">
+        <v>1.74</v>
+      </c>
+      <c r="BF8">
+        <v>1.74</v>
+      </c>
+      <c r="BG8">
+        <v>1.74</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>2.04</v>
+      </c>
+      <c r="BJ8">
+        <v>18</v>
+      </c>
+      <c r="BK8">
+        <v>1.5</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.64</v>
+      </c>
+      <c r="BN8">
+        <v>6.6</v>
+      </c>
+      <c r="BO8">
+        <v>3.25</v>
+      </c>
+      <c r="BP8">
+        <v>30</v>
+      </c>
+      <c r="BQ8">
+        <v>1.55</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.61</v>
+      </c>
+      <c r="BT8">
+        <v>10</v>
+      </c>
+      <c r="BU8">
+        <v>4.6</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.6</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.61</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.61</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9">
+        <v>1.97</v>
+      </c>
+      <c r="G9">
+        <v>2.02</v>
+      </c>
+      <c r="H9">
+        <v>4.8</v>
+      </c>
+      <c r="I9">
+        <v>5.1</v>
+      </c>
+      <c r="J9">
+        <v>3.35</v>
+      </c>
+      <c r="K9">
+        <v>3.4</v>
+      </c>
+      <c r="L9">
+        <v>1.57</v>
+      </c>
+      <c r="M9">
+        <v>1.11</v>
+      </c>
+      <c r="N9">
+        <v>2.72</v>
+      </c>
+      <c r="O9">
+        <v>1.51</v>
+      </c>
+      <c r="P9">
+        <v>1.58</v>
+      </c>
+      <c r="Q9">
+        <v>2.52</v>
+      </c>
+      <c r="R9">
+        <v>1.21</v>
+      </c>
+      <c r="S9">
+        <v>5.3</v>
+      </c>
+      <c r="T9">
+        <v>2.18</v>
+      </c>
+      <c r="U9">
+        <v>1.73</v>
+      </c>
+      <c r="V9">
+        <v>1.25</v>
+      </c>
+      <c r="W9">
+        <v>1.98</v>
+      </c>
+      <c r="X9">
+        <v>10</v>
+      </c>
+      <c r="Y9">
+        <v>13.5</v>
+      </c>
+      <c r="Z9">
+        <v>36</v>
+      </c>
+      <c r="AA9">
+        <v>160</v>
+      </c>
+      <c r="AB9">
+        <v>7</v>
+      </c>
+      <c r="AC9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9">
+        <v>22</v>
+      </c>
+      <c r="AE9">
+        <v>100</v>
+      </c>
+      <c r="AF9">
+        <v>11</v>
+      </c>
+      <c r="AG9">
+        <v>11.5</v>
+      </c>
+      <c r="AH9">
+        <v>27</v>
+      </c>
+      <c r="AI9">
+        <v>120</v>
+      </c>
+      <c r="AJ9">
+        <v>26</v>
+      </c>
+      <c r="AK9">
+        <v>28</v>
+      </c>
+      <c r="AL9">
+        <v>70</v>
+      </c>
+      <c r="AM9">
+        <v>240</v>
+      </c>
+      <c r="AN9">
+        <v>25</v>
+      </c>
+      <c r="AO9">
+        <v>160</v>
+      </c>
+      <c r="AP9">
+        <v>8.4</v>
+      </c>
+      <c r="AQ9">
+        <v>10.5</v>
+      </c>
+      <c r="AR9">
+        <v>24</v>
+      </c>
+      <c r="AS9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT9">
+        <v>5.8</v>
+      </c>
+      <c r="AU9">
+        <v>6.8</v>
+      </c>
+      <c r="AV9">
+        <v>17</v>
+      </c>
+      <c r="AW9">
+        <v>8.4</v>
+      </c>
+      <c r="AX9">
+        <v>9</v>
+      </c>
+      <c r="AY9">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9">
+        <v>21</v>
+      </c>
+      <c r="BA9">
+        <v>8.6</v>
+      </c>
+      <c r="BB9">
+        <v>20</v>
+      </c>
+      <c r="BC9">
+        <v>21</v>
+      </c>
+      <c r="BD9">
+        <v>8</v>
+      </c>
+      <c r="BE9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF9">
+        <v>20</v>
+      </c>
+      <c r="BG9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH9">
+        <v>2.84</v>
+      </c>
+      <c r="BI9">
+        <v>2.48</v>
+      </c>
+      <c r="BJ9">
+        <v>12</v>
+      </c>
+      <c r="BK9">
+        <v>7.6</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>11</v>
+      </c>
+      <c r="BN9">
+        <v>4.6</v>
+      </c>
+      <c r="BO9">
+        <v>3.9</v>
+      </c>
+      <c r="BP9">
+        <v>17</v>
+      </c>
+      <c r="BQ9">
+        <v>7</v>
+      </c>
+      <c r="BR9">
+        <v>42</v>
+      </c>
+      <c r="BS9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU9">
+        <v>5.3</v>
+      </c>
+      <c r="BV9">
+        <v>55</v>
+      </c>
+      <c r="BW9">
+        <v>9.6</v>
+      </c>
+      <c r="BX9">
+        <v>95</v>
+      </c>
+      <c r="BY9">
+        <v>10</v>
+      </c>
+      <c r="BZ9">
+        <v>44</v>
+      </c>
+      <c r="CA9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -331,7 +331,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 01:11:05</t>
+    <t>2026-07-29 03:18:48</t>
   </si>
 </sst>
 </file>
@@ -925,13 +925,13 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
         <v>4.8</v>
@@ -946,40 +946,40 @@
         <v>1.67</v>
       </c>
       <c r="M2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q2">
         <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
         <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V2">
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y2">
         <v>11</v>
@@ -1006,7 +1006,7 @@
         <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>30</v>
@@ -1015,16 +1015,16 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK2">
         <v>36</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM2">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="AN2">
         <v>34</v>
@@ -1033,13 +1033,13 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AS2">
         <v>40</v>
@@ -1057,55 +1057,55 @@
         <v>36</v>
       </c>
       <c r="AX2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY2">
         <v>11</v>
       </c>
       <c r="AZ2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA2">
         <v>44</v>
       </c>
       <c r="BB2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC2">
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE2">
         <v>55</v>
       </c>
       <c r="BF2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG2">
         <v>44</v>
       </c>
       <c r="BH2">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BI2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
         <v>3.55</v>
@@ -1114,13 +1114,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR2">
         <v>48</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>8</v>
@@ -1132,19 +1132,19 @@
         <v>55</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
+        <v>10.5</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
         <v>10</v>
-      </c>
-      <c r="BZ2">
-        <v>1000</v>
-      </c>
-      <c r="CA2">
-        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1182,19 +1182,19 @@
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L3">
         <v>1.39</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
         <v>4.2</v>
       </c>
       <c r="O3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
         <v>2.06</v>
@@ -1203,13 +1203,13 @@
         <v>1.9</v>
       </c>
       <c r="R3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
         <v>3.3</v>
       </c>
       <c r="T3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U3">
         <v>2.18</v>
@@ -1221,13 +1221,13 @@
         <v>2.14</v>
       </c>
       <c r="X3">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y3">
         <v>19.5</v>
       </c>
       <c r="Z3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1239,46 +1239,46 @@
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE3">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF3">
         <v>12</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ3">
         <v>22</v>
       </c>
       <c r="AK3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP3">
         <v>14</v>
       </c>
       <c r="AQ3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR3">
         <v>32</v>
@@ -1287,16 +1287,16 @@
         <v>38</v>
       </c>
       <c r="AT3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3">
         <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW3">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AX3">
         <v>10</v>
@@ -1305,19 +1305,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE3">
         <v>38</v>
@@ -1326,46 +1326,46 @@
         <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BH3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI3">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BJ3">
         <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN3">
         <v>4.6</v>
       </c>
       <c r="BO3">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP3">
         <v>12.5</v>
       </c>
       <c r="BQ3">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU3">
         <v>6</v>
@@ -1374,19 +1374,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>105</v>
@@ -1409,19 +1409,19 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
       <c r="I4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>3.55</v>
@@ -1436,7 +1436,7 @@
         <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
         <v>1.78</v>
@@ -1445,19 +1445,19 @@
         <v>2.22</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
         <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U4">
         <v>1.95</v>
       </c>
       <c r="V4">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W4">
         <v>1.27</v>
@@ -1490,10 +1490,10 @@
         <v>32</v>
       </c>
       <c r="AG4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI4">
         <v>44</v>
@@ -1505,13 +1505,13 @@
         <v>1000</v>
       </c>
       <c r="AL4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN4">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
         <v>17.5</v>
@@ -1565,7 +1565,7 @@
         <v>42</v>
       </c>
       <c r="BF4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BG4">
         <v>15.5</v>
@@ -1675,7 +1675,7 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O5">
         <v>1.47</v>
@@ -1893,7 +1893,7 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G6">
         <v>2.04</v>
@@ -1902,7 +1902,7 @@
         <v>4.3</v>
       </c>
       <c r="I6">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J6">
         <v>3.5</v>
@@ -1917,7 +1917,7 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="O6">
         <v>1.32</v>
@@ -1929,130 +1929,130 @@
         <v>1.97</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V6">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W6">
         <v>1.96</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y6">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE6">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI6">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP6">
-        <v>1.11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6">
-        <v>1.05</v>
+        <v>13</v>
       </c>
       <c r="AR6">
-        <v>1.09</v>
+        <v>4.8</v>
       </c>
       <c r="AS6">
-        <v>1.11</v>
+        <v>5.2</v>
       </c>
       <c r="AT6">
-        <v>1.11</v>
+        <v>7.4</v>
       </c>
       <c r="AU6">
-        <v>1.11</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>1.11</v>
+        <v>15.5</v>
       </c>
       <c r="AW6">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="AX6">
-        <v>1.11</v>
+        <v>10</v>
       </c>
       <c r="AY6">
-        <v>1.11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>1.11</v>
+        <v>16</v>
       </c>
       <c r="BA6">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="BB6">
-        <v>1.11</v>
+        <v>18.5</v>
       </c>
       <c r="BC6">
-        <v>1.11</v>
+        <v>17.5</v>
       </c>
       <c r="BD6">
-        <v>1.11</v>
+        <v>4.8</v>
       </c>
       <c r="BE6">
-        <v>1.11</v>
+        <v>5.2</v>
       </c>
       <c r="BF6">
-        <v>1.11</v>
+        <v>10.5</v>
       </c>
       <c r="BG6">
-        <v>1.11</v>
+        <v>5.1</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2141,13 +2141,13 @@
         <v>2.6</v>
       </c>
       <c r="H7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K7">
         <v>3.05</v>
@@ -2186,7 +2186,7 @@
         <v>1.33</v>
       </c>
       <c r="W7">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -2377,94 +2377,94 @@
         <v>103</v>
       </c>
       <c r="F8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G8">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H8">
         <v>4</v>
       </c>
       <c r="I8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J8">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="K8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N8">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="P8">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q8">
         <v>3</v>
       </c>
       <c r="R8">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="S8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T8">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U8">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W8">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X8">
+        <v>7.2</v>
+      </c>
+      <c r="Y8">
+        <v>10</v>
+      </c>
+      <c r="Z8">
+        <v>36</v>
+      </c>
+      <c r="AA8">
+        <v>140</v>
+      </c>
+      <c r="AB8">
+        <v>6.8</v>
+      </c>
+      <c r="AC8">
         <v>7.4</v>
       </c>
-      <c r="Y8">
-        <v>12.5</v>
-      </c>
-      <c r="Z8">
-        <v>1000</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>1000</v>
-      </c>
-      <c r="AC8">
-        <v>1000</v>
-      </c>
       <c r="AD8">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ8">
         <v>46</v>
@@ -2473,130 +2473,130 @@
         <v>48</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP8">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8">
-        <v>1.52</v>
+        <v>8.6</v>
       </c>
       <c r="AR8">
-        <v>1.74</v>
+        <v>7.4</v>
       </c>
       <c r="AS8">
-        <v>1.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8">
-        <v>1.73</v>
+        <v>5.7</v>
       </c>
       <c r="AU8">
-        <v>1.73</v>
+        <v>6.2</v>
       </c>
       <c r="AV8">
-        <v>1.62</v>
+        <v>16.5</v>
       </c>
       <c r="AW8">
-        <v>1.74</v>
+        <v>8.6</v>
       </c>
       <c r="AX8">
-        <v>1.57</v>
+        <v>11</v>
       </c>
       <c r="AY8">
-        <v>1.57</v>
+        <v>11</v>
       </c>
       <c r="AZ8">
-        <v>1.73</v>
+        <v>7.4</v>
       </c>
       <c r="BA8">
-        <v>1.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8">
-        <v>1.67</v>
+        <v>7.4</v>
       </c>
       <c r="BC8">
-        <v>1.68</v>
+        <v>7.6</v>
       </c>
       <c r="BD8">
-        <v>1.74</v>
+        <v>8.6</v>
       </c>
       <c r="BE8">
-        <v>1.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8">
-        <v>1.74</v>
+        <v>30</v>
       </c>
       <c r="BG8">
-        <v>1.74</v>
+        <v>9</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="BI8">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ8">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>1.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.64</v>
+        <v>16.5</v>
       </c>
       <c r="BN8">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BO8">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="BP8">
         <v>30</v>
       </c>
       <c r="BQ8">
-        <v>1.55</v>
+        <v>9.6</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS8">
-        <v>1.61</v>
+        <v>13</v>
       </c>
       <c r="BT8">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BU8">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW8">
-        <v>1.6</v>
+        <v>12.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.61</v>
+        <v>14</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.61</v>
+        <v>13.5</v>
       </c>
       <c r="CB8" t="s">
         <v>105</v>
@@ -2619,16 +2619,16 @@
         <v>104</v>
       </c>
       <c r="F9">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G9">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>4.8</v>
       </c>
       <c r="I9">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>3.35</v>
@@ -2646,13 +2646,13 @@
         <v>2.72</v>
       </c>
       <c r="O9">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="P9">
         <v>1.58</v>
       </c>
       <c r="Q9">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R9">
         <v>1.21</v>
@@ -2661,7 +2661,7 @@
         <v>5.3</v>
       </c>
       <c r="T9">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="U9">
         <v>1.73</v>
@@ -2670,34 +2670,34 @@
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Y9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z9">
         <v>36</v>
       </c>
       <c r="AA9">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD9">
         <v>22</v>
       </c>
       <c r="AE9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG9">
         <v>11.5</v>
@@ -2706,10 +2706,10 @@
         <v>27</v>
       </c>
       <c r="AI9">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK9">
         <v>28</v>
@@ -2718,13 +2718,13 @@
         <v>70</v>
       </c>
       <c r="AM9">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
         <v>25</v>
       </c>
       <c r="AO9">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
         <v>8.4</v>
@@ -2733,52 +2733,52 @@
         <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS9">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AT9">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW9">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="AX9">
         <v>9</v>
       </c>
       <c r="AY9">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA9">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="BB9">
         <v>20</v>
       </c>
       <c r="BC9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD9">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BE9">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BF9">
         <v>20</v>
       </c>
       <c r="BG9">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BH9">
         <v>2.84</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -331,7 +331,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 03:18:48</t>
+    <t>2026-07-29 05:26:39</t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G2">
         <v>2.2</v>
@@ -940,19 +940,19 @@
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P2">
         <v>1.46</v>
@@ -961,16 +961,16 @@
         <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
         <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V2">
         <v>1.26</v>
@@ -979,28 +979,28 @@
         <v>1.83</v>
       </c>
       <c r="X2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y2">
         <v>11</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB2">
         <v>6.2</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF2">
         <v>11.5</v>
@@ -1012,7 +1012,7 @@
         <v>30</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ2">
         <v>28</v>
@@ -1021,7 +1021,7 @@
         <v>36</v>
       </c>
       <c r="AL2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM2">
         <v>290</v>
@@ -1030,58 +1030,58 @@
         <v>34</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2">
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS2">
         <v>40</v>
       </c>
       <c r="AT2">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AX2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA2">
         <v>44</v>
       </c>
       <c r="BB2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BD2">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE2">
         <v>55</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BG2">
         <v>44</v>
@@ -1090,7 +1090,7 @@
         <v>2.62</v>
       </c>
       <c r="BI2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ2">
         <v>13</v>
@@ -1102,19 +1102,19 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
         <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP2">
         <v>19.5</v>
       </c>
       <c r="BQ2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR2">
         <v>48</v>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="BT2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU2">
         <v>5.8</v>
@@ -1132,19 +1132,19 @@
         <v>55</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
+        <v>11</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
         <v>10.5</v>
-      </c>
-      <c r="BZ2">
-        <v>1000</v>
-      </c>
-      <c r="CA2">
-        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1173,7 +1173,7 @@
         <v>1.87</v>
       </c>
       <c r="H3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I3">
         <v>5</v>
@@ -1182,7 +1182,7 @@
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
         <v>1.39</v>
@@ -1191,7 +1191,7 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
         <v>1.3</v>
@@ -1239,10 +1239,10 @@
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF3">
         <v>12</v>
@@ -1257,16 +1257,16 @@
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK3">
         <v>19</v>
       </c>
       <c r="AL3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
         <v>12</v>
@@ -1290,7 +1290,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV3">
         <v>17</v>
@@ -1409,19 +1409,19 @@
         <v>99</v>
       </c>
       <c r="F4">
+        <v>4.5</v>
+      </c>
+      <c r="G4">
         <v>4.6</v>
       </c>
-      <c r="G4">
-        <v>4.7</v>
-      </c>
       <c r="H4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
         <v>3.55</v>
@@ -1436,31 +1436,31 @@
         <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
         <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
         <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U4">
         <v>1.95</v>
       </c>
       <c r="V4">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X4">
         <v>11.5</v>
@@ -1499,13 +1499,13 @@
         <v>44</v>
       </c>
       <c r="AJ4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
         <v>1000</v>
       </c>
       <c r="AL4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
         <v>140</v>
@@ -1532,10 +1532,10 @@
         <v>13</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4">
         <v>20</v>
@@ -1595,13 +1595,13 @@
         <v>5.2</v>
       </c>
       <c r="BP4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
         <v>12</v>
       </c>
       <c r="BR4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
         <v>13</v>
@@ -1675,7 +1675,7 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O5">
         <v>1.47</v>
@@ -1705,7 +1705,7 @@
         <v>1.01</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y5">
         <v>1000</v>
@@ -1762,55 +1762,55 @@
         <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1935,7 +1935,7 @@
         <v>3.4</v>
       </c>
       <c r="T6">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U6">
         <v>1.98</v>
@@ -2380,22 +2380,22 @@
         <v>2.26</v>
       </c>
       <c r="G8">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H8">
         <v>4</v>
       </c>
       <c r="I8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J8">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="K8">
         <v>3.05</v>
       </c>
       <c r="L8">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="M8">
         <v>1.15</v>
@@ -2428,7 +2428,7 @@
         <v>1.29</v>
       </c>
       <c r="W8">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X8">
         <v>7.2</v>
@@ -2548,7 +2548,7 @@
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2578,7 +2578,7 @@
         <v>7.2</v>
       </c>
       <c r="BU8">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV8">
         <v>65</v>
@@ -2640,7 +2640,7 @@
         <v>1.57</v>
       </c>
       <c r="M9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N9">
         <v>2.72</v>
@@ -2685,7 +2685,7 @@
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -2697,7 +2697,7 @@
         <v>95</v>
       </c>
       <c r="AF9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG9">
         <v>11.5</v>
@@ -2709,7 +2709,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK9">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO9">
         <v>1000</v>
@@ -2730,7 +2730,7 @@
         <v>8.4</v>
       </c>
       <c r="AQ9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR9">
         <v>25</v>
@@ -2748,7 +2748,7 @@
         <v>18</v>
       </c>
       <c r="AW9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX9">
         <v>9</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -331,7 +331,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 05:26:39</t>
+    <t>2026-07-29 07:34:29</t>
   </si>
 </sst>
 </file>
@@ -934,13 +934,13 @@
         <v>4.5</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
         <v>1.68</v>
@@ -952,34 +952,34 @@
         <v>2.48</v>
       </c>
       <c r="O2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q2">
         <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
         <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
         <v>1.83</v>
       </c>
       <c r="X2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Y2">
         <v>11</v>
@@ -991,10 +991,10 @@
         <v>130</v>
       </c>
       <c r="AB2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD2">
         <v>22</v>
@@ -1012,7 +1012,7 @@
         <v>30</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
         <v>28</v>
@@ -1027,25 +1027,25 @@
         <v>290</v>
       </c>
       <c r="AN2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO2">
         <v>180</v>
       </c>
       <c r="AP2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2">
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AT2">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1060,7 +1060,7 @@
         <v>10</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
         <v>26</v>
@@ -1090,61 +1090,61 @@
         <v>2.62</v>
       </c>
       <c r="BI2">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BO2">
         <v>3.6</v>
       </c>
       <c r="BP2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
         <v>55</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1167,19 +1167,19 @@
         <v>98</v>
       </c>
       <c r="F3">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K3">
         <v>3.9</v>
@@ -1191,7 +1191,7 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
         <v>1.3</v>
@@ -1203,7 +1203,7 @@
         <v>1.9</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S3">
         <v>3.3</v>
@@ -1215,22 +1215,22 @@
         <v>2.18</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X3">
         <v>15.5</v>
       </c>
       <c r="Y3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z3">
         <v>42</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB3">
         <v>9.199999999999999</v>
@@ -1257,28 +1257,28 @@
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL3">
         <v>40</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN3">
         <v>12</v>
       </c>
       <c r="AO3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR3">
         <v>32</v>
@@ -1290,7 +1290,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
         <v>17</v>
@@ -1311,10 +1311,10 @@
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
         <v>30</v>
@@ -1326,13 +1326,13 @@
         <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH3">
         <v>3.55</v>
       </c>
       <c r="BI3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ3">
         <v>9.800000000000001</v>
@@ -1344,31 +1344,31 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN3">
         <v>4.6</v>
       </c>
       <c r="BO3">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP3">
         <v>12.5</v>
       </c>
       <c r="BQ3">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT3">
         <v>8</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1380,7 +1380,7 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
@@ -1421,13 +1421,13 @@
         <v>2.04</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1436,10 +1436,10 @@
         <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
         <v>2.24</v>
@@ -1454,13 +1454,13 @@
         <v>1.98</v>
       </c>
       <c r="U4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V4">
         <v>1.96</v>
       </c>
       <c r="W4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X4">
         <v>11.5</v>
@@ -1478,7 +1478,7 @@
         <v>14.5</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
         <v>11</v>
@@ -1496,16 +1496,16 @@
         <v>22</v>
       </c>
       <c r="AI4">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM4">
         <v>140</v>
@@ -1514,13 +1514,13 @@
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AP4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR4">
         <v>10</v>
@@ -1547,7 +1547,7 @@
         <v>16.5</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
         <v>36</v>
@@ -1562,49 +1562,49 @@
         <v>60</v>
       </c>
       <c r="BE4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF4">
         <v>70</v>
       </c>
       <c r="BG4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN4">
         <v>7.6</v>
       </c>
       <c r="BO4">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT4">
         <v>4.6</v>
@@ -1616,19 +1616,19 @@
         <v>15</v>
       </c>
       <c r="BW4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>105</v>
@@ -1896,19 +1896,19 @@
         <v>1.86</v>
       </c>
       <c r="G6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H6">
         <v>4.3</v>
       </c>
       <c r="I6">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1926,25 +1926,25 @@
         <v>1.85</v>
       </c>
       <c r="Q6">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T6">
         <v>1.81</v>
       </c>
       <c r="U6">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V6">
         <v>1.24</v>
       </c>
       <c r="W6">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X6">
         <v>16.5</v>
@@ -1953,7 +1953,7 @@
         <v>16.5</v>
       </c>
       <c r="Z6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA6">
         <v>130</v>
@@ -1968,7 +1968,7 @@
         <v>22</v>
       </c>
       <c r="AE6">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF6">
         <v>13.5</v>
@@ -1980,13 +1980,13 @@
         <v>23</v>
       </c>
       <c r="AI6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ6">
         <v>26</v>
       </c>
       <c r="AK6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL6">
         <v>44</v>
@@ -1998,22 +1998,22 @@
         <v>16.5</v>
       </c>
       <c r="AO6">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6">
         <v>13</v>
       </c>
       <c r="AR6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU6">
         <v>7.2</v>
@@ -2022,7 +2022,7 @@
         <v>15.5</v>
       </c>
       <c r="AW6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX6">
         <v>10</v>
@@ -2034,7 +2034,7 @@
         <v>16</v>
       </c>
       <c r="BA6">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB6">
         <v>18.5</v>
@@ -2043,16 +2043,16 @@
         <v>17.5</v>
       </c>
       <c r="BD6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF6">
         <v>10.5</v>
       </c>
       <c r="BG6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2076,7 +2076,7 @@
         <v>6</v>
       </c>
       <c r="BO6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BP6">
         <v>18.5</v>
@@ -2141,13 +2141,13 @@
         <v>2.6</v>
       </c>
       <c r="H7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J7">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K7">
         <v>3.05</v>
@@ -2156,40 +2156,40 @@
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N7">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="O7">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P7">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q7">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="R7">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S7">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T7">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y7">
         <v>10.5</v>
@@ -2198,13 +2198,13 @@
         <v>26</v>
       </c>
       <c r="AA7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB7">
         <v>7.6</v>
       </c>
       <c r="AC7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
         <v>18</v>
@@ -2222,7 +2222,7 @@
         <v>25</v>
       </c>
       <c r="AI7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ7">
         <v>42</v>
@@ -2237,109 +2237,109 @@
         <v>270</v>
       </c>
       <c r="AN7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP7">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7">
         <v>20</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AT7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV7">
         <v>14</v>
       </c>
       <c r="AW7">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AX7">
         <v>12</v>
       </c>
       <c r="AY7">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA7">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BB7">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BC7">
+        <v>6.4</v>
+      </c>
+      <c r="BD7">
+        <v>7</v>
+      </c>
+      <c r="BE7">
         <v>7.6</v>
       </c>
-      <c r="BD7">
-        <v>8.4</v>
-      </c>
-      <c r="BE7">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF7">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG7">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BJ7">
         <v>17</v>
       </c>
       <c r="BK7">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BN7">
         <v>7</v>
       </c>
       <c r="BO7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP7">
         <v>32</v>
       </c>
       <c r="BQ7">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BT7">
         <v>9.199999999999999</v>
       </c>
       <c r="BU7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
         <v>1.61</v>
@@ -2348,7 +2348,7 @@
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
@@ -2395,28 +2395,28 @@
         <v>3.05</v>
       </c>
       <c r="L8">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="M8">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N8">
         <v>2.28</v>
       </c>
       <c r="O8">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P8">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R8">
         <v>1.14</v>
       </c>
       <c r="S8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T8">
         <v>2.36</v>
@@ -2431,10 +2431,10 @@
         <v>1.71</v>
       </c>
       <c r="X8">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z8">
         <v>36</v>
@@ -2443,40 +2443,40 @@
         <v>140</v>
       </c>
       <c r="AB8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC8">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE8">
         <v>110</v>
       </c>
       <c r="AF8">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AH8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI8">
         <v>150</v>
       </c>
       <c r="AJ8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK8">
         <v>48</v>
       </c>
       <c r="AL8">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM8">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AN8">
         <v>55</v>
@@ -2488,61 +2488,61 @@
         <v>6.2</v>
       </c>
       <c r="AQ8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AS8">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="AT8">
         <v>5.7</v>
       </c>
       <c r="AU8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW8">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX8">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AY8">
         <v>11</v>
       </c>
       <c r="AZ8">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA8">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BB8">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BC8">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BD8">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE8">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="BF8">
-        <v>30</v>
+        <v>4.5</v>
       </c>
       <c r="BG8">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="BH8">
         <v>2.48</v>
       </c>
       <c r="BI8">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
@@ -2563,13 +2563,13 @@
         <v>4.3</v>
       </c>
       <c r="BP8">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
         <v>9.6</v>
       </c>
       <c r="BR8">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
         <v>13</v>
@@ -2578,10 +2578,10 @@
         <v>7.2</v>
       </c>
       <c r="BU8">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BV8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
         <v>12.5</v>
@@ -2590,7 +2590,7 @@
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>14</v>
+        <v>2.12</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
@@ -2637,13 +2637,13 @@
         <v>3.4</v>
       </c>
       <c r="L9">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="M9">
         <v>1.12</v>
       </c>
       <c r="N9">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O9">
         <v>1.54</v>
@@ -2652,7 +2652,7 @@
         <v>1.58</v>
       </c>
       <c r="Q9">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R9">
         <v>1.21</v>
@@ -2664,7 +2664,7 @@
         <v>2.3</v>
       </c>
       <c r="U9">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V9">
         <v>1.25</v>
@@ -2697,7 +2697,7 @@
         <v>95</v>
       </c>
       <c r="AF9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG9">
         <v>11.5</v>
@@ -2715,13 +2715,13 @@
         <v>28</v>
       </c>
       <c r="AL9">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AO9">
         <v>1000</v>
@@ -2733,19 +2733,19 @@
         <v>11</v>
       </c>
       <c r="AR9">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AS9">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AT9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU9">
         <v>7</v>
       </c>
       <c r="AV9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW9">
         <v>36</v>
@@ -2757,7 +2757,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA9">
         <v>40</v>
@@ -2784,61 +2784,61 @@
         <v>2.84</v>
       </c>
       <c r="BI9">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="BJ9">
         <v>12</v>
       </c>
       <c r="BK9">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BP9">
         <v>17</v>
       </c>
       <c r="BQ9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR9">
         <v>42</v>
       </c>
       <c r="BS9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV9">
         <v>55</v>
       </c>
       <c r="BW9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX9">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ9">
         <v>44</v>
       </c>
       <c r="CA9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB9" t="s">
         <v>105</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -331,7 +331,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 07:34:29</t>
+    <t>2026-07-29 09:42:01</t>
   </si>
 </sst>
 </file>
@@ -925,16 +925,16 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J2">
         <v>3.05</v>
@@ -943,19 +943,19 @@
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M2">
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O2">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P2">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q2">
         <v>3.05</v>
@@ -970,13 +970,13 @@
         <v>2.38</v>
       </c>
       <c r="U2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V2">
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
         <v>7.6</v>
@@ -1009,13 +1009,13 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK2">
         <v>36</v>
@@ -1027,7 +1027,7 @@
         <v>290</v>
       </c>
       <c r="AN2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO2">
         <v>180</v>
@@ -1045,10 +1045,10 @@
         <v>90</v>
       </c>
       <c r="AT2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
         <v>18.5</v>
@@ -1060,13 +1060,13 @@
         <v>10</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB2">
         <v>25</v>
@@ -1084,19 +1084,19 @@
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH2">
         <v>2.62</v>
       </c>
       <c r="BI2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1108,7 +1108,7 @@
         <v>4.9</v>
       </c>
       <c r="BO2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP2">
         <v>21</v>
@@ -1129,22 +1129,22 @@
         <v>5.6</v>
       </c>
       <c r="BV2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW2">
         <v>9</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>60</v>
       </c>
       <c r="CA2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1176,13 +1176,13 @@
         <v>4.9</v>
       </c>
       <c r="I3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>3.85</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L3">
         <v>1.39</v>
@@ -1194,16 +1194,16 @@
         <v>4.2</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q3">
         <v>1.9</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S3">
         <v>3.3</v>
@@ -1215,7 +1215,7 @@
         <v>2.18</v>
       </c>
       <c r="V3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
         <v>2.16</v>
@@ -1233,25 +1233,25 @@
         <v>120</v>
       </c>
       <c r="AB3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC3">
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE3">
         <v>65</v>
       </c>
       <c r="AF3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI3">
         <v>65</v>
@@ -1260,19 +1260,19 @@
         <v>19.5</v>
       </c>
       <c r="AK3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM3">
         <v>100</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
         <v>14.5</v>
@@ -1281,7 +1281,7 @@
         <v>17</v>
       </c>
       <c r="AR3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS3">
         <v>38</v>
@@ -1290,7 +1290,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3">
         <v>17</v>
@@ -1302,7 +1302,7 @@
         <v>10</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
         <v>17</v>
@@ -1311,82 +1311,82 @@
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD3">
         <v>30</v>
       </c>
       <c r="BE3">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BF3">
         <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BH3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI3">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3">
         <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BN3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP3">
         <v>12.5</v>
       </c>
       <c r="BQ3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
+        <v>12</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
         <v>12.5</v>
       </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>13.5</v>
-      </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="s">
         <v>105</v>
@@ -1409,199 +1409,199 @@
         <v>99</v>
       </c>
       <c r="F4">
+        <v>4.4</v>
+      </c>
+      <c r="G4">
         <v>4.5</v>
       </c>
-      <c r="G4">
-        <v>4.6</v>
-      </c>
       <c r="H4">
+        <v>2.04</v>
+      </c>
+      <c r="I4">
+        <v>2.08</v>
+      </c>
+      <c r="J4">
+        <v>3.4</v>
+      </c>
+      <c r="K4">
+        <v>3.45</v>
+      </c>
+      <c r="L4">
+        <v>1.5</v>
+      </c>
+      <c r="M4">
+        <v>1.1</v>
+      </c>
+      <c r="N4">
+        <v>3.2</v>
+      </c>
+      <c r="O4">
+        <v>1.43</v>
+      </c>
+      <c r="P4">
+        <v>1.72</v>
+      </c>
+      <c r="Q4">
+        <v>2.36</v>
+      </c>
+      <c r="R4">
+        <v>1.27</v>
+      </c>
+      <c r="S4">
+        <v>4.5</v>
+      </c>
+      <c r="T4">
         <v>2.02</v>
       </c>
-      <c r="I4">
-        <v>2.04</v>
-      </c>
-      <c r="J4">
-        <v>3.45</v>
-      </c>
-      <c r="K4">
-        <v>3.55</v>
-      </c>
-      <c r="L4">
-        <v>1.48</v>
-      </c>
-      <c r="M4">
-        <v>1.09</v>
-      </c>
-      <c r="N4">
-        <v>3.35</v>
-      </c>
-      <c r="O4">
-        <v>1.4</v>
-      </c>
-      <c r="P4">
-        <v>1.77</v>
-      </c>
-      <c r="Q4">
-        <v>2.24</v>
-      </c>
-      <c r="R4">
-        <v>1.29</v>
-      </c>
-      <c r="S4">
-        <v>4.2</v>
-      </c>
-      <c r="T4">
-        <v>1.98</v>
-      </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="V4">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="W4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y4">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="Z4">
         <v>11</v>
       </c>
       <c r="AA4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC4">
         <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF4">
         <v>32</v>
       </c>
       <c r="AG4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL4">
         <v>80</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR4">
         <v>10</v>
       </c>
       <c r="AS4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX4">
         <v>28</v>
       </c>
       <c r="AY4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB4">
         <v>38</v>
       </c>
       <c r="BC4">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BD4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BF4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BG4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BH4">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>16</v>
+        <v>2.52</v>
       </c>
       <c r="BN4">
         <v>7.6</v>
       </c>
       <c r="BO4">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ4">
         <v>12.5</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS4">
         <v>13.5</v>
@@ -1613,19 +1613,19 @@
         <v>4.1</v>
       </c>
       <c r="BV4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW4">
         <v>8.199999999999999</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY4">
         <v>11.5</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA4">
         <v>11.5</v>
@@ -1896,13 +1896,13 @@
         <v>1.86</v>
       </c>
       <c r="G6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H6">
         <v>4.3</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J6">
         <v>3.45</v>
@@ -1911,7 +1911,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M6">
         <v>1.07</v>
@@ -1935,19 +1935,19 @@
         <v>3.45</v>
       </c>
       <c r="T6">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U6">
         <v>1.99</v>
       </c>
       <c r="V6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W6">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y6">
         <v>16.5</v>
@@ -1983,7 +1983,7 @@
         <v>80</v>
       </c>
       <c r="AJ6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK6">
         <v>24</v>
@@ -2010,7 +2010,7 @@
         <v>4.7</v>
       </c>
       <c r="AS6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT6">
         <v>6.8</v>
@@ -2022,7 +2022,7 @@
         <v>15.5</v>
       </c>
       <c r="AW6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX6">
         <v>10</v>
@@ -2034,7 +2034,7 @@
         <v>16</v>
       </c>
       <c r="BA6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB6">
         <v>18.5</v>
@@ -2043,10 +2043,10 @@
         <v>17.5</v>
       </c>
       <c r="BD6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF6">
         <v>10.5</v>
@@ -2058,61 +2058,61 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.91</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="BN6">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BO6">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BP6">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BQ6">
-        <v>1.73</v>
+        <v>2.24</v>
       </c>
       <c r="BR6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="BT6">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.86</v>
+        <v>2.52</v>
       </c>
       <c r="BZ6">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="CB6" t="s">
         <v>105</v>
@@ -2138,7 +2138,7 @@
         <v>2.44</v>
       </c>
       <c r="G7">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H7">
         <v>3.65</v>
@@ -2159,37 +2159,37 @@
         <v>1.15</v>
       </c>
       <c r="N7">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O7">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P7">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q7">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="R7">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U7">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10.5</v>
@@ -2201,10 +2201,10 @@
         <v>110</v>
       </c>
       <c r="AB7">
+        <v>7.4</v>
+      </c>
+      <c r="AC7">
         <v>7.6</v>
-      </c>
-      <c r="AC7">
-        <v>7.4</v>
       </c>
       <c r="AD7">
         <v>18</v>
@@ -2225,7 +2225,7 @@
         <v>120</v>
       </c>
       <c r="AJ7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK7">
         <v>40</v>
@@ -2252,7 +2252,7 @@
         <v>20</v>
       </c>
       <c r="AS7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
@@ -2264,7 +2264,7 @@
         <v>14</v>
       </c>
       <c r="AW7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX7">
         <v>12</v>
@@ -2276,85 +2276,85 @@
         <v>20</v>
       </c>
       <c r="BA7">
+        <v>7.4</v>
+      </c>
+      <c r="BB7">
+        <v>6.6</v>
+      </c>
+      <c r="BC7">
+        <v>6.6</v>
+      </c>
+      <c r="BD7">
         <v>7.2</v>
       </c>
-      <c r="BB7">
-        <v>32</v>
-      </c>
-      <c r="BC7">
-        <v>6.4</v>
-      </c>
-      <c r="BD7">
+      <c r="BE7">
+        <v>7.8</v>
+      </c>
+      <c r="BF7">
+        <v>6.8</v>
+      </c>
+      <c r="BG7">
+        <v>7.4</v>
+      </c>
+      <c r="BH7">
+        <v>2.68</v>
+      </c>
+      <c r="BI7">
+        <v>2.16</v>
+      </c>
+      <c r="BJ7">
+        <v>12</v>
+      </c>
+      <c r="BK7">
+        <v>5.7</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>10.5</v>
+      </c>
+      <c r="BN7">
+        <v>5.3</v>
+      </c>
+      <c r="BO7">
+        <v>4.4</v>
+      </c>
+      <c r="BP7">
+        <v>24</v>
+      </c>
+      <c r="BQ7">
+        <v>7.6</v>
+      </c>
+      <c r="BR7">
+        <v>50</v>
+      </c>
+      <c r="BS7">
+        <v>9</v>
+      </c>
+      <c r="BT7">
         <v>7</v>
       </c>
-      <c r="BE7">
-        <v>7.6</v>
-      </c>
-      <c r="BF7">
-        <v>6.6</v>
-      </c>
-      <c r="BG7">
-        <v>7.2</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.66</v>
-      </c>
-      <c r="BJ7">
-        <v>17</v>
-      </c>
-      <c r="BK7">
-        <v>1.51</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.66</v>
-      </c>
-      <c r="BN7">
-        <v>7</v>
-      </c>
-      <c r="BO7">
-        <v>3.6</v>
-      </c>
-      <c r="BP7">
-        <v>32</v>
-      </c>
-      <c r="BQ7">
-        <v>1.58</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>1.62</v>
-      </c>
-      <c r="BT7">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BU7">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW7">
-        <v>1.61</v>
+        <v>8.6</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY7">
-        <v>1.63</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA7">
-        <v>1.63</v>
+        <v>9.4</v>
       </c>
       <c r="CB7" t="s">
         <v>105</v>
@@ -2380,7 +2380,7 @@
         <v>2.26</v>
       </c>
       <c r="G8">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H8">
         <v>4</v>
@@ -2395,34 +2395,34 @@
         <v>3.05</v>
       </c>
       <c r="L8">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.16</v>
       </c>
       <c r="N8">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O8">
         <v>1.67</v>
       </c>
       <c r="P8">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q8">
         <v>3.05</v>
       </c>
       <c r="R8">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S8">
         <v>6.8</v>
       </c>
       <c r="T8">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U8">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V8">
         <v>1.29</v>
@@ -2443,7 +2443,7 @@
         <v>140</v>
       </c>
       <c r="AB8">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC8">
         <v>8.6</v>
@@ -2458,10 +2458,10 @@
         <v>15.5</v>
       </c>
       <c r="AG8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI8">
         <v>150</v>
@@ -2470,31 +2470,31 @@
         <v>44</v>
       </c>
       <c r="AK8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM8">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AN8">
         <v>55</v>
       </c>
       <c r="AO8">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR8">
         <v>20</v>
       </c>
       <c r="AS8">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AT8">
         <v>5.7</v>
@@ -2506,7 +2506,7 @@
         <v>17</v>
       </c>
       <c r="AW8">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AX8">
         <v>9.4</v>
@@ -2515,88 +2515,88 @@
         <v>11</v>
       </c>
       <c r="AZ8">
+        <v>4</v>
+      </c>
+      <c r="BA8">
+        <v>4.4</v>
+      </c>
+      <c r="BB8">
+        <v>4.1</v>
+      </c>
+      <c r="BC8">
+        <v>4.1</v>
+      </c>
+      <c r="BD8">
         <v>4.3</v>
       </c>
-      <c r="BA8">
-        <v>4.7</v>
-      </c>
-      <c r="BB8">
+      <c r="BE8">
         <v>4.4</v>
       </c>
-      <c r="BC8">
+      <c r="BF8">
+        <v>4.1</v>
+      </c>
+      <c r="BG8">
         <v>4.4</v>
       </c>
-      <c r="BD8">
-        <v>4.7</v>
-      </c>
-      <c r="BE8">
-        <v>4.8</v>
-      </c>
-      <c r="BF8">
-        <v>4.5</v>
-      </c>
-      <c r="BG8">
-        <v>4.8</v>
-      </c>
       <c r="BH8">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>16.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>105</v>
@@ -2619,13 +2619,13 @@
         <v>104</v>
       </c>
       <c r="F9">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -2637,7 +2637,7 @@
         <v>3.4</v>
       </c>
       <c r="L9">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="M9">
         <v>1.12</v>
@@ -2661,7 +2661,7 @@
         <v>5.3</v>
       </c>
       <c r="T9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U9">
         <v>1.74</v>
@@ -2670,10 +2670,10 @@
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X9">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>13</v>
@@ -2694,7 +2694,7 @@
         <v>22</v>
       </c>
       <c r="AE9">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
         <v>10.5</v>
@@ -2736,7 +2736,7 @@
         <v>21</v>
       </c>
       <c r="AS9">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AT9">
         <v>6</v>
@@ -2745,13 +2745,13 @@
         <v>7</v>
       </c>
       <c r="AV9">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW9">
         <v>36</v>
       </c>
       <c r="AX9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY9">
         <v>10.5</v>
@@ -2766,7 +2766,7 @@
         <v>20</v>
       </c>
       <c r="BC9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD9">
         <v>32</v>
@@ -2784,19 +2784,19 @@
         <v>2.84</v>
       </c>
       <c r="BI9">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ9">
         <v>12</v>
       </c>
       <c r="BK9">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
@@ -2808,16 +2808,16 @@
         <v>17</v>
       </c>
       <c r="BQ9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR9">
         <v>42</v>
       </c>
       <c r="BS9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9">
         <v>4.8</v>
@@ -2826,19 +2826,19 @@
         <v>55</v>
       </c>
       <c r="BW9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ9">
         <v>44</v>
       </c>
       <c r="CA9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>105</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="110">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>2026-07-30</t>
   </si>
   <si>
@@ -274,6 +277,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>21:30:00</t>
   </si>
   <si>
@@ -295,6 +301,9 @@
     <t>Sportivo San Lorenzo</t>
   </si>
   <si>
+    <t>Cumbaya FC</t>
+  </si>
+  <si>
     <t>Libertad</t>
   </si>
   <si>
@@ -319,6 +328,9 @@
     <t>Guarani (Par)</t>
   </si>
   <si>
+    <t>CD Cuenca Juniors</t>
+  </si>
+  <si>
     <t>Deportivo Recoleta</t>
   </si>
   <si>
@@ -331,7 +343,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 09:42:01</t>
+    <t>2026-07-29 11:49:36</t>
   </si>
 </sst>
 </file>
@@ -663,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -913,73 +925,73 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="G2">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K2">
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O2">
         <v>1.64</v>
       </c>
       <c r="P2">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R2">
         <v>1.16</v>
       </c>
       <c r="S2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
         <v>2.38</v>
       </c>
       <c r="U2">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V2">
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y2">
         <v>11</v>
@@ -997,10 +1009,10 @@
         <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF2">
         <v>11.5</v>
@@ -1015,25 +1027,25 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL2">
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AN2">
         <v>34</v>
       </c>
       <c r="AO2">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
         <v>10</v>
@@ -1048,7 +1060,7 @@
         <v>6</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>18.5</v>
@@ -1060,7 +1072,7 @@
         <v>10</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
         <v>26</v>
@@ -1075,13 +1087,13 @@
         <v>30</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="BF2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG2">
         <v>42</v>
@@ -1090,64 +1102,64 @@
         <v>2.62</v>
       </c>
       <c r="BI2">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO2">
         <v>3.65</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV2">
         <v>50</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>80</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1155,28 +1167,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F3">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G3">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J3">
         <v>3.85</v>
@@ -1185,61 +1197,61 @@
         <v>3.95</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q3">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R3">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U3">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W3">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y3">
         <v>18.5</v>
       </c>
       <c r="Z3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA3">
         <v>120</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE3">
         <v>65</v>
@@ -1251,52 +1263,52 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
         <v>19.5</v>
       </c>
       <c r="AK3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL3">
         <v>34</v>
       </c>
       <c r="AM3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
         <v>17</v>
       </c>
       <c r="AR3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS3">
         <v>38</v>
       </c>
       <c r="AT3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV3">
         <v>17</v>
       </c>
       <c r="AW3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX3">
         <v>10</v>
@@ -1305,7 +1317,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA3">
         <v>55</v>
@@ -1314,82 +1326,82 @@
         <v>18</v>
       </c>
       <c r="BC3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
         <v>30</v>
       </c>
       <c r="BE3">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="BF3">
         <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BH3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI3">
         <v>3.25</v>
       </c>
       <c r="BJ3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP3">
         <v>12.5</v>
       </c>
       <c r="BQ3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR3">
         <v>26</v>
       </c>
       <c r="BS3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1397,58 +1409,58 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G4">
         <v>4.5</v>
       </c>
       <c r="H4">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="I4">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
         <v>2.36</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T4">
         <v>2.02</v>
@@ -1457,40 +1469,40 @@
         <v>1.93</v>
       </c>
       <c r="V4">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="W4">
         <v>1.28</v>
       </c>
       <c r="X4">
+        <v>10.5</v>
+      </c>
+      <c r="Y4">
+        <v>7.6</v>
+      </c>
+      <c r="Z4">
+        <v>11.5</v>
+      </c>
+      <c r="AA4">
+        <v>26</v>
+      </c>
+      <c r="AB4">
+        <v>13</v>
+      </c>
+      <c r="AC4">
+        <v>7.2</v>
+      </c>
+      <c r="AD4">
         <v>11</v>
       </c>
-      <c r="Y4">
-        <v>7.4</v>
-      </c>
-      <c r="Z4">
-        <v>11</v>
-      </c>
-      <c r="AA4">
+      <c r="AE4">
         <v>25</v>
       </c>
-      <c r="AB4">
-        <v>13.5</v>
-      </c>
-      <c r="AC4">
-        <v>7.4</v>
-      </c>
-      <c r="AD4">
-        <v>10.5</v>
-      </c>
-      <c r="AE4">
-        <v>24</v>
-      </c>
       <c r="AF4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH4">
         <v>21</v>
@@ -1499,10 +1511,10 @@
         <v>48</v>
       </c>
       <c r="AJ4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL4">
         <v>80</v>
@@ -1511,13 +1523,13 @@
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AO4">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4">
         <v>7.2</v>
@@ -1526,10 +1538,10 @@
         <v>10</v>
       </c>
       <c r="AS4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU4">
         <v>7</v>
@@ -1541,7 +1553,7 @@
         <v>22</v>
       </c>
       <c r="AX4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY4">
         <v>17</v>
@@ -1550,10 +1562,10 @@
         <v>19</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB4">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BC4">
         <v>55</v>
@@ -1562,76 +1574,76 @@
         <v>70</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BF4">
         <v>75</v>
       </c>
       <c r="BG4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH4">
         <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.52</v>
+        <v>15</v>
       </c>
       <c r="BN4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO4">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BP4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ4">
+        <v>11.5</v>
+      </c>
+      <c r="BR4">
+        <v>55</v>
+      </c>
+      <c r="BS4">
         <v>12.5</v>
       </c>
-      <c r="BR4">
-        <v>60</v>
-      </c>
-      <c r="BS4">
-        <v>13.5</v>
-      </c>
       <c r="BT4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV4">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BW4">
         <v>8.199999999999999</v>
       </c>
       <c r="BX4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1639,16 +1651,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1873,440 +1885,440 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F6">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
-        <v>2.04</v>
+        <v>990</v>
       </c>
       <c r="H6">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="I6">
-        <v>5.1</v>
+        <v>990</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L6">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="O6">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.85</v>
+        <v>1.06</v>
       </c>
       <c r="Q6">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="S6">
-        <v>3.45</v>
+        <v>1.47</v>
       </c>
       <c r="T6">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.99</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7">
+        <v>1.86</v>
+      </c>
+      <c r="G7">
+        <v>2.04</v>
+      </c>
+      <c r="H7">
+        <v>4.3</v>
+      </c>
+      <c r="I7">
+        <v>5.6</v>
+      </c>
+      <c r="J7">
+        <v>3.45</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>1.36</v>
+      </c>
+      <c r="M7">
+        <v>1.07</v>
+      </c>
+      <c r="N7">
+        <v>3.45</v>
+      </c>
+      <c r="O7">
+        <v>1.32</v>
+      </c>
+      <c r="P7">
+        <v>1.85</v>
+      </c>
+      <c r="Q7">
+        <v>1.95</v>
+      </c>
+      <c r="R7">
+        <v>1.33</v>
+      </c>
+      <c r="S7">
+        <v>3.45</v>
+      </c>
+      <c r="T7">
+        <v>1.81</v>
+      </c>
+      <c r="U7">
+        <v>1.99</v>
+      </c>
+      <c r="V7">
+        <v>1.24</v>
+      </c>
+      <c r="W7">
+        <v>1.96</v>
+      </c>
+      <c r="X7">
+        <v>16</v>
+      </c>
+      <c r="Y7">
+        <v>18.5</v>
+      </c>
+      <c r="Z7">
+        <v>42</v>
+      </c>
+      <c r="AA7">
+        <v>130</v>
+      </c>
+      <c r="AB7">
+        <v>10</v>
+      </c>
+      <c r="AC7">
+        <v>9.6</v>
+      </c>
+      <c r="AD7">
+        <v>22</v>
+      </c>
+      <c r="AE7">
+        <v>75</v>
+      </c>
+      <c r="AF7">
+        <v>13.5</v>
+      </c>
+      <c r="AG7">
+        <v>12</v>
+      </c>
+      <c r="AH7">
+        <v>23</v>
+      </c>
+      <c r="AI7">
         <v>80</v>
       </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7">
-        <v>2.44</v>
-      </c>
-      <c r="G7">
-        <v>2.58</v>
-      </c>
-      <c r="H7">
-        <v>3.65</v>
-      </c>
-      <c r="I7">
-        <v>3.9</v>
-      </c>
-      <c r="J7">
-        <v>2.88</v>
-      </c>
-      <c r="K7">
-        <v>3.05</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.15</v>
-      </c>
-      <c r="N7">
-        <v>2.48</v>
-      </c>
-      <c r="O7">
-        <v>1.61</v>
-      </c>
-      <c r="P7">
-        <v>1.48</v>
-      </c>
-      <c r="Q7">
-        <v>2.82</v>
-      </c>
-      <c r="R7">
-        <v>1.17</v>
-      </c>
-      <c r="S7">
-        <v>6.2</v>
-      </c>
-      <c r="T7">
-        <v>2.22</v>
-      </c>
-      <c r="U7">
-        <v>1.72</v>
-      </c>
-      <c r="V7">
-        <v>1.35</v>
-      </c>
-      <c r="W7">
-        <v>1.63</v>
-      </c>
-      <c r="X7">
+      <c r="AJ7">
+        <v>25</v>
+      </c>
+      <c r="AK7">
+        <v>24</v>
+      </c>
+      <c r="AL7">
+        <v>44</v>
+      </c>
+      <c r="AM7">
+        <v>130</v>
+      </c>
+      <c r="AN7">
+        <v>16.5</v>
+      </c>
+      <c r="AO7">
+        <v>85</v>
+      </c>
+      <c r="AP7">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7">
+        <v>12</v>
+      </c>
+      <c r="AR7">
+        <v>4.6</v>
+      </c>
+      <c r="AS7">
+        <v>5</v>
+      </c>
+      <c r="AT7">
+        <v>7.4</v>
+      </c>
+      <c r="AU7">
+        <v>7.2</v>
+      </c>
+      <c r="AV7">
+        <v>15.5</v>
+      </c>
+      <c r="AW7">
+        <v>4.8</v>
+      </c>
+      <c r="AX7">
         <v>9</v>
       </c>
-      <c r="Y7">
+      <c r="AY7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7">
+        <v>16.5</v>
+      </c>
+      <c r="BA7">
+        <v>4.9</v>
+      </c>
+      <c r="BB7">
+        <v>16.5</v>
+      </c>
+      <c r="BC7">
+        <v>16</v>
+      </c>
+      <c r="BD7">
+        <v>4.6</v>
+      </c>
+      <c r="BE7">
+        <v>5</v>
+      </c>
+      <c r="BF7">
         <v>10.5</v>
       </c>
-      <c r="Z7">
-        <v>26</v>
-      </c>
-      <c r="AA7">
-        <v>110</v>
-      </c>
-      <c r="AB7">
-        <v>7.4</v>
-      </c>
-      <c r="AC7">
-        <v>7.6</v>
-      </c>
-      <c r="AD7">
-        <v>18</v>
-      </c>
-      <c r="AE7">
-        <v>70</v>
-      </c>
-      <c r="AF7">
-        <v>15</v>
-      </c>
-      <c r="AG7">
-        <v>13.5</v>
-      </c>
-      <c r="AH7">
-        <v>25</v>
-      </c>
-      <c r="AI7">
-        <v>120</v>
-      </c>
-      <c r="AJ7">
-        <v>40</v>
-      </c>
-      <c r="AK7">
-        <v>40</v>
-      </c>
-      <c r="AL7">
-        <v>75</v>
-      </c>
-      <c r="AM7">
-        <v>270</v>
-      </c>
-      <c r="AN7">
-        <v>46</v>
-      </c>
-      <c r="AO7">
-        <v>120</v>
-      </c>
-      <c r="AP7">
-        <v>5.8</v>
-      </c>
-      <c r="AQ7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR7">
-        <v>20</v>
-      </c>
-      <c r="AS7">
-        <v>7.4</v>
-      </c>
-      <c r="AT7">
-        <v>6.2</v>
-      </c>
-      <c r="AU7">
-        <v>6.2</v>
-      </c>
-      <c r="AV7">
-        <v>14</v>
-      </c>
-      <c r="AW7">
-        <v>7.2</v>
-      </c>
-      <c r="AX7">
-        <v>12</v>
-      </c>
-      <c r="AY7">
-        <v>11</v>
-      </c>
-      <c r="AZ7">
-        <v>20</v>
-      </c>
-      <c r="BA7">
-        <v>7.4</v>
-      </c>
-      <c r="BB7">
-        <v>6.6</v>
-      </c>
-      <c r="BC7">
-        <v>6.6</v>
-      </c>
-      <c r="BD7">
-        <v>7.2</v>
-      </c>
-      <c r="BE7">
-        <v>7.8</v>
-      </c>
-      <c r="BF7">
-        <v>6.8</v>
-      </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH7">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="BJ7">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2315,49 +2327,49 @@
         <v>10.5</v>
       </c>
       <c r="BN7">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO7">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="BP7">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BQ7">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU7">
+        <v>4.8</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
         <v>9</v>
       </c>
-      <c r="BT7">
-        <v>7</v>
-      </c>
-      <c r="BU7">
-        <v>5.7</v>
-      </c>
-      <c r="BV7">
-        <v>40</v>
-      </c>
-      <c r="BW7">
-        <v>8.6</v>
-      </c>
       <c r="BX7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
         <v>9.4</v>
       </c>
       <c r="BZ7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="CB7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2365,321 +2377,321 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F8">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="G8">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="I8">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J8">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="K8">
         <v>3.05</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
+        <v>1.14</v>
+      </c>
+      <c r="N8">
+        <v>2.48</v>
+      </c>
+      <c r="O8">
+        <v>1.61</v>
+      </c>
+      <c r="P8">
+        <v>1.49</v>
+      </c>
+      <c r="Q8">
+        <v>2.8</v>
+      </c>
+      <c r="R8">
         <v>1.16</v>
       </c>
-      <c r="N8">
-        <v>2.32</v>
-      </c>
-      <c r="O8">
-        <v>1.67</v>
-      </c>
-      <c r="P8">
-        <v>1.44</v>
-      </c>
-      <c r="Q8">
-        <v>3.05</v>
-      </c>
-      <c r="R8">
-        <v>1.15</v>
-      </c>
       <c r="S8">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="T8">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="U8">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="V8">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="X8">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z8">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AA8">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AB8">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC8">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD8">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE8">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AF8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG8">
         <v>15.5</v>
       </c>
       <c r="AH8">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AI8">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AJ8">
+        <v>42</v>
+      </c>
+      <c r="AK8">
+        <v>48</v>
+      </c>
+      <c r="AL8">
+        <v>75</v>
+      </c>
+      <c r="AM8">
+        <v>280</v>
+      </c>
+      <c r="AN8">
         <v>44</v>
       </c>
-      <c r="AK8">
-        <v>46</v>
-      </c>
-      <c r="AL8">
-        <v>95</v>
-      </c>
-      <c r="AM8">
-        <v>330</v>
-      </c>
-      <c r="AN8">
-        <v>55</v>
-      </c>
       <c r="AO8">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AP8">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ8">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AR8">
         <v>20</v>
       </c>
       <c r="AS8">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT8">
+        <v>6</v>
+      </c>
+      <c r="AU8">
+        <v>6.2</v>
+      </c>
+      <c r="AV8">
+        <v>12.5</v>
+      </c>
+      <c r="AW8">
+        <v>6.2</v>
+      </c>
+      <c r="AX8">
+        <v>10.5</v>
+      </c>
+      <c r="AY8">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8">
+        <v>17</v>
+      </c>
+      <c r="BA8">
+        <v>6.4</v>
+      </c>
+      <c r="BB8">
+        <v>32</v>
+      </c>
+      <c r="BC8">
+        <v>6</v>
+      </c>
+      <c r="BD8">
+        <v>6.2</v>
+      </c>
+      <c r="BE8">
+        <v>6.6</v>
+      </c>
+      <c r="BF8">
+        <v>30</v>
+      </c>
+      <c r="BG8">
+        <v>6.4</v>
+      </c>
+      <c r="BH8">
+        <v>2.68</v>
+      </c>
+      <c r="BI8">
+        <v>2.16</v>
+      </c>
+      <c r="BJ8">
+        <v>12</v>
+      </c>
+      <c r="BK8">
+        <v>8.6</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>10.5</v>
+      </c>
+      <c r="BN8">
+        <v>5.3</v>
+      </c>
+      <c r="BO8">
+        <v>3.9</v>
+      </c>
+      <c r="BP8">
+        <v>24</v>
+      </c>
+      <c r="BQ8">
+        <v>7.6</v>
+      </c>
+      <c r="BR8">
+        <v>50</v>
+      </c>
+      <c r="BS8">
+        <v>9</v>
+      </c>
+      <c r="BT8">
+        <v>7</v>
+      </c>
+      <c r="BU8">
         <v>5.7</v>
       </c>
-      <c r="AU8">
-        <v>6.4</v>
-      </c>
-      <c r="AV8">
-        <v>17</v>
-      </c>
-      <c r="AW8">
-        <v>4.3</v>
-      </c>
-      <c r="AX8">
+      <c r="BV8">
+        <v>40</v>
+      </c>
+      <c r="BW8">
+        <v>8.6</v>
+      </c>
+      <c r="BX8">
+        <v>65</v>
+      </c>
+      <c r="BY8">
         <v>9.4</v>
       </c>
-      <c r="AY8">
-        <v>11</v>
-      </c>
-      <c r="AZ8">
-        <v>4</v>
-      </c>
-      <c r="BA8">
-        <v>4.4</v>
-      </c>
-      <c r="BB8">
-        <v>4.1</v>
-      </c>
-      <c r="BC8">
-        <v>4.1</v>
-      </c>
-      <c r="BD8">
-        <v>4.3</v>
-      </c>
-      <c r="BE8">
-        <v>4.4</v>
-      </c>
-      <c r="BF8">
-        <v>4.1</v>
-      </c>
-      <c r="BG8">
-        <v>4.4</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.04</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.04</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>1.04</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>1.04</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
-      <c r="BS8">
-        <v>1.04</v>
-      </c>
-      <c r="BT8">
-        <v>1000</v>
-      </c>
-      <c r="BU8">
-        <v>1.04</v>
-      </c>
-      <c r="BV8">
-        <v>1000</v>
-      </c>
-      <c r="BW8">
-        <v>1.04</v>
-      </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>1.04</v>
-      </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F9">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="G9">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="J9">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="K9">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="L9">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="M9">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="N9">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="P9">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Q9">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="R9">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="S9">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="T9">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U9">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W9">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Y9">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2688,160 +2700,402 @@
         <v>6.6</v>
       </c>
       <c r="AC9">
+        <v>7.4</v>
+      </c>
+      <c r="AD9">
+        <v>23</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>14</v>
+      </c>
+      <c r="AG9">
+        <v>15</v>
+      </c>
+      <c r="AH9">
+        <v>34</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>42</v>
+      </c>
+      <c r="AK9">
+        <v>44</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>320</v>
+      </c>
+      <c r="AN9">
+        <v>50</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>6.6</v>
+      </c>
+      <c r="AQ9">
+        <v>9</v>
+      </c>
+      <c r="AR9">
+        <v>20</v>
+      </c>
+      <c r="AS9">
+        <v>36</v>
+      </c>
+      <c r="AT9">
+        <v>5.9</v>
+      </c>
+      <c r="AU9">
+        <v>6.6</v>
+      </c>
+      <c r="AV9">
+        <v>17</v>
+      </c>
+      <c r="AW9">
+        <v>34</v>
+      </c>
+      <c r="AX9">
+        <v>11</v>
+      </c>
+      <c r="AY9">
+        <v>11.5</v>
+      </c>
+      <c r="AZ9">
+        <v>19.5</v>
+      </c>
+      <c r="BA9">
+        <v>42</v>
+      </c>
+      <c r="BB9">
+        <v>21</v>
+      </c>
+      <c r="BC9">
+        <v>22</v>
+      </c>
+      <c r="BD9">
+        <v>36</v>
+      </c>
+      <c r="BE9">
+        <v>55</v>
+      </c>
+      <c r="BF9">
+        <v>24</v>
+      </c>
+      <c r="BG9">
+        <v>40</v>
+      </c>
+      <c r="BH9">
+        <v>2.48</v>
+      </c>
+      <c r="BI9">
+        <v>2.16</v>
+      </c>
+      <c r="BJ9">
+        <v>12.5</v>
+      </c>
+      <c r="BK9">
+        <v>7.2</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>16.5</v>
+      </c>
+      <c r="BN9">
+        <v>4.9</v>
+      </c>
+      <c r="BO9">
+        <v>3.8</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>13</v>
+      </c>
+      <c r="BT9">
+        <v>7.2</v>
+      </c>
+      <c r="BU9">
+        <v>5.4</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>12.5</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>2.12</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>13.5</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10">
+        <v>1.99</v>
+      </c>
+      <c r="G10">
+        <v>2.02</v>
+      </c>
+      <c r="H10">
+        <v>4.8</v>
+      </c>
+      <c r="I10">
+        <v>4.9</v>
+      </c>
+      <c r="J10">
+        <v>3.35</v>
+      </c>
+      <c r="K10">
+        <v>3.4</v>
+      </c>
+      <c r="L10">
+        <v>1.57</v>
+      </c>
+      <c r="M10">
+        <v>1.13</v>
+      </c>
+      <c r="N10">
+        <v>2.72</v>
+      </c>
+      <c r="O10">
+        <v>1.55</v>
+      </c>
+      <c r="P10">
+        <v>1.57</v>
+      </c>
+      <c r="Q10">
+        <v>2.64</v>
+      </c>
+      <c r="R10">
+        <v>1.2</v>
+      </c>
+      <c r="S10">
+        <v>5.5</v>
+      </c>
+      <c r="T10">
+        <v>2.28</v>
+      </c>
+      <c r="U10">
+        <v>1.73</v>
+      </c>
+      <c r="V10">
+        <v>1.25</v>
+      </c>
+      <c r="W10">
+        <v>1.98</v>
+      </c>
+      <c r="X10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y10">
+        <v>12.5</v>
+      </c>
+      <c r="Z10">
+        <v>36</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>6.6</v>
+      </c>
+      <c r="AC10">
         <v>8</v>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <v>22</v>
       </c>
-      <c r="AE9">
-        <v>1000</v>
-      </c>
-      <c r="AF9">
+      <c r="AE10">
+        <v>95</v>
+      </c>
+      <c r="AF10">
         <v>10.5</v>
       </c>
-      <c r="AG9">
+      <c r="AG10">
         <v>11.5</v>
       </c>
-      <c r="AH9">
+      <c r="AH10">
         <v>27</v>
       </c>
-      <c r="AI9">
-        <v>1000</v>
-      </c>
-      <c r="AJ9">
-        <v>25</v>
-      </c>
-      <c r="AK9">
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>24</v>
+      </c>
+      <c r="AK10">
         <v>28</v>
       </c>
-      <c r="AL9">
-        <v>1000</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
         <v>32</v>
       </c>
-      <c r="AO9">
-        <v>1000</v>
-      </c>
-      <c r="AP9">
-        <v>8.4</v>
-      </c>
-      <c r="AQ9">
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ10">
         <v>11</v>
       </c>
-      <c r="AR9">
+      <c r="AR10">
         <v>21</v>
       </c>
-      <c r="AS9">
+      <c r="AS10">
+        <v>65</v>
+      </c>
+      <c r="AT10">
+        <v>6</v>
+      </c>
+      <c r="AU10">
+        <v>7</v>
+      </c>
+      <c r="AV10">
+        <v>17.5</v>
+      </c>
+      <c r="AW10">
+        <v>34</v>
+      </c>
+      <c r="AX10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY10">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10">
+        <v>20</v>
+      </c>
+      <c r="BA10">
         <v>40</v>
       </c>
-      <c r="AT9">
-        <v>6</v>
-      </c>
-      <c r="AU9">
+      <c r="BB10">
+        <v>20</v>
+      </c>
+      <c r="BC10">
+        <v>21</v>
+      </c>
+      <c r="BD10">
+        <v>32</v>
+      </c>
+      <c r="BE10">
+        <v>50</v>
+      </c>
+      <c r="BF10">
+        <v>20</v>
+      </c>
+      <c r="BG10">
+        <v>42</v>
+      </c>
+      <c r="BH10">
+        <v>2.84</v>
+      </c>
+      <c r="BI10">
+        <v>2.32</v>
+      </c>
+      <c r="BJ10">
+        <v>12</v>
+      </c>
+      <c r="BK10">
+        <v>5.9</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>11</v>
+      </c>
+      <c r="BN10">
+        <v>4.6</v>
+      </c>
+      <c r="BO10">
+        <v>3.6</v>
+      </c>
+      <c r="BP10">
+        <v>17</v>
+      </c>
+      <c r="BQ10">
         <v>7</v>
       </c>
-      <c r="AV9">
-        <v>17.5</v>
-      </c>
-      <c r="AW9">
-        <v>36</v>
-      </c>
-      <c r="AX9">
-        <v>9.4</v>
-      </c>
-      <c r="AY9">
-        <v>10.5</v>
-      </c>
-      <c r="AZ9">
-        <v>20</v>
-      </c>
-      <c r="BA9">
-        <v>40</v>
-      </c>
-      <c r="BB9">
-        <v>20</v>
-      </c>
-      <c r="BC9">
-        <v>21</v>
-      </c>
-      <c r="BD9">
-        <v>32</v>
-      </c>
-      <c r="BE9">
-        <v>50</v>
-      </c>
-      <c r="BF9">
-        <v>20</v>
-      </c>
-      <c r="BG9">
+      <c r="BR10">
         <v>42</v>
       </c>
-      <c r="BH9">
-        <v>2.84</v>
-      </c>
-      <c r="BI9">
-        <v>2.34</v>
-      </c>
-      <c r="BJ9">
-        <v>12</v>
-      </c>
-      <c r="BK9">
-        <v>5.9</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>11</v>
-      </c>
-      <c r="BN9">
-        <v>4.6</v>
-      </c>
-      <c r="BO9">
-        <v>3.6</v>
-      </c>
-      <c r="BP9">
-        <v>17</v>
-      </c>
-      <c r="BQ9">
-        <v>7</v>
-      </c>
-      <c r="BR9">
-        <v>42</v>
-      </c>
-      <c r="BS9">
+      <c r="BS10">
         <v>9.199999999999999</v>
       </c>
-      <c r="BT9">
+      <c r="BT10">
         <v>8.199999999999999</v>
       </c>
-      <c r="BU9">
+      <c r="BU10">
         <v>4.8</v>
       </c>
-      <c r="BV9">
+      <c r="BV10">
         <v>55</v>
       </c>
-      <c r="BW9">
+      <c r="BW10">
         <v>9.6</v>
       </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
         <v>10</v>
       </c>
-      <c r="BZ9">
+      <c r="BZ10">
         <v>44</v>
       </c>
-      <c r="CA9">
+      <c r="CA10">
         <v>9.199999999999999</v>
       </c>
-      <c r="CB9" t="s">
-        <v>105</v>
+      <c r="CB10" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="112">
   <si>
     <t>League</t>
   </si>
@@ -304,6 +304,9 @@
     <t>Cumbaya FC</t>
   </si>
   <si>
+    <t>Atletico Rojiblanco</t>
+  </si>
+  <si>
     <t>Libertad</t>
   </si>
   <si>
@@ -331,6 +334,9 @@
     <t>CD Cuenca Juniors</t>
   </si>
   <si>
+    <t>LDU de Portoviejo</t>
+  </si>
+  <si>
     <t>Deportivo Recoleta</t>
   </si>
   <si>
@@ -343,7 +349,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 11:49:36</t>
+    <t>2026-07-29 13:57:47</t>
   </si>
 </sst>
 </file>
@@ -675,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -934,25 +940,25 @@
         <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F2">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
         <v>1.66</v>
@@ -961,7 +967,7 @@
         <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O2">
         <v>1.64</v>
@@ -970,7 +976,7 @@
         <v>1.49</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R2">
         <v>1.16</v>
@@ -979,52 +985,52 @@
         <v>6.6</v>
       </c>
       <c r="T2">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="X2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z2">
         <v>32</v>
       </c>
       <c r="AA2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ2">
         <v>28</v>
@@ -1036,13 +1042,13 @@
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="AN2">
         <v>34</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP2">
         <v>7</v>
@@ -1057,7 +1063,7 @@
         <v>90</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1069,7 +1075,7 @@
         <v>70</v>
       </c>
       <c r="AX2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY2">
         <v>11</v>
@@ -1078,88 +1084,88 @@
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="BB2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD2">
         <v>50</v>
       </c>
       <c r="BE2">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BG2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH2">
         <v>2.62</v>
       </c>
       <c r="BI2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
         <v>3.65</v>
       </c>
       <c r="BP2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BQ2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR2">
         <v>48</v>
       </c>
       <c r="BS2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>80</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2">
         <v>55</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1176,22 +1182,22 @@
         <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F3">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="G3">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K3">
         <v>3.95</v>
@@ -1200,112 +1206,112 @@
         <v>1.4</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
         <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R3">
         <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V3">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y3">
         <v>18.5</v>
       </c>
       <c r="Z3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA3">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH3">
         <v>19</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM3">
         <v>110</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AP3">
         <v>14</v>
       </c>
       <c r="AQ3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR3">
         <v>36</v>
       </c>
       <c r="AS3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AW3">
         <v>55</v>
@@ -1314,7 +1320,7 @@
         <v>10</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
         <v>18</v>
@@ -1323,7 +1329,7 @@
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC3">
         <v>16.5</v>
@@ -1338,7 +1344,7 @@
         <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BH3">
         <v>3.5</v>
@@ -1350,58 +1356,58 @@
         <v>9.6</v>
       </c>
       <c r="BK3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BN3">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR3">
         <v>26</v>
       </c>
       <c r="BS3">
+        <v>12</v>
+      </c>
+      <c r="BT3">
+        <v>8.4</v>
+      </c>
+      <c r="BU3">
+        <v>6</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>14.5</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>15.5</v>
+      </c>
+      <c r="BZ3">
+        <v>22</v>
+      </c>
+      <c r="CA3">
         <v>11</v>
       </c>
-      <c r="BT3">
-        <v>8</v>
-      </c>
-      <c r="BU3">
-        <v>5.6</v>
-      </c>
-      <c r="BV3">
-        <v>40</v>
-      </c>
-      <c r="BW3">
-        <v>13</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>13.5</v>
-      </c>
-      <c r="BZ3">
-        <v>23</v>
-      </c>
-      <c r="CA3">
-        <v>10.5</v>
-      </c>
       <c r="CB3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1418,25 +1424,25 @@
         <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F4">
+        <v>4.2</v>
+      </c>
+      <c r="G4">
         <v>4.3</v>
       </c>
-      <c r="G4">
-        <v>4.5</v>
-      </c>
       <c r="H4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I4">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J4">
         <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>1.51</v>
@@ -1454,7 +1460,7 @@
         <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1469,13 +1475,13 @@
         <v>1.93</v>
       </c>
       <c r="V4">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>7.6</v>
@@ -1496,19 +1502,19 @@
         <v>11</v>
       </c>
       <c r="AE4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF4">
         <v>29</v>
       </c>
       <c r="AG4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH4">
         <v>21</v>
       </c>
       <c r="AI4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ4">
         <v>100</v>
@@ -1535,7 +1541,7 @@
         <v>7.2</v>
       </c>
       <c r="AR4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS4">
         <v>24</v>
@@ -1550,22 +1556,22 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA4">
         <v>44</v>
       </c>
       <c r="BB4">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="BC4">
         <v>55</v>
@@ -1574,49 +1580,49 @@
         <v>70</v>
       </c>
       <c r="BE4">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="BF4">
         <v>75</v>
       </c>
       <c r="BG4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BH4">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="BI4">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BN4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO4">
         <v>6.6</v>
       </c>
       <c r="BP4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BT4">
         <v>4.7</v>
@@ -1628,22 +1634,22 @@
         <v>16.5</v>
       </c>
       <c r="BW4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX4">
         <v>36</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BZ4">
         <v>36</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CB4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1660,7 +1666,7 @@
         <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1690,19 +1696,19 @@
         <v>1.25</v>
       </c>
       <c r="O5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P5">
         <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -1885,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1902,7 +1908,7 @@
         <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F6">
         <v>1.04</v>
@@ -1917,7 +1923,7 @@
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1953,10 +1959,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2127,440 +2133,440 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
         <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
         <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F7">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
-        <v>5.6</v>
+        <v>990</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L7">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="P7">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>3.45</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.99</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
         <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
         <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F8">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="G8">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="I8">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="J8">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="M8">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="O8">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="P8">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="Q8">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="R8">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="S8">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="T8">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="U8">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="W8">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="X8">
+        <v>16</v>
+      </c>
+      <c r="Y8">
+        <v>18.5</v>
+      </c>
+      <c r="Z8">
+        <v>42</v>
+      </c>
+      <c r="AA8">
+        <v>130</v>
+      </c>
+      <c r="AB8">
+        <v>10</v>
+      </c>
+      <c r="AC8">
+        <v>9.6</v>
+      </c>
+      <c r="AD8">
+        <v>22</v>
+      </c>
+      <c r="AE8">
+        <v>75</v>
+      </c>
+      <c r="AF8">
+        <v>13.5</v>
+      </c>
+      <c r="AG8">
+        <v>12</v>
+      </c>
+      <c r="AH8">
+        <v>23</v>
+      </c>
+      <c r="AI8">
+        <v>80</v>
+      </c>
+      <c r="AJ8">
+        <v>25</v>
+      </c>
+      <c r="AK8">
+        <v>24</v>
+      </c>
+      <c r="AL8">
+        <v>44</v>
+      </c>
+      <c r="AM8">
+        <v>130</v>
+      </c>
+      <c r="AN8">
+        <v>16.5</v>
+      </c>
+      <c r="AO8">
+        <v>85</v>
+      </c>
+      <c r="AP8">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8">
+        <v>12</v>
+      </c>
+      <c r="AR8">
+        <v>4.6</v>
+      </c>
+      <c r="AS8">
+        <v>5</v>
+      </c>
+      <c r="AT8">
+        <v>7.4</v>
+      </c>
+      <c r="AU8">
+        <v>7.2</v>
+      </c>
+      <c r="AV8">
+        <v>15.5</v>
+      </c>
+      <c r="AW8">
+        <v>4.8</v>
+      </c>
+      <c r="AX8">
         <v>9</v>
       </c>
-      <c r="Y8">
+      <c r="AY8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8">
+        <v>16.5</v>
+      </c>
+      <c r="BA8">
+        <v>4.9</v>
+      </c>
+      <c r="BB8">
+        <v>16.5</v>
+      </c>
+      <c r="BC8">
+        <v>16</v>
+      </c>
+      <c r="BD8">
+        <v>4.6</v>
+      </c>
+      <c r="BE8">
+        <v>5</v>
+      </c>
+      <c r="BF8">
         <v>10.5</v>
       </c>
-      <c r="Z8">
-        <v>26</v>
-      </c>
-      <c r="AA8">
-        <v>110</v>
-      </c>
-      <c r="AB8">
-        <v>7.4</v>
-      </c>
-      <c r="AC8">
-        <v>7.6</v>
-      </c>
-      <c r="AD8">
-        <v>20</v>
-      </c>
-      <c r="AE8">
-        <v>70</v>
-      </c>
-      <c r="AF8">
-        <v>15</v>
-      </c>
-      <c r="AG8">
-        <v>15.5</v>
-      </c>
-      <c r="AH8">
-        <v>26</v>
-      </c>
-      <c r="AI8">
-        <v>120</v>
-      </c>
-      <c r="AJ8">
-        <v>42</v>
-      </c>
-      <c r="AK8">
-        <v>48</v>
-      </c>
-      <c r="AL8">
-        <v>75</v>
-      </c>
-      <c r="AM8">
-        <v>280</v>
-      </c>
-      <c r="AN8">
-        <v>44</v>
-      </c>
-      <c r="AO8">
-        <v>120</v>
-      </c>
-      <c r="AP8">
-        <v>5.7</v>
-      </c>
-      <c r="AQ8">
-        <v>7.2</v>
-      </c>
-      <c r="AR8">
-        <v>20</v>
-      </c>
-      <c r="AS8">
-        <v>6.4</v>
-      </c>
-      <c r="AT8">
-        <v>6</v>
-      </c>
-      <c r="AU8">
-        <v>6.2</v>
-      </c>
-      <c r="AV8">
-        <v>12.5</v>
-      </c>
-      <c r="AW8">
-        <v>6.2</v>
-      </c>
-      <c r="AX8">
+      <c r="BG8">
+        <v>4.9</v>
+      </c>
+      <c r="BH8">
+        <v>3.45</v>
+      </c>
+      <c r="BI8">
+        <v>3</v>
+      </c>
+      <c r="BJ8">
         <v>10.5</v>
       </c>
-      <c r="AY8">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8">
-        <v>17</v>
-      </c>
-      <c r="BA8">
-        <v>6.4</v>
-      </c>
-      <c r="BB8">
-        <v>32</v>
-      </c>
-      <c r="BC8">
-        <v>6</v>
-      </c>
-      <c r="BD8">
-        <v>6.2</v>
-      </c>
-      <c r="BE8">
-        <v>6.6</v>
-      </c>
-      <c r="BF8">
-        <v>30</v>
-      </c>
-      <c r="BG8">
-        <v>6.4</v>
-      </c>
-      <c r="BH8">
-        <v>2.68</v>
-      </c>
-      <c r="BI8">
-        <v>2.16</v>
-      </c>
-      <c r="BJ8">
-        <v>12</v>
-      </c>
       <c r="BK8">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2569,49 +2575,49 @@
         <v>10.5</v>
       </c>
       <c r="BN8">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO8">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BP8">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BQ8">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR8">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU8">
+        <v>4.8</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
         <v>9</v>
       </c>
-      <c r="BT8">
-        <v>7</v>
-      </c>
-      <c r="BU8">
-        <v>5.7</v>
-      </c>
-      <c r="BV8">
-        <v>40</v>
-      </c>
-      <c r="BW8">
-        <v>8.6</v>
-      </c>
       <c r="BX8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
         <v>9.4</v>
       </c>
       <c r="BZ8">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2628,312 +2634,312 @@
         <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F9">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="G9">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="H9">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="I9">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="J9">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L9">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M9">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O9">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="P9">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q9">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="R9">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S9">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="T9">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="U9">
+        <v>1.73</v>
+      </c>
+      <c r="V9">
+        <v>1.36</v>
+      </c>
+      <c r="W9">
         <v>1.65</v>
       </c>
-      <c r="V9">
-        <v>1.31</v>
-      </c>
-      <c r="W9">
-        <v>1.71</v>
-      </c>
       <c r="X9">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB9">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD9">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG9">
         <v>15</v>
       </c>
       <c r="AH9">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AI9">
         <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AK9">
         <v>44</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM9">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AO9">
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AR9">
         <v>20</v>
       </c>
       <c r="AS9">
+        <v>32</v>
+      </c>
+      <c r="AT9">
+        <v>6.6</v>
+      </c>
+      <c r="AU9">
+        <v>6.2</v>
+      </c>
+      <c r="AV9">
+        <v>15</v>
+      </c>
+      <c r="AW9">
+        <v>29</v>
+      </c>
+      <c r="AX9">
+        <v>12</v>
+      </c>
+      <c r="AY9">
+        <v>12</v>
+      </c>
+      <c r="AZ9">
+        <v>21</v>
+      </c>
+      <c r="BA9">
+        <v>38</v>
+      </c>
+      <c r="BB9">
+        <v>32</v>
+      </c>
+      <c r="BC9">
+        <v>23</v>
+      </c>
+      <c r="BD9">
+        <v>34</v>
+      </c>
+      <c r="BE9">
+        <v>48</v>
+      </c>
+      <c r="BF9">
+        <v>23</v>
+      </c>
+      <c r="BG9">
         <v>36</v>
       </c>
-      <c r="AT9">
-        <v>5.9</v>
-      </c>
-      <c r="AU9">
-        <v>6.6</v>
-      </c>
-      <c r="AV9">
-        <v>17</v>
-      </c>
-      <c r="AW9">
-        <v>34</v>
-      </c>
-      <c r="AX9">
-        <v>11</v>
-      </c>
-      <c r="AY9">
-        <v>11.5</v>
-      </c>
-      <c r="AZ9">
-        <v>19.5</v>
-      </c>
-      <c r="BA9">
-        <v>42</v>
-      </c>
-      <c r="BB9">
-        <v>21</v>
-      </c>
-      <c r="BC9">
-        <v>22</v>
-      </c>
-      <c r="BD9">
-        <v>36</v>
-      </c>
-      <c r="BE9">
-        <v>55</v>
-      </c>
-      <c r="BF9">
-        <v>24</v>
-      </c>
-      <c r="BG9">
-        <v>40</v>
-      </c>
       <c r="BH9">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="BI9">
         <v>2.16</v>
       </c>
       <c r="BJ9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK9">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN9">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BO9">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ9">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS9">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BT9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU9">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY9">
-        <v>2.12</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA9">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="CB9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
         <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
         <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F10">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="H10">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J10">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="K10">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="L10">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="M10">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N10">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="O10">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="P10">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="Q10">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="R10">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="S10">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="T10">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U10">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W10">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="X10">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="Y10">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z10">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -2942,160 +2948,402 @@
         <v>6.6</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE10">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AG10">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AH10">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AI10">
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AK10">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AL10">
         <v>1000</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN10">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS10">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AT10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU10">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW10">
         <v>34</v>
       </c>
       <c r="AX10">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AY10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10">
         <v>20</v>
       </c>
       <c r="BA10">
+        <v>42</v>
+      </c>
+      <c r="BB10">
+        <v>21</v>
+      </c>
+      <c r="BC10">
+        <v>23</v>
+      </c>
+      <c r="BD10">
+        <v>36</v>
+      </c>
+      <c r="BE10">
+        <v>55</v>
+      </c>
+      <c r="BF10">
+        <v>24</v>
+      </c>
+      <c r="BG10">
         <v>40</v>
       </c>
-      <c r="BB10">
+      <c r="BH10">
+        <v>2.48</v>
+      </c>
+      <c r="BI10">
+        <v>2.16</v>
+      </c>
+      <c r="BJ10">
+        <v>12.5</v>
+      </c>
+      <c r="BK10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>16.5</v>
+      </c>
+      <c r="BN10">
+        <v>4.9</v>
+      </c>
+      <c r="BO10">
+        <v>3.8</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>13</v>
+      </c>
+      <c r="BT10">
+        <v>7.2</v>
+      </c>
+      <c r="BU10">
+        <v>5.4</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>12.5</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>2.12</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>13.5</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11">
+        <v>1.99</v>
+      </c>
+      <c r="G11">
+        <v>2.02</v>
+      </c>
+      <c r="H11">
+        <v>4.8</v>
+      </c>
+      <c r="I11">
+        <v>4.9</v>
+      </c>
+      <c r="J11">
+        <v>3.35</v>
+      </c>
+      <c r="K11">
+        <v>3.4</v>
+      </c>
+      <c r="L11">
+        <v>1.57</v>
+      </c>
+      <c r="M11">
+        <v>1.13</v>
+      </c>
+      <c r="N11">
+        <v>2.7</v>
+      </c>
+      <c r="O11">
+        <v>1.55</v>
+      </c>
+      <c r="P11">
+        <v>1.57</v>
+      </c>
+      <c r="Q11">
+        <v>2.64</v>
+      </c>
+      <c r="R11">
+        <v>1.2</v>
+      </c>
+      <c r="S11">
+        <v>5.5</v>
+      </c>
+      <c r="T11">
+        <v>2.3</v>
+      </c>
+      <c r="U11">
+        <v>1.73</v>
+      </c>
+      <c r="V11">
+        <v>1.25</v>
+      </c>
+      <c r="W11">
+        <v>1.98</v>
+      </c>
+      <c r="X11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y11">
+        <v>12.5</v>
+      </c>
+      <c r="Z11">
+        <v>36</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>6.6</v>
+      </c>
+      <c r="AC11">
+        <v>8</v>
+      </c>
+      <c r="AD11">
+        <v>22</v>
+      </c>
+      <c r="AE11">
+        <v>95</v>
+      </c>
+      <c r="AF11">
+        <v>10.5</v>
+      </c>
+      <c r="AG11">
+        <v>11.5</v>
+      </c>
+      <c r="AH11">
+        <v>27</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>24</v>
+      </c>
+      <c r="AK11">
+        <v>28</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>25</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>8</v>
+      </c>
+      <c r="AQ11">
+        <v>11</v>
+      </c>
+      <c r="AR11">
+        <v>21</v>
+      </c>
+      <c r="AS11">
+        <v>65</v>
+      </c>
+      <c r="AT11">
+        <v>6</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>18</v>
+      </c>
+      <c r="AW11">
+        <v>34</v>
+      </c>
+      <c r="AX11">
+        <v>9.4</v>
+      </c>
+      <c r="AY11">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11">
         <v>20</v>
       </c>
-      <c r="BC10">
+      <c r="BA11">
+        <v>40</v>
+      </c>
+      <c r="BB11">
+        <v>20</v>
+      </c>
+      <c r="BC11">
         <v>21</v>
       </c>
-      <c r="BD10">
+      <c r="BD11">
         <v>32</v>
       </c>
-      <c r="BE10">
+      <c r="BE11">
         <v>50</v>
       </c>
-      <c r="BF10">
+      <c r="BF11">
         <v>20</v>
       </c>
-      <c r="BG10">
+      <c r="BG11">
         <v>42</v>
       </c>
-      <c r="BH10">
+      <c r="BH11">
         <v>2.84</v>
       </c>
-      <c r="BI10">
+      <c r="BI11">
         <v>2.32</v>
       </c>
-      <c r="BJ10">
+      <c r="BJ11">
         <v>12</v>
       </c>
-      <c r="BK10">
-        <v>5.9</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
+      <c r="BK11">
+        <v>6.2</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
         <v>11</v>
       </c>
-      <c r="BN10">
+      <c r="BN11">
         <v>4.6</v>
       </c>
-      <c r="BO10">
-        <v>3.6</v>
-      </c>
-      <c r="BP10">
+      <c r="BO11">
+        <v>3.9</v>
+      </c>
+      <c r="BP11">
         <v>17</v>
       </c>
-      <c r="BQ10">
+      <c r="BQ11">
         <v>7</v>
       </c>
-      <c r="BR10">
+      <c r="BR11">
         <v>42</v>
       </c>
-      <c r="BS10">
+      <c r="BS11">
         <v>9.199999999999999</v>
       </c>
-      <c r="BT10">
+      <c r="BT11">
         <v>8.199999999999999</v>
       </c>
-      <c r="BU10">
+      <c r="BU11">
         <v>4.8</v>
       </c>
-      <c r="BV10">
+      <c r="BV11">
         <v>55</v>
       </c>
-      <c r="BW10">
+      <c r="BW11">
         <v>9.6</v>
       </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
+      <c r="BX11">
+        <v>75</v>
+      </c>
+      <c r="BY11">
         <v>10</v>
       </c>
-      <c r="BZ10">
+      <c r="BZ11">
         <v>44</v>
       </c>
-      <c r="CA10">
+      <c r="CA11">
         <v>9.199999999999999</v>
       </c>
-      <c r="CB10" t="s">
-        <v>109</v>
+      <c r="CB11" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -349,7 +349,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 13:57:47</t>
+    <t>2026-07-29 16:07:01</t>
   </si>
 </sst>
 </file>
@@ -943,16 +943,16 @@
         <v>101</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H2">
+        <v>4.6</v>
+      </c>
+      <c r="I2">
         <v>4.7</v>
-      </c>
-      <c r="I2">
-        <v>4.9</v>
       </c>
       <c r="J2">
         <v>3.15</v>
@@ -976,10 +976,10 @@
         <v>1.49</v>
       </c>
       <c r="Q2">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="R2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S2">
         <v>6.6</v>
@@ -988,13 +988,13 @@
         <v>2.42</v>
       </c>
       <c r="U2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X2">
         <v>7.6</v>
@@ -1006,7 +1006,7 @@
         <v>32</v>
       </c>
       <c r="AA2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB2">
         <v>6.2</v>
@@ -1018,7 +1018,7 @@
         <v>22</v>
       </c>
       <c r="AE2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF2">
         <v>11</v>
@@ -1042,7 +1042,7 @@
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AN2">
         <v>34</v>
@@ -1063,7 +1063,7 @@
         <v>90</v>
       </c>
       <c r="AT2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1075,7 +1075,7 @@
         <v>70</v>
       </c>
       <c r="AX2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2">
         <v>11</v>
@@ -1084,10 +1084,10 @@
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC2">
         <v>29</v>
@@ -1096,10 +1096,10 @@
         <v>50</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="BF2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BG2">
         <v>44</v>
@@ -1185,19 +1185,19 @@
         <v>102</v>
       </c>
       <c r="F3">
+        <v>1.77</v>
+      </c>
+      <c r="G3">
         <v>1.78</v>
       </c>
-      <c r="G3">
-        <v>1.79</v>
-      </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K3">
         <v>3.95</v>
@@ -1206,19 +1206,19 @@
         <v>1.4</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
         <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q3">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R3">
         <v>1.4</v>
@@ -1227,16 +1227,16 @@
         <v>3.35</v>
       </c>
       <c r="T3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X3">
         <v>14.5</v>
@@ -1251,16 +1251,16 @@
         <v>360</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC3">
         <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AF3">
         <v>10.5</v>
@@ -1269,16 +1269,16 @@
         <v>9.6</v>
       </c>
       <c r="AH3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI3">
         <v>75</v>
       </c>
       <c r="AJ3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL3">
         <v>36</v>
@@ -1290,7 +1290,7 @@
         <v>11.5</v>
       </c>
       <c r="AO3">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AP3">
         <v>14</v>
@@ -1299,28 +1299,28 @@
         <v>17.5</v>
       </c>
       <c r="AR3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AS3">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AT3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW3">
         <v>55</v>
       </c>
       <c r="AX3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
         <v>18</v>
@@ -1332,10 +1332,10 @@
         <v>17</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE3">
         <v>85</v>
@@ -1347,16 +1347,16 @@
         <v>70</v>
       </c>
       <c r="BH3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI3">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1365,10 +1365,10 @@
         <v>19</v>
       </c>
       <c r="BN3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP3">
         <v>12</v>
@@ -1389,7 +1389,7 @@
         <v>6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW3">
         <v>14.5</v>
@@ -1401,10 +1401,10 @@
         <v>15.5</v>
       </c>
       <c r="BZ3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1433,7 +1433,7 @@
         <v>4.3</v>
       </c>
       <c r="H4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I4">
         <v>2.16</v>
@@ -1442,37 +1442,37 @@
         <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R4">
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V4">
         <v>1.86</v>
@@ -1481,7 +1481,7 @@
         <v>1.3</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
         <v>7.6</v>
@@ -1493,7 +1493,7 @@
         <v>26</v>
       </c>
       <c r="AB4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC4">
         <v>7.2</v>
@@ -1505,7 +1505,7 @@
         <v>26</v>
       </c>
       <c r="AF4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG4">
         <v>17.5</v>
@@ -1547,13 +1547,13 @@
         <v>24</v>
       </c>
       <c r="AT4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW4">
         <v>23</v>
@@ -1562,7 +1562,7 @@
         <v>26</v>
       </c>
       <c r="AY4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ4">
         <v>20</v>
@@ -1580,7 +1580,7 @@
         <v>70</v>
       </c>
       <c r="BE4">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="BF4">
         <v>75</v>
@@ -1589,7 +1589,7 @@
         <v>20</v>
       </c>
       <c r="BH4">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BI4">
         <v>2.74</v>
@@ -1604,7 +1604,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BN4">
         <v>7.2</v>
@@ -1616,37 +1616,37 @@
         <v>38</v>
       </c>
       <c r="BQ4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BT4">
         <v>4.7</v>
       </c>
       <c r="BU4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV4">
         <v>16.5</v>
       </c>
       <c r="BW4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX4">
         <v>36</v>
       </c>
       <c r="BY4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB4" t="s">
         <v>111</v>
@@ -2156,7 +2156,7 @@
         <v>1.04</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H7">
         <v>1.04</v>
@@ -2165,7 +2165,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2201,7 +2201,7 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
         <v>1.01</v>
@@ -2398,7 +2398,7 @@
         <v>1.85</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H8">
         <v>4.3</v>
@@ -2446,7 +2446,7 @@
         <v>1.24</v>
       </c>
       <c r="W8">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="X8">
         <v>16</v>
@@ -2560,7 +2560,7 @@
         <v>3.45</v>
       </c>
       <c r="BI8">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
@@ -2637,31 +2637,31 @@
         <v>108</v>
       </c>
       <c r="F9">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="G9">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="H9">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="I9">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J9">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K9">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N9">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O9">
         <v>1.61</v>
@@ -2670,7 +2670,7 @@
         <v>1.49</v>
       </c>
       <c r="Q9">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
         <v>1.17</v>
@@ -2679,28 +2679,28 @@
         <v>6.2</v>
       </c>
       <c r="T9">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U9">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Z9">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB9">
         <v>7.4</v>
@@ -2709,7 +2709,7 @@
         <v>7</v>
       </c>
       <c r="AD9">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE9">
         <v>70</v>
@@ -2718,7 +2718,7 @@
         <v>14.5</v>
       </c>
       <c r="AG9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH9">
         <v>25</v>
@@ -2727,10 +2727,10 @@
         <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AK9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL9">
         <v>75</v>
@@ -2739,13 +2739,13 @@
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AO9">
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9">
         <v>8.4</v>
@@ -2757,7 +2757,7 @@
         <v>32</v>
       </c>
       <c r="AT9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU9">
         <v>6.2</v>
@@ -2769,10 +2769,10 @@
         <v>29</v>
       </c>
       <c r="AX9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9">
         <v>21</v>
@@ -2784,7 +2784,7 @@
         <v>32</v>
       </c>
       <c r="BC9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD9">
         <v>34</v>
@@ -2793,16 +2793,16 @@
         <v>48</v>
       </c>
       <c r="BF9">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BG9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH9">
         <v>2.68</v>
       </c>
       <c r="BI9">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ9">
         <v>12</v>
@@ -2817,34 +2817,34 @@
         <v>10.5</v>
       </c>
       <c r="BN9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO9">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ9">
         <v>7.6</v>
       </c>
       <c r="BR9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS9">
         <v>9</v>
       </c>
       <c r="BT9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU9">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX9">
         <v>65</v>
@@ -2856,7 +2856,7 @@
         <v>60</v>
       </c>
       <c r="CA9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2897,7 +2897,7 @@
         <v>3.05</v>
       </c>
       <c r="L10">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="M10">
         <v>1.16</v>
@@ -2906,7 +2906,7 @@
         <v>2.34</v>
       </c>
       <c r="O10">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P10">
         <v>1.44</v>
@@ -2930,7 +2930,7 @@
         <v>1.31</v>
       </c>
       <c r="W10">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X10">
         <v>7.6</v>
@@ -2939,7 +2939,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -2957,7 +2957,7 @@
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG10">
         <v>15</v>
@@ -3050,7 +3050,7 @@
         <v>12.5</v>
       </c>
       <c r="BK10">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3130,7 +3130,7 @@
         <v>4.8</v>
       </c>
       <c r="I11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3139,7 +3139,7 @@
         <v>3.4</v>
       </c>
       <c r="L11">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="M11">
         <v>1.13</v>
@@ -3160,10 +3160,10 @@
         <v>1.2</v>
       </c>
       <c r="S11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U11">
         <v>1.73</v>
@@ -3268,7 +3268,7 @@
         <v>20</v>
       </c>
       <c r="BC11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD11">
         <v>32</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -349,7 +349,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 16:07:01</t>
+    <t>2026-07-29 18:15:31</t>
   </si>
 </sst>
 </file>
@@ -943,16 +943,16 @@
         <v>101</v>
       </c>
       <c r="F2">
+        <v>2.1</v>
+      </c>
+      <c r="G2">
         <v>2.12</v>
-      </c>
-      <c r="G2">
-        <v>2.14</v>
       </c>
       <c r="H2">
         <v>4.6</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2">
         <v>3.15</v>
@@ -961,25 +961,25 @@
         <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M2">
         <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O2">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q2">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="R2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
         <v>6.6</v>
@@ -991,10 +991,10 @@
         <v>1.66</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X2">
         <v>7.6</v>
@@ -1039,7 +1039,7 @@
         <v>34</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM2">
         <v>260</v>
@@ -1051,7 +1051,7 @@
         <v>170</v>
       </c>
       <c r="AP2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2">
         <v>10</v>
@@ -1096,73 +1096,73 @@
         <v>50</v>
       </c>
       <c r="BE2">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG2">
         <v>44</v>
       </c>
       <c r="BH2">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="BI2">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BN2">
         <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
         <v>19</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR2">
         <v>48</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
         <v>55</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX2">
         <v>80</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ2">
         <v>55</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1191,13 +1191,13 @@
         <v>1.78</v>
       </c>
       <c r="H3">
+        <v>5.4</v>
+      </c>
+      <c r="I3">
         <v>5.5</v>
       </c>
-      <c r="I3">
-        <v>5.6</v>
-      </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K3">
         <v>3.95</v>
@@ -1209,34 +1209,34 @@
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O3">
         <v>1.31</v>
       </c>
       <c r="P3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q3">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V3">
         <v>1.21</v>
       </c>
       <c r="W3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X3">
         <v>14.5</v>
@@ -1248,25 +1248,25 @@
         <v>42</v>
       </c>
       <c r="AA3">
-        <v>360</v>
+        <v>140</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3">
         <v>21</v>
       </c>
       <c r="AE3">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF3">
         <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3">
         <v>19.5</v>
@@ -1275,7 +1275,7 @@
         <v>75</v>
       </c>
       <c r="AJ3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK3">
         <v>17.5</v>
@@ -1284,16 +1284,16 @@
         <v>36</v>
       </c>
       <c r="AM3">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AN3">
         <v>11.5</v>
       </c>
       <c r="AO3">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AP3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3">
         <v>17.5</v>
@@ -1302,10 +1302,10 @@
         <v>40</v>
       </c>
       <c r="AS3">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU3">
         <v>8</v>
@@ -1314,10 +1314,10 @@
         <v>19</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AX3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY3">
         <v>9.4</v>
@@ -1326,13 +1326,13 @@
         <v>18</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB3">
         <v>17</v>
       </c>
       <c r="BC3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
         <v>32</v>
@@ -1347,22 +1347,22 @@
         <v>70</v>
       </c>
       <c r="BH3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ3">
         <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BN3">
         <v>4.3</v>
@@ -1374,37 +1374,37 @@
         <v>12</v>
       </c>
       <c r="BQ3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR3">
         <v>26</v>
       </c>
       <c r="BS3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT3">
         <v>8.4</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BV3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BZ3">
         <v>21</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1427,16 +1427,16 @@
         <v>103</v>
       </c>
       <c r="F4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H4">
+        <v>2.12</v>
+      </c>
+      <c r="I4">
         <v>2.14</v>
-      </c>
-      <c r="I4">
-        <v>2.16</v>
       </c>
       <c r="J4">
         <v>3.3</v>
@@ -1445,16 +1445,16 @@
         <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M4">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
         <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
         <v>1.68</v>
@@ -1466,7 +1466,7 @@
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
         <v>2.04</v>
@@ -1475,13 +1475,13 @@
         <v>1.92</v>
       </c>
       <c r="V4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>7.6</v>
@@ -1493,10 +1493,10 @@
         <v>26</v>
       </c>
       <c r="AB4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
         <v>11</v>
@@ -1529,7 +1529,7 @@
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AO4">
         <v>22</v>
@@ -1550,13 +1550,13 @@
         <v>11.5</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX4">
         <v>26</v>
@@ -1568,10 +1568,10 @@
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB4">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BC4">
         <v>55</v>
@@ -1580,7 +1580,7 @@
         <v>70</v>
       </c>
       <c r="BE4">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BF4">
         <v>75</v>
@@ -1589,7 +1589,7 @@
         <v>20</v>
       </c>
       <c r="BH4">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BI4">
         <v>2.74</v>
@@ -1604,7 +1604,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN4">
         <v>7.2</v>
@@ -1622,7 +1622,7 @@
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BT4">
         <v>4.7</v>
@@ -1634,13 +1634,13 @@
         <v>16.5</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX4">
         <v>36</v>
       </c>
       <c r="BY4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ4">
         <v>38</v>
@@ -1669,103 +1669,103 @@
         <v>104</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="O5">
         <v>1.48</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q5">
-        <v>1.48</v>
+        <v>2.32</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.48</v>
+        <v>4.5</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X5">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
         <v>1000</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM5">
         <v>1000</v>
@@ -1774,61 +1774,61 @@
         <v>1000</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="AR5">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="AT5">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="AU5">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="AV5">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="AW5">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="AX5">
-        <v>1.04</v>
+        <v>18.5</v>
       </c>
       <c r="AY5">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BB5">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BC5">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BD5">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BE5">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BF5">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BG5">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1923,7 +1923,7 @@
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2165,7 +2165,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2261,52 +2261,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2398,13 +2398,13 @@
         <v>1.85</v>
       </c>
       <c r="G8">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H8">
         <v>4.3</v>
       </c>
       <c r="I8">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J8">
         <v>3.5</v>
@@ -2413,13 +2413,13 @@
         <v>4.1</v>
       </c>
       <c r="L8">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
         <v>1.32</v>
@@ -2446,7 +2446,7 @@
         <v>1.24</v>
       </c>
       <c r="W8">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X8">
         <v>16</v>
@@ -2560,7 +2560,7 @@
         <v>3.45</v>
       </c>
       <c r="BI8">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
@@ -2646,7 +2646,7 @@
         <v>3.45</v>
       </c>
       <c r="I9">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J9">
         <v>2.92</v>
@@ -2655,19 +2655,19 @@
         <v>3</v>
       </c>
       <c r="L9">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="M9">
         <v>1.15</v>
       </c>
       <c r="N9">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O9">
         <v>1.61</v>
       </c>
       <c r="P9">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -2700,7 +2700,7 @@
         <v>23</v>
       </c>
       <c r="AA9">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
         <v>7.4</v>
@@ -2715,7 +2715,7 @@
         <v>70</v>
       </c>
       <c r="AF9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG9">
         <v>14</v>
@@ -2751,7 +2751,7 @@
         <v>8.4</v>
       </c>
       <c r="AR9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS9">
         <v>32</v>
@@ -2879,16 +2879,16 @@
         <v>109</v>
       </c>
       <c r="F10">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H10">
         <v>4</v>
       </c>
       <c r="I10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J10">
         <v>2.98</v>
@@ -2903,13 +2903,13 @@
         <v>1.16</v>
       </c>
       <c r="N10">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O10">
         <v>1.67</v>
       </c>
       <c r="P10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q10">
         <v>3.05</v>
@@ -2927,16 +2927,16 @@
         <v>1.65</v>
       </c>
       <c r="V10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X10">
         <v>7.6</v>
       </c>
       <c r="Y10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z10">
         <v>27</v>
@@ -3026,7 +3026,7 @@
         <v>21</v>
       </c>
       <c r="BC10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD10">
         <v>36</v>
@@ -3044,40 +3044,40 @@
         <v>2.48</v>
       </c>
       <c r="BI10">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ10">
         <v>12.5</v>
       </c>
       <c r="BK10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BN10">
         <v>4.9</v>
       </c>
       <c r="BO10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU10">
         <v>5.4</v>
@@ -3086,19 +3086,19 @@
         <v>1000</v>
       </c>
       <c r="BW10">
+        <v>12</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>13</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
         <v>12.5</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>2.12</v>
-      </c>
-      <c r="BZ10">
-        <v>1000</v>
-      </c>
-      <c r="CA10">
-        <v>13.5</v>
       </c>
       <c r="CB10" t="s">
         <v>111</v>
@@ -3121,10 +3121,10 @@
         <v>110</v>
       </c>
       <c r="F11">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G11">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>4.8</v>
@@ -3139,64 +3139,64 @@
         <v>3.4</v>
       </c>
       <c r="L11">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="M11">
         <v>1.13</v>
       </c>
       <c r="N11">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O11">
         <v>1.55</v>
       </c>
       <c r="P11">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q11">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R11">
         <v>1.2</v>
       </c>
       <c r="S11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T11">
         <v>2.28</v>
       </c>
       <c r="U11">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V11">
         <v>1.25</v>
       </c>
       <c r="W11">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X11">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y11">
         <v>12.5</v>
       </c>
       <c r="Z11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB11">
         <v>6.6</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD11">
         <v>22</v>
       </c>
       <c r="AE11">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF11">
         <v>10.5</v>
@@ -3208,7 +3208,7 @@
         <v>27</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ11">
         <v>24</v>
@@ -3217,40 +3217,40 @@
         <v>28</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR11">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AS11">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AT11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW11">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AX11">
         <v>9.4</v>
@@ -3259,25 +3259,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA11">
         <v>40</v>
       </c>
       <c r="BB11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD11">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BE11">
         <v>50</v>
       </c>
       <c r="BF11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG11">
         <v>42</v>
@@ -3286,13 +3286,13 @@
         <v>2.84</v>
       </c>
       <c r="BI11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ11">
         <v>12</v>
       </c>
       <c r="BK11">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3304,7 +3304,7 @@
         <v>4.6</v>
       </c>
       <c r="BO11">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BP11">
         <v>17</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -349,7 +349,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 18:15:31</t>
+    <t>2026-07-29 20:24:43</t>
   </si>
 </sst>
 </file>
@@ -943,16 +943,16 @@
         <v>101</v>
       </c>
       <c r="F2">
+        <v>2.08</v>
+      </c>
+      <c r="G2">
         <v>2.1</v>
       </c>
-      <c r="G2">
-        <v>2.12</v>
-      </c>
       <c r="H2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J2">
         <v>3.15</v>
@@ -970,31 +970,31 @@
         <v>2.5</v>
       </c>
       <c r="O2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q2">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R2">
         <v>1.16</v>
       </c>
       <c r="S2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T2">
         <v>2.42</v>
       </c>
       <c r="U2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X2">
         <v>7.6</v>
@@ -1006,7 +1006,7 @@
         <v>32</v>
       </c>
       <c r="AA2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB2">
         <v>6.2</v>
@@ -1018,7 +1018,7 @@
         <v>22</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF2">
         <v>11</v>
@@ -1027,13 +1027,13 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK2">
         <v>34</v>
@@ -1048,22 +1048,22 @@
         <v>34</v>
       </c>
       <c r="AO2">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS2">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="AT2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1072,10 +1072,10 @@
         <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AX2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY2">
         <v>11</v>
@@ -1093,13 +1093,13 @@
         <v>29</v>
       </c>
       <c r="BD2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BE2">
         <v>55</v>
       </c>
       <c r="BF2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BG2">
         <v>44</v>
@@ -1114,16 +1114,16 @@
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
         <v>4.1</v>
@@ -1132,37 +1132,37 @@
         <v>19</v>
       </c>
       <c r="BQ2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR2">
         <v>48</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BV2">
         <v>55</v>
       </c>
       <c r="BW2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BY2">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BZ2">
         <v>55</v>
       </c>
       <c r="CA2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1191,10 +1191,10 @@
         <v>1.78</v>
       </c>
       <c r="H3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J3">
         <v>3.9</v>
@@ -1209,64 +1209,64 @@
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
         <v>1.31</v>
       </c>
       <c r="P3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q3">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
         <v>1.21</v>
       </c>
       <c r="W3">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="X3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y3">
         <v>18.5</v>
       </c>
       <c r="Z3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA3">
         <v>140</v>
       </c>
       <c r="AB3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF3">
         <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH3">
         <v>19.5</v>
@@ -1275,7 +1275,7 @@
         <v>75</v>
       </c>
       <c r="AJ3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK3">
         <v>17.5</v>
@@ -1284,40 +1284,40 @@
         <v>36</v>
       </c>
       <c r="AM3">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="AN3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO3">
-        <v>140</v>
+        <v>950</v>
       </c>
       <c r="AP3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR3">
         <v>40</v>
       </c>
       <c r="AS3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU3">
         <v>8</v>
       </c>
       <c r="AV3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AX3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3">
         <v>9.4</v>
@@ -1338,13 +1338,13 @@
         <v>32</v>
       </c>
       <c r="BE3">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="BF3">
         <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BH3">
         <v>3.5</v>
@@ -1353,16 +1353,16 @@
         <v>3.3</v>
       </c>
       <c r="BJ3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK3">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BN3">
         <v>4.3</v>
@@ -1374,37 +1374,37 @@
         <v>12</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BR3">
         <v>26</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU3">
         <v>7.6</v>
       </c>
       <c r="BV3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW3">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BX3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY3">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BZ3">
         <v>21</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1448,31 +1448,31 @@
         <v>1.54</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Q4">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
         <v>1.87</v>
@@ -1481,16 +1481,16 @@
         <v>1.29</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Y4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB4">
         <v>12.5</v>
@@ -1505,37 +1505,37 @@
         <v>26</v>
       </c>
       <c r="AF4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG4">
         <v>17.5</v>
       </c>
       <c r="AH4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI4">
         <v>50</v>
       </c>
       <c r="AJ4">
+        <v>110</v>
+      </c>
+      <c r="AK4">
+        <v>70</v>
+      </c>
+      <c r="AL4">
+        <v>85</v>
+      </c>
+      <c r="AM4">
+        <v>160</v>
+      </c>
+      <c r="AN4">
         <v>100</v>
-      </c>
-      <c r="AK4">
-        <v>65</v>
-      </c>
-      <c r="AL4">
-        <v>80</v>
-      </c>
-      <c r="AM4">
-        <v>150</v>
-      </c>
-      <c r="AN4">
-        <v>90</v>
       </c>
       <c r="AO4">
         <v>22</v>
       </c>
       <c r="AP4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
         <v>7.2</v>
@@ -1559,91 +1559,91 @@
         <v>24</v>
       </c>
       <c r="AX4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB4">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BC4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BD4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE4">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="BF4">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="BG4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH4">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BI4">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>18.5</v>
+        <v>160</v>
       </c>
       <c r="BN4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO4">
         <v>6.6</v>
       </c>
       <c r="BP4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BQ4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BR4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BT4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV4">
         <v>16.5</v>
       </c>
       <c r="BW4">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BX4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA4">
         <v>13.5</v>
@@ -1669,166 +1669,166 @@
         <v>104</v>
       </c>
       <c r="F5">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="G5">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="H5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I5">
         <v>2.38</v>
       </c>
       <c r="J5">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="K5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
         <v>1.52</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="P5">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="Q5">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S5">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="T5">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="U5">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="V5">
         <v>1.72</v>
       </c>
       <c r="W5">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X5">
+        <v>9</v>
+      </c>
+      <c r="Y5">
+        <v>7.6</v>
+      </c>
+      <c r="Z5">
+        <v>14</v>
+      </c>
+      <c r="AA5">
+        <v>36</v>
+      </c>
+      <c r="AB5">
+        <v>11.5</v>
+      </c>
+      <c r="AC5">
+        <v>7.6</v>
+      </c>
+      <c r="AD5">
+        <v>12.5</v>
+      </c>
+      <c r="AE5">
+        <v>34</v>
+      </c>
+      <c r="AF5">
+        <v>28</v>
+      </c>
+      <c r="AG5">
+        <v>18</v>
+      </c>
+      <c r="AH5">
+        <v>24</v>
+      </c>
+      <c r="AI5">
+        <v>65</v>
+      </c>
+      <c r="AJ5">
+        <v>110</v>
+      </c>
+      <c r="AK5">
+        <v>70</v>
+      </c>
+      <c r="AL5">
+        <v>200</v>
+      </c>
+      <c r="AM5">
+        <v>500</v>
+      </c>
+      <c r="AN5">
+        <v>110</v>
+      </c>
+      <c r="AO5">
+        <v>34</v>
+      </c>
+      <c r="AP5">
+        <v>7.6</v>
+      </c>
+      <c r="AQ5">
+        <v>6.4</v>
+      </c>
+      <c r="AR5">
         <v>11</v>
       </c>
-      <c r="Y5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z5">
-        <v>16.5</v>
-      </c>
-      <c r="AA5">
-        <v>42</v>
-      </c>
-      <c r="AB5">
-        <v>14.5</v>
-      </c>
-      <c r="AC5">
-        <v>9.4</v>
-      </c>
-      <c r="AD5">
-        <v>16</v>
-      </c>
-      <c r="AE5">
-        <v>42</v>
-      </c>
-      <c r="AF5">
-        <v>36</v>
-      </c>
-      <c r="AG5">
+      <c r="AS5">
         <v>22</v>
       </c>
-      <c r="AH5">
-        <v>950</v>
-      </c>
-      <c r="AI5">
-        <v>75</v>
-      </c>
-      <c r="AJ5">
-        <v>1000</v>
-      </c>
-      <c r="AK5">
-        <v>85</v>
-      </c>
-      <c r="AL5">
-        <v>100</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>1000</v>
-      </c>
-      <c r="AO5">
-        <v>42</v>
-      </c>
-      <c r="AP5">
-        <v>6.4</v>
-      </c>
-      <c r="AQ5">
-        <v>5.1</v>
-      </c>
-      <c r="AR5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS5">
-        <v>3.15</v>
-      </c>
       <c r="AT5">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AU5">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW5">
-        <v>3.15</v>
+        <v>21</v>
       </c>
       <c r="AX5">
         <v>18.5</v>
       </c>
       <c r="AY5">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BA5">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5">
-        <v>3.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC5">
-        <v>3.3</v>
+        <v>8.4</v>
       </c>
       <c r="BD5">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="BE5">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="BF5">
-        <v>3.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5">
-        <v>3.15</v>
+        <v>21</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1911,22 +1911,22 @@
         <v>105</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="G6">
-        <v>990</v>
+        <v>3.6</v>
       </c>
       <c r="H6">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.11</v>
+        <v>2.64</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1941,13 +1941,13 @@
         <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q6">
         <v>1.47</v>
       </c>
       <c r="R6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="S6">
         <v>1.47</v>
@@ -1959,118 +1959,118 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2165,7 +2165,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2177,22 +2177,22 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P7">
         <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R7">
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2318,61 +2318,61 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>111</v>
@@ -2401,19 +2401,19 @@
         <v>2.02</v>
       </c>
       <c r="H8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I8">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J8">
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2425,7 +2425,7 @@
         <v>1.32</v>
       </c>
       <c r="P8">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
         <v>1.96</v>
@@ -2458,7 +2458,7 @@
         <v>42</v>
       </c>
       <c r="AA8">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -2470,37 +2470,37 @@
         <v>22</v>
       </c>
       <c r="AE8">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AF8">
         <v>13.5</v>
       </c>
       <c r="AG8">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
         <v>23</v>
       </c>
       <c r="AI8">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AM8">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN8">
         <v>16.5</v>
       </c>
       <c r="AO8">
-        <v>85</v>
+        <v>310</v>
       </c>
       <c r="AP8">
         <v>10.5</v>
@@ -2509,10 +2509,10 @@
         <v>12</v>
       </c>
       <c r="AR8">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT8">
         <v>7.4</v>
@@ -2524,7 +2524,7 @@
         <v>15.5</v>
       </c>
       <c r="AW8">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AX8">
         <v>9</v>
@@ -2536,7 +2536,7 @@
         <v>16.5</v>
       </c>
       <c r="BA8">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB8">
         <v>16.5</v>
@@ -2545,16 +2545,16 @@
         <v>16</v>
       </c>
       <c r="BD8">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="BE8">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF8">
         <v>10.5</v>
       </c>
       <c r="BG8">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH8">
         <v>3.45</v>
@@ -2590,7 +2590,7 @@
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
         <v>8.199999999999999</v>
@@ -2640,19 +2640,19 @@
         <v>2.56</v>
       </c>
       <c r="G9">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I9">
         <v>3.7</v>
       </c>
       <c r="J9">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L9">
         <v>1.61</v>
@@ -2664,43 +2664,43 @@
         <v>2.48</v>
       </c>
       <c r="O9">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="P9">
         <v>1.48</v>
       </c>
       <c r="Q9">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="R9">
         <v>1.17</v>
       </c>
       <c r="S9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T9">
         <v>2.24</v>
       </c>
       <c r="U9">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V9">
         <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z9">
         <v>23</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB9">
         <v>7.4</v>
@@ -2712,7 +2712,7 @@
         <v>17.5</v>
       </c>
       <c r="AE9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF9">
         <v>15</v>
@@ -2721,10 +2721,10 @@
         <v>14</v>
       </c>
       <c r="AH9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ9">
         <v>44</v>
@@ -2739,13 +2739,13 @@
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9">
         <v>8.4</v>
@@ -2766,13 +2766,13 @@
         <v>15</v>
       </c>
       <c r="AW9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX9">
         <v>13</v>
       </c>
       <c r="AY9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ9">
         <v>21</v>
@@ -2790,19 +2790,19 @@
         <v>34</v>
       </c>
       <c r="BE9">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF9">
         <v>36</v>
       </c>
       <c r="BG9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH9">
         <v>2.68</v>
       </c>
       <c r="BI9">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="BJ9">
         <v>12</v>
@@ -2897,13 +2897,13 @@
         <v>3.05</v>
       </c>
       <c r="L10">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="M10">
         <v>1.16</v>
       </c>
       <c r="N10">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O10">
         <v>1.67</v>
@@ -2933,7 +2933,7 @@
         <v>1.72</v>
       </c>
       <c r="X10">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -2942,7 +2942,7 @@
         <v>27</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB10">
         <v>6.6</v>
@@ -2954,7 +2954,7 @@
         <v>23</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF10">
         <v>12.5</v>
@@ -2966,7 +2966,7 @@
         <v>34</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AJ10">
         <v>42</v>
@@ -2975,16 +2975,16 @@
         <v>44</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM10">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN10">
         <v>50</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP10">
         <v>6.4</v>
@@ -2999,13 +2999,13 @@
         <v>36</v>
       </c>
       <c r="AT10">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU10">
         <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AW10">
         <v>34</v>
@@ -3032,7 +3032,7 @@
         <v>36</v>
       </c>
       <c r="BE10">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="BF10">
         <v>24</v>
@@ -3044,40 +3044,40 @@
         <v>2.48</v>
       </c>
       <c r="BI10">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BJ10">
         <v>12.5</v>
       </c>
       <c r="BK10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN10">
         <v>4.9</v>
       </c>
       <c r="BO10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU10">
         <v>5.4</v>
@@ -3086,19 +3086,19 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB10" t="s">
         <v>111</v>
@@ -3121,13 +3121,13 @@
         <v>110</v>
       </c>
       <c r="F11">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I11">
         <v>5</v>
@@ -3142,7 +3142,7 @@
         <v>1.57</v>
       </c>
       <c r="M11">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N11">
         <v>2.74</v>
@@ -3154,19 +3154,19 @@
         <v>1.58</v>
       </c>
       <c r="Q11">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R11">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T11">
         <v>2.28</v>
       </c>
       <c r="U11">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V11">
         <v>1.25</v>
@@ -3175,7 +3175,7 @@
         <v>2</v>
       </c>
       <c r="X11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y11">
         <v>12.5</v>
@@ -3211,10 +3211,10 @@
         <v>120</v>
       </c>
       <c r="AJ11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL11">
         <v>60</v>
@@ -3223,13 +3223,13 @@
         <v>220</v>
       </c>
       <c r="AN11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AP11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ11">
         <v>11.5</v>
@@ -3238,10 +3238,10 @@
         <v>30</v>
       </c>
       <c r="AS11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU11">
         <v>7.4</v>
@@ -3256,7 +3256,7 @@
         <v>9.4</v>
       </c>
       <c r="AY11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
         <v>23</v>
@@ -3274,10 +3274,10 @@
         <v>50</v>
       </c>
       <c r="BE11">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG11">
         <v>42</v>
@@ -3292,13 +3292,13 @@
         <v>12</v>
       </c>
       <c r="BK11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN11">
         <v>4.6</v>
@@ -3307,7 +3307,7 @@
         <v>3.6</v>
       </c>
       <c r="BP11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ11">
         <v>7</v>
@@ -3316,31 +3316,31 @@
         <v>42</v>
       </c>
       <c r="BS11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT11">
         <v>8.199999999999999</v>
       </c>
       <c r="BU11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV11">
         <v>55</v>
       </c>
       <c r="BW11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX11">
         <v>75</v>
       </c>
       <c r="BY11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB11" t="s">
         <v>111</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -349,7 +349,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 20:24:43</t>
+    <t>2026-07-29 22:33:30</t>
   </si>
 </sst>
 </file>
@@ -943,226 +943,226 @@
         <v>101</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="H2">
-        <v>4.8</v>
+        <v>19.5</v>
       </c>
       <c r="I2">
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>5.3</v>
+      </c>
+      <c r="K2">
+        <v>5.4</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>3.5</v>
+      </c>
+      <c r="O2">
+        <v>1.38</v>
+      </c>
+      <c r="P2">
+        <v>1.53</v>
+      </c>
+      <c r="Q2">
+        <v>2.82</v>
+      </c>
+      <c r="R2">
+        <v>1.14</v>
+      </c>
+      <c r="S2">
+        <v>7.8</v>
+      </c>
+      <c r="T2">
+        <v>2.38</v>
+      </c>
+      <c r="U2">
+        <v>1.68</v>
+      </c>
+      <c r="V2">
+        <v>1.04</v>
+      </c>
+      <c r="W2">
+        <v>4.2</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>3.7</v>
+      </c>
+      <c r="AC2">
+        <v>6.8</v>
+      </c>
+      <c r="AD2">
+        <v>30</v>
+      </c>
+      <c r="AE2">
+        <v>270</v>
+      </c>
+      <c r="AF2">
         <v>4.9</v>
       </c>
-      <c r="J2">
-        <v>3.15</v>
-      </c>
-      <c r="K2">
-        <v>3.2</v>
-      </c>
-      <c r="L2">
-        <v>1.67</v>
-      </c>
-      <c r="M2">
-        <v>1.15</v>
-      </c>
-      <c r="N2">
-        <v>2.5</v>
-      </c>
-      <c r="O2">
-        <v>1.66</v>
-      </c>
-      <c r="P2">
-        <v>1.49</v>
-      </c>
-      <c r="Q2">
-        <v>3</v>
-      </c>
-      <c r="R2">
-        <v>1.16</v>
-      </c>
-      <c r="S2">
-        <v>6.8</v>
-      </c>
-      <c r="T2">
-        <v>2.42</v>
-      </c>
-      <c r="U2">
-        <v>1.67</v>
-      </c>
-      <c r="V2">
-        <v>1.25</v>
-      </c>
-      <c r="W2">
-        <v>1.9</v>
-      </c>
-      <c r="X2">
-        <v>7.6</v>
-      </c>
-      <c r="Y2">
-        <v>11.5</v>
-      </c>
-      <c r="Z2">
-        <v>32</v>
-      </c>
-      <c r="AA2">
-        <v>140</v>
-      </c>
-      <c r="AB2">
+      <c r="AG2">
+        <v>9.6</v>
+      </c>
+      <c r="AH2">
+        <v>38</v>
+      </c>
+      <c r="AI2">
+        <v>300</v>
+      </c>
+      <c r="AJ2">
+        <v>13.5</v>
+      </c>
+      <c r="AK2">
+        <v>27</v>
+      </c>
+      <c r="AL2">
+        <v>130</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>30</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>20</v>
+      </c>
+      <c r="AQ2">
+        <v>20</v>
+      </c>
+      <c r="AR2">
+        <v>20</v>
+      </c>
+      <c r="AS2">
+        <v>20</v>
+      </c>
+      <c r="AT2">
+        <v>3.45</v>
+      </c>
+      <c r="AU2">
         <v>6.2</v>
       </c>
-      <c r="AC2">
-        <v>7.6</v>
-      </c>
-      <c r="AD2">
-        <v>22</v>
-      </c>
-      <c r="AE2">
-        <v>100</v>
-      </c>
-      <c r="AF2">
-        <v>11</v>
-      </c>
-      <c r="AG2">
+      <c r="AV2">
+        <v>25</v>
+      </c>
+      <c r="AW2">
+        <v>130</v>
+      </c>
+      <c r="AX2">
+        <v>4.5</v>
+      </c>
+      <c r="AY2">
+        <v>8.4</v>
+      </c>
+      <c r="AZ2">
+        <v>30</v>
+      </c>
+      <c r="BA2">
+        <v>210</v>
+      </c>
+      <c r="BB2">
         <v>12</v>
       </c>
-      <c r="AH2">
-        <v>29</v>
-      </c>
-      <c r="AI2">
-        <v>180</v>
-      </c>
-      <c r="AJ2">
-        <v>27</v>
-      </c>
-      <c r="AK2">
-        <v>34</v>
-      </c>
-      <c r="AL2">
-        <v>70</v>
-      </c>
-      <c r="AM2">
-        <v>260</v>
-      </c>
-      <c r="AN2">
-        <v>34</v>
-      </c>
-      <c r="AO2">
-        <v>180</v>
-      </c>
-      <c r="AP2">
-        <v>7</v>
-      </c>
-      <c r="AQ2">
-        <v>10</v>
-      </c>
-      <c r="AR2">
-        <v>28</v>
-      </c>
-      <c r="AS2">
-        <v>40</v>
-      </c>
-      <c r="AT2">
-        <v>5.8</v>
-      </c>
-      <c r="AU2">
-        <v>6.8</v>
-      </c>
-      <c r="AV2">
-        <v>18.5</v>
-      </c>
-      <c r="AW2">
-        <v>55</v>
-      </c>
-      <c r="AX2">
-        <v>10</v>
-      </c>
-      <c r="AY2">
-        <v>11</v>
-      </c>
-      <c r="AZ2">
-        <v>26</v>
-      </c>
-      <c r="BA2">
-        <v>42</v>
-      </c>
-      <c r="BB2">
+      <c r="BC2">
         <v>24</v>
       </c>
-      <c r="BC2">
-        <v>29</v>
-      </c>
       <c r="BD2">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>400</v>
       </c>
       <c r="BF2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BG2">
-        <v>44</v>
+        <v>430</v>
       </c>
       <c r="BH2">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1185,226 +1185,226 @@
         <v>102</v>
       </c>
       <c r="F3">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="G3">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>2.72</v>
       </c>
       <c r="K3">
-        <v>3.95</v>
+        <v>2.76</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>1.73</v>
       </c>
       <c r="O3">
-        <v>1.31</v>
+        <v>2.32</v>
       </c>
       <c r="P3">
-        <v>2.04</v>
+        <v>1.2</v>
       </c>
       <c r="Q3">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="S3">
-        <v>3.35</v>
+        <v>16.5</v>
       </c>
       <c r="T3">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W3">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
-        <v>15</v>
+        <v>4.6</v>
       </c>
       <c r="Y3">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AC3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>20</v>
+        <v>990</v>
       </c>
       <c r="AE3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG3">
-        <v>10</v>
+        <v>990</v>
       </c>
       <c r="AH3">
-        <v>19.5</v>
+        <v>990</v>
       </c>
       <c r="AI3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>17.5</v>
+        <v>480</v>
       </c>
       <c r="AL3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="AO3">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AQ3">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AR3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AS3">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AT3">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="AW3">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="AX3">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="AZ3">
-        <v>18</v>
+        <v>5.4</v>
       </c>
       <c r="BA3">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="BB3">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>50</v>
       </c>
       <c r="BD3">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="BE3">
-        <v>38</v>
+        <v>7.4</v>
       </c>
       <c r="BF3">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="BG3">
-        <v>65</v>
+        <v>5.8</v>
       </c>
       <c r="BH3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1427,226 +1427,226 @@
         <v>103</v>
       </c>
       <c r="F4">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="G4">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="I4">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>140</v>
       </c>
       <c r="K4">
-        <v>3.35</v>
+        <v>200</v>
       </c>
       <c r="L4">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1.65</v>
+        <v>8.6</v>
       </c>
       <c r="Q4">
-        <v>2.48</v>
+        <v>1.12</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="S4">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>6.2</v>
       </c>
       <c r="U4">
-        <v>1.88</v>
+        <v>1.09</v>
       </c>
       <c r="V4">
-        <v>1.87</v>
+        <v>120</v>
       </c>
       <c r="W4">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
+        <v>9.6</v>
+      </c>
+      <c r="AA4">
+        <v>5.1</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>620</v>
+      </c>
+      <c r="AE4">
+        <v>990</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1.68</v>
+      </c>
+      <c r="AP4">
         <v>11</v>
       </c>
-      <c r="AA4">
-        <v>27</v>
-      </c>
-      <c r="AB4">
+      <c r="AQ4">
+        <v>11</v>
+      </c>
+      <c r="AR4">
+        <v>8.6</v>
+      </c>
+      <c r="AS4">
+        <v>4.6</v>
+      </c>
+      <c r="AT4">
+        <v>10.5</v>
+      </c>
+      <c r="AU4">
+        <v>11</v>
+      </c>
+      <c r="AV4">
+        <v>16.5</v>
+      </c>
+      <c r="AW4">
+        <v>10.5</v>
+      </c>
+      <c r="AX4">
+        <v>11</v>
+      </c>
+      <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
+        <v>11</v>
+      </c>
+      <c r="BA4">
+        <v>11</v>
+      </c>
+      <c r="BB4">
+        <v>11</v>
+      </c>
+      <c r="BC4">
+        <v>11</v>
+      </c>
+      <c r="BD4">
+        <v>11</v>
+      </c>
+      <c r="BE4">
         <v>12.5</v>
       </c>
-      <c r="AC4">
-        <v>7.4</v>
-      </c>
-      <c r="AD4">
+      <c r="BF4">
         <v>11</v>
       </c>
-      <c r="AE4">
-        <v>26</v>
-      </c>
-      <c r="AF4">
-        <v>29</v>
-      </c>
-      <c r="AG4">
-        <v>17.5</v>
-      </c>
-      <c r="AH4">
-        <v>22</v>
-      </c>
-      <c r="AI4">
-        <v>50</v>
-      </c>
-      <c r="AJ4">
-        <v>110</v>
-      </c>
-      <c r="AK4">
-        <v>70</v>
-      </c>
-      <c r="AL4">
-        <v>85</v>
-      </c>
-      <c r="AM4">
-        <v>160</v>
-      </c>
-      <c r="AN4">
-        <v>100</v>
-      </c>
-      <c r="AO4">
-        <v>22</v>
-      </c>
-      <c r="AP4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ4">
-        <v>7.2</v>
-      </c>
-      <c r="AR4">
-        <v>10.5</v>
-      </c>
-      <c r="AS4">
-        <v>24</v>
-      </c>
-      <c r="AT4">
-        <v>11.5</v>
-      </c>
-      <c r="AU4">
-        <v>7</v>
-      </c>
-      <c r="AV4">
-        <v>10</v>
-      </c>
-      <c r="AW4">
-        <v>24</v>
-      </c>
-      <c r="AX4">
-        <v>28</v>
-      </c>
-      <c r="AY4">
-        <v>16.5</v>
-      </c>
-      <c r="AZ4">
-        <v>21</v>
-      </c>
-      <c r="BA4">
-        <v>44</v>
-      </c>
-      <c r="BB4">
-        <v>90</v>
-      </c>
-      <c r="BC4">
-        <v>60</v>
-      </c>
-      <c r="BD4">
-        <v>65</v>
-      </c>
-      <c r="BE4">
-        <v>130</v>
-      </c>
-      <c r="BF4">
-        <v>95</v>
-      </c>
       <c r="BG4">
-        <v>21</v>
+        <v>1.67</v>
       </c>
       <c r="BH4">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>111</v>
@@ -1911,22 +1911,22 @@
         <v>105</v>
       </c>
       <c r="F6">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="G6">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="H6">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I6">
-        <v>990</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <v>2.64</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1941,16 +1941,16 @@
         <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Q6">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="R6">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="S6">
-        <v>1.47</v>
+        <v>1.05</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2028,13 +2028,13 @@
         <v>1.14</v>
       </c>
       <c r="AS6">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT6">
         <v>1.24</v>
       </c>
       <c r="AU6">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AV6">
         <v>1.14</v>
@@ -2055,7 +2055,7 @@
         <v>1.14</v>
       </c>
       <c r="BB6">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BC6">
         <v>1.14</v>
@@ -2165,7 +2165,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2180,19 +2180,19 @@
         <v>1.24</v>
       </c>
       <c r="O7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
         <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R7">
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2398,7 +2398,7 @@
         <v>1.85</v>
       </c>
       <c r="G8">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>4.4</v>
@@ -2407,13 +2407,13 @@
         <v>5.2</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="L8">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2446,13 +2446,13 @@
         <v>1.24</v>
       </c>
       <c r="W8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X8">
         <v>16</v>
       </c>
       <c r="Y8">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z8">
         <v>42</v>
@@ -2461,7 +2461,7 @@
         <v>900</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC8">
         <v>9.6</v>
@@ -2497,7 +2497,7 @@
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AO8">
         <v>310</v>
@@ -2512,7 +2512,7 @@
         <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT8">
         <v>7.4</v>
@@ -2524,7 +2524,7 @@
         <v>15.5</v>
       </c>
       <c r="AW8">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX8">
         <v>9</v>
@@ -2536,7 +2536,7 @@
         <v>16.5</v>
       </c>
       <c r="BA8">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB8">
         <v>16.5</v>
@@ -2548,13 +2548,13 @@
         <v>18</v>
       </c>
       <c r="BE8">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF8">
         <v>10.5</v>
       </c>
       <c r="BG8">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH8">
         <v>3.45</v>
@@ -2643,7 +2643,7 @@
         <v>2.64</v>
       </c>
       <c r="H9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I9">
         <v>3.7</v>
@@ -2664,19 +2664,19 @@
         <v>2.48</v>
       </c>
       <c r="O9">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P9">
         <v>1.48</v>
       </c>
       <c r="Q9">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
         <v>1.17</v>
       </c>
       <c r="S9">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T9">
         <v>2.24</v>
@@ -2739,7 +2739,7 @@
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO9">
         <v>220</v>
@@ -2802,7 +2802,7 @@
         <v>2.68</v>
       </c>
       <c r="BI9">
-        <v>2.42</v>
+        <v>2.14</v>
       </c>
       <c r="BJ9">
         <v>12</v>
@@ -2879,7 +2879,7 @@
         <v>109</v>
       </c>
       <c r="F10">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G10">
         <v>2.38</v>
@@ -2897,7 +2897,7 @@
         <v>3.05</v>
       </c>
       <c r="L10">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="M10">
         <v>1.16</v>
@@ -2906,7 +2906,7 @@
         <v>2.36</v>
       </c>
       <c r="O10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P10">
         <v>1.43</v>
@@ -2933,7 +2933,7 @@
         <v>1.72</v>
       </c>
       <c r="X10">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -3005,7 +3005,7 @@
         <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW10">
         <v>34</v>
@@ -3098,7 +3098,7 @@
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="s">
         <v>111</v>
@@ -3121,16 +3121,16 @@
         <v>110</v>
       </c>
       <c r="F11">
+        <v>1.98</v>
+      </c>
+      <c r="G11">
         <v>1.99</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
       </c>
       <c r="H11">
         <v>4.9</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3148,19 +3148,19 @@
         <v>2.74</v>
       </c>
       <c r="O11">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P11">
         <v>1.58</v>
       </c>
       <c r="Q11">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R11">
         <v>1.21</v>
       </c>
       <c r="S11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T11">
         <v>2.28</v>
@@ -3184,7 +3184,7 @@
         <v>34</v>
       </c>
       <c r="AA11">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
         <v>6.6</v>
@@ -3202,7 +3202,7 @@
         <v>10.5</v>
       </c>
       <c r="AG11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH11">
         <v>27</v>
@@ -3238,7 +3238,7 @@
         <v>30</v>
       </c>
       <c r="AS11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT11">
         <v>6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="105">
   <si>
     <t>League</t>
   </si>
@@ -256,24 +256,21 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
     <t>Brazilian Serie A</t>
   </si>
   <si>
-    <t>Paraguayan Primera Division</t>
-  </si>
-  <si>
-    <t>Ecuadorian Serie B</t>
-  </si>
-  <si>
     <t>2026-07-30</t>
   </si>
   <si>
-    <t>00:30:00</t>
-  </si>
-  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -289,15 +286,6 @@
     <t>22:30:00</t>
   </si>
   <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
-    <t>EC Vitoria Salvador</t>
-  </si>
-  <si>
     <t>Sportivo San Lorenzo</t>
   </si>
   <si>
@@ -319,15 +307,6 @@
     <t>Corinthians</t>
   </si>
   <si>
-    <t>CA Platense</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>SE Palmeiras</t>
-  </si>
-  <si>
     <t>Guarani (Par)</t>
   </si>
   <si>
@@ -349,7 +328,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-29 22:33:30</t>
+    <t>2026-07-30 00:42:57</t>
   </si>
 </sst>
 </file>
@@ -681,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -937,226 +916,226 @@
         <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F2">
-        <v>1.3</v>
+        <v>3.75</v>
       </c>
       <c r="G2">
+        <v>4.2</v>
+      </c>
+      <c r="H2">
+        <v>2.26</v>
+      </c>
+      <c r="I2">
+        <v>2.38</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3.25</v>
+      </c>
+      <c r="L2">
+        <v>1.52</v>
+      </c>
+      <c r="M2">
+        <v>1.12</v>
+      </c>
+      <c r="N2">
+        <v>2.6</v>
+      </c>
+      <c r="O2">
+        <v>1.52</v>
+      </c>
+      <c r="P2">
+        <v>1.54</v>
+      </c>
+      <c r="Q2">
+        <v>2.52</v>
+      </c>
+      <c r="R2">
+        <v>1.19</v>
+      </c>
+      <c r="S2">
+        <v>5.1</v>
+      </c>
+      <c r="T2">
+        <v>2.08</v>
+      </c>
+      <c r="U2">
+        <v>1.77</v>
+      </c>
+      <c r="V2">
+        <v>1.73</v>
+      </c>
+      <c r="W2">
         <v>1.31</v>
       </c>
-      <c r="H2">
-        <v>19.5</v>
-      </c>
-      <c r="I2">
-        <v>23</v>
-      </c>
-      <c r="J2">
-        <v>5.3</v>
-      </c>
-      <c r="K2">
-        <v>5.4</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>3.5</v>
-      </c>
-      <c r="O2">
-        <v>1.38</v>
-      </c>
-      <c r="P2">
-        <v>1.53</v>
-      </c>
-      <c r="Q2">
-        <v>2.82</v>
-      </c>
-      <c r="R2">
-        <v>1.14</v>
-      </c>
-      <c r="S2">
-        <v>7.8</v>
-      </c>
-      <c r="T2">
-        <v>2.38</v>
-      </c>
-      <c r="U2">
-        <v>1.68</v>
-      </c>
-      <c r="V2">
-        <v>1.04</v>
-      </c>
-      <c r="W2">
-        <v>4.2</v>
-      </c>
       <c r="X2">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB2">
-        <v>3.7</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>30</v>
+        <v>12.5</v>
       </c>
       <c r="AE2">
-        <v>270</v>
+        <v>34</v>
       </c>
       <c r="AF2">
-        <v>4.9</v>
+        <v>27</v>
       </c>
       <c r="AG2">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="AH2">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>300</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>13.5</v>
+        <v>95</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="AL2">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN2">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP2">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AS2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT2">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="AU2">
         <v>6.2</v>
       </c>
       <c r="AV2">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AW2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AX2">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY2">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AZ2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="BA2">
-        <v>210</v>
+        <v>9</v>
       </c>
       <c r="BB2">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BC2">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="BD2">
-        <v>90</v>
+        <v>9.4</v>
       </c>
       <c r="BE2">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>25</v>
+        <v>9.6</v>
       </c>
       <c r="BG2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1165,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1176,238 +1155,238 @@
         <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F3">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="G3">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>2.84</v>
       </c>
       <c r="I3">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="J3">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="K3">
-        <v>2.76</v>
+        <v>6.4</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.73</v>
+        <v>1.1</v>
       </c>
       <c r="O3">
-        <v>2.32</v>
+        <v>1.27</v>
       </c>
       <c r="P3">
+        <v>1.06</v>
+      </c>
+      <c r="Q3">
+        <v>1.44</v>
+      </c>
+      <c r="R3">
+        <v>1.05</v>
+      </c>
+      <c r="S3">
+        <v>1.92</v>
+      </c>
+      <c r="T3">
+        <v>1.11</v>
+      </c>
+      <c r="U3">
+        <v>1.11</v>
+      </c>
+      <c r="V3">
         <v>1.2</v>
       </c>
-      <c r="Q3">
-        <v>5.7</v>
-      </c>
-      <c r="R3">
-        <v>1.06</v>
-      </c>
-      <c r="S3">
-        <v>16.5</v>
-      </c>
-      <c r="T3">
-        <v>3.4</v>
-      </c>
-      <c r="U3">
-        <v>1.29</v>
-      </c>
-      <c r="V3">
-        <v>1.19</v>
-      </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="X3">
-        <v>4.6</v>
+        <v>970</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="Z3">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB3">
-        <v>4.4</v>
+        <v>970</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>500</v>
       </c>
       <c r="AD3">
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF3">
-        <v>9.800000000000001</v>
+        <v>500</v>
       </c>
       <c r="AG3">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="AH3">
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK3">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN3">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>4</v>
+        <v>1.16</v>
       </c>
       <c r="AQ3">
-        <v>9</v>
+        <v>1.14</v>
       </c>
       <c r="AR3">
-        <v>34</v>
+        <v>1.14</v>
       </c>
       <c r="AS3">
-        <v>150</v>
+        <v>1.24</v>
       </c>
       <c r="AT3">
-        <v>3.8</v>
+        <v>1.24</v>
       </c>
       <c r="AU3">
-        <v>7.6</v>
+        <v>1.21</v>
       </c>
       <c r="AV3">
-        <v>32</v>
+        <v>1.14</v>
       </c>
       <c r="AW3">
-        <v>190</v>
+        <v>1.14</v>
       </c>
       <c r="AX3">
-        <v>7.8</v>
+        <v>1.14</v>
       </c>
       <c r="AY3">
-        <v>16</v>
+        <v>1.14</v>
       </c>
       <c r="AZ3">
-        <v>5.4</v>
+        <v>1.14</v>
       </c>
       <c r="BA3">
-        <v>260</v>
+        <v>1.14</v>
       </c>
       <c r="BB3">
-        <v>26</v>
+        <v>1.24</v>
       </c>
       <c r="BC3">
-        <v>50</v>
+        <v>1.14</v>
       </c>
       <c r="BD3">
-        <v>180</v>
+        <v>1.14</v>
       </c>
       <c r="BE3">
-        <v>7.4</v>
+        <v>1.24</v>
       </c>
       <c r="BF3">
-        <v>44</v>
+        <v>1.55</v>
       </c>
       <c r="BG3">
-        <v>5.8</v>
+        <v>1.55</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1418,64 +1397,64 @@
         <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F4">
-        <v>1000</v>
+        <v>1.04</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H4">
+        <v>1.04</v>
+      </c>
+      <c r="I4">
+        <v>990</v>
+      </c>
+      <c r="J4">
+        <v>1.04</v>
+      </c>
+      <c r="K4">
+        <v>950</v>
+      </c>
+      <c r="L4">
         <v>1.01</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>1.01</v>
       </c>
-      <c r="J4">
-        <v>140</v>
-      </c>
-      <c r="K4">
-        <v>200</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
-        <v>8.6</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="R4">
-        <v>2.84</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
-        <v>6.2</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
-        <v>120</v>
+        <v>1.02</v>
       </c>
       <c r="W4">
         <v>1.01</v>
@@ -1487,10 +1466,10 @@
         <v>1000</v>
       </c>
       <c r="Z4">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
         <v>1000</v>
@@ -1499,10 +1478,10 @@
         <v>1000</v>
       </c>
       <c r="AD4">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
         <v>1000</v>
@@ -1532,1818 +1511,1092 @@
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>1.68</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
         <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>1.84</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4.4</v>
+      </c>
+      <c r="I5">
+        <v>5.2</v>
+      </c>
+      <c r="J5">
+        <v>3.55</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>1.41</v>
+      </c>
+      <c r="M5">
+        <v>1.07</v>
+      </c>
+      <c r="N5">
+        <v>3.5</v>
+      </c>
+      <c r="O5">
+        <v>1.32</v>
+      </c>
+      <c r="P5">
+        <v>1.87</v>
+      </c>
+      <c r="Q5">
+        <v>1.96</v>
+      </c>
+      <c r="R5">
+        <v>1.33</v>
+      </c>
+      <c r="S5">
+        <v>3.45</v>
+      </c>
+      <c r="T5">
+        <v>1.84</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>1.24</v>
+      </c>
+      <c r="W5">
+        <v>2</v>
+      </c>
+      <c r="X5">
+        <v>16</v>
+      </c>
+      <c r="Y5">
+        <v>17</v>
+      </c>
+      <c r="Z5">
+        <v>95</v>
+      </c>
+      <c r="AA5">
+        <v>900</v>
+      </c>
+      <c r="AB5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC5">
+        <v>9.6</v>
+      </c>
+      <c r="AD5">
+        <v>22</v>
+      </c>
+      <c r="AE5">
+        <v>160</v>
+      </c>
+      <c r="AF5">
+        <v>13.5</v>
+      </c>
+      <c r="AG5">
+        <v>10.5</v>
+      </c>
+      <c r="AH5">
+        <v>23</v>
+      </c>
+      <c r="AI5">
+        <v>170</v>
+      </c>
+      <c r="AJ5">
+        <v>23</v>
+      </c>
+      <c r="AK5">
+        <v>22</v>
+      </c>
+      <c r="AL5">
+        <v>85</v>
+      </c>
+      <c r="AM5">
+        <v>580</v>
+      </c>
+      <c r="AN5">
+        <v>15</v>
+      </c>
+      <c r="AO5">
+        <v>310</v>
+      </c>
+      <c r="AP5">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5">
+        <v>12</v>
+      </c>
+      <c r="AR5">
+        <v>14.5</v>
+      </c>
+      <c r="AS5">
+        <v>6.6</v>
+      </c>
+      <c r="AT5">
+        <v>7.4</v>
+      </c>
+      <c r="AU5">
+        <v>7.2</v>
+      </c>
+      <c r="AV5">
+        <v>15.5</v>
+      </c>
+      <c r="AW5">
+        <v>6.4</v>
+      </c>
+      <c r="AX5">
+        <v>9</v>
+      </c>
+      <c r="AY5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5">
+        <v>16.5</v>
+      </c>
+      <c r="BA5">
+        <v>6.4</v>
+      </c>
+      <c r="BB5">
+        <v>16.5</v>
+      </c>
+      <c r="BC5">
+        <v>16</v>
+      </c>
+      <c r="BD5">
+        <v>18</v>
+      </c>
+      <c r="BE5">
+        <v>6.6</v>
+      </c>
+      <c r="BF5">
+        <v>10.5</v>
+      </c>
+      <c r="BG5">
+        <v>6.6</v>
+      </c>
+      <c r="BH5">
+        <v>3.45</v>
+      </c>
+      <c r="BI5">
+        <v>2.78</v>
+      </c>
+      <c r="BJ5">
+        <v>10.5</v>
+      </c>
+      <c r="BK5">
+        <v>5.5</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>10.5</v>
+      </c>
+      <c r="BN5">
+        <v>4.7</v>
+      </c>
+      <c r="BO5">
+        <v>3.65</v>
+      </c>
+      <c r="BP5">
+        <v>14</v>
+      </c>
+      <c r="BQ5">
+        <v>6.2</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>8.4</v>
+      </c>
+      <c r="BT5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU5">
+        <v>4.8</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>9</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>9.4</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>8</v>
+      </c>
+      <c r="CB5" t="s">
         <v>104</v>
-      </c>
-      <c r="F5">
-        <v>3.75</v>
-      </c>
-      <c r="G5">
-        <v>4.2</v>
-      </c>
-      <c r="H5">
-        <v>2.22</v>
-      </c>
-      <c r="I5">
-        <v>2.38</v>
-      </c>
-      <c r="J5">
-        <v>2.96</v>
-      </c>
-      <c r="K5">
-        <v>3.3</v>
-      </c>
-      <c r="L5">
-        <v>1.52</v>
-      </c>
-      <c r="M5">
-        <v>1.12</v>
-      </c>
-      <c r="N5">
-        <v>2.6</v>
-      </c>
-      <c r="O5">
-        <v>1.52</v>
-      </c>
-      <c r="P5">
-        <v>1.54</v>
-      </c>
-      <c r="Q5">
-        <v>2.52</v>
-      </c>
-      <c r="R5">
-        <v>1.19</v>
-      </c>
-      <c r="S5">
-        <v>5.1</v>
-      </c>
-      <c r="T5">
-        <v>2.08</v>
-      </c>
-      <c r="U5">
-        <v>1.77</v>
-      </c>
-      <c r="V5">
-        <v>1.72</v>
-      </c>
-      <c r="W5">
-        <v>1.31</v>
-      </c>
-      <c r="X5">
-        <v>9</v>
-      </c>
-      <c r="Y5">
-        <v>7.6</v>
-      </c>
-      <c r="Z5">
-        <v>14</v>
-      </c>
-      <c r="AA5">
-        <v>36</v>
-      </c>
-      <c r="AB5">
-        <v>11.5</v>
-      </c>
-      <c r="AC5">
-        <v>7.6</v>
-      </c>
-      <c r="AD5">
-        <v>12.5</v>
-      </c>
-      <c r="AE5">
-        <v>34</v>
-      </c>
-      <c r="AF5">
-        <v>28</v>
-      </c>
-      <c r="AG5">
-        <v>18</v>
-      </c>
-      <c r="AH5">
-        <v>24</v>
-      </c>
-      <c r="AI5">
-        <v>65</v>
-      </c>
-      <c r="AJ5">
-        <v>110</v>
-      </c>
-      <c r="AK5">
-        <v>70</v>
-      </c>
-      <c r="AL5">
-        <v>200</v>
-      </c>
-      <c r="AM5">
-        <v>500</v>
-      </c>
-      <c r="AN5">
-        <v>110</v>
-      </c>
-      <c r="AO5">
-        <v>34</v>
-      </c>
-      <c r="AP5">
-        <v>7.6</v>
-      </c>
-      <c r="AQ5">
-        <v>6.4</v>
-      </c>
-      <c r="AR5">
-        <v>11</v>
-      </c>
-      <c r="AS5">
-        <v>22</v>
-      </c>
-      <c r="AT5">
-        <v>9</v>
-      </c>
-      <c r="AU5">
-        <v>6.2</v>
-      </c>
-      <c r="AV5">
-        <v>10</v>
-      </c>
-      <c r="AW5">
-        <v>21</v>
-      </c>
-      <c r="AX5">
-        <v>18.5</v>
-      </c>
-      <c r="AY5">
-        <v>14.5</v>
-      </c>
-      <c r="AZ5">
-        <v>19</v>
-      </c>
-      <c r="BA5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC5">
-        <v>8.4</v>
-      </c>
-      <c r="BD5">
-        <v>8.6</v>
-      </c>
-      <c r="BE5">
-        <v>9</v>
-      </c>
-      <c r="BF5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG5">
-        <v>21</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.04</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.04</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.04</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.04</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.04</v>
-      </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
-        <v>1.04</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>1.04</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>1.04</v>
-      </c>
-      <c r="BZ5">
-        <v>0</v>
-      </c>
-      <c r="CA5">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
         <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F6">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="G6">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="H6">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>3.7</v>
       </c>
       <c r="J6">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="K6">
-        <v>6.4</v>
+        <v>2.98</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>2.52</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="P6">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="Q6">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="R6">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="X6">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="Y6">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="Z6">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AA6">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB6">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AC6">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="AD6">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AE6">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF6">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AG6">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI6">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AJ6">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AK6">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AL6">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AP6">
-        <v>1.16</v>
+        <v>7</v>
       </c>
       <c r="AQ6">
-        <v>1.14</v>
+        <v>8.6</v>
       </c>
       <c r="AR6">
-        <v>1.14</v>
+        <v>19</v>
       </c>
       <c r="AS6">
-        <v>1.24</v>
+        <v>32</v>
       </c>
       <c r="AT6">
-        <v>1.24</v>
+        <v>6.8</v>
       </c>
       <c r="AU6">
-        <v>1.21</v>
+        <v>6</v>
       </c>
       <c r="AV6">
-        <v>1.14</v>
+        <v>15</v>
       </c>
       <c r="AW6">
-        <v>1.14</v>
+        <v>30</v>
       </c>
       <c r="AX6">
-        <v>1.14</v>
+        <v>12.5</v>
       </c>
       <c r="AY6">
-        <v>1.14</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6">
-        <v>1.14</v>
+        <v>20</v>
       </c>
       <c r="BA6">
-        <v>1.14</v>
+        <v>38</v>
       </c>
       <c r="BB6">
-        <v>1.24</v>
+        <v>32</v>
       </c>
       <c r="BC6">
-        <v>1.14</v>
+        <v>32</v>
       </c>
       <c r="BD6">
-        <v>1.14</v>
+        <v>34</v>
       </c>
       <c r="BE6">
-        <v>1.24</v>
+        <v>70</v>
       </c>
       <c r="BF6">
-        <v>1.55</v>
+        <v>25</v>
       </c>
       <c r="BG6">
-        <v>1.55</v>
+        <v>36</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
         <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>2.38</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>990</v>
+        <v>4.3</v>
       </c>
       <c r="J7">
+        <v>2.96</v>
+      </c>
+      <c r="K7">
+        <v>3.05</v>
+      </c>
+      <c r="L7">
+        <v>1.67</v>
+      </c>
+      <c r="M7">
         <v>1.16</v>
       </c>
-      <c r="K7">
-        <v>950</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.01</v>
-      </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="O7">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q7">
-        <v>1.38</v>
+        <v>3.05</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S7">
-        <v>1.38</v>
+        <v>6.8</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>2.38</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>16.5</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
         <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F8">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I8">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="L8">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="O8">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="P8">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="Q8">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S8">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="T8">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="V8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
         <v>2</v>
       </c>
       <c r="X8">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y8">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z8">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AA8">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AC8">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD8">
         <v>22</v>
       </c>
       <c r="AE8">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AF8">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH8">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI8">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AJ8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK8">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AL8">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AM8">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AO8">
-        <v>310</v>
+        <v>690</v>
       </c>
       <c r="AP8">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AQ8">
         <v>12</v>
       </c>
       <c r="AR8">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AS8">
-        <v>6.6</v>
+        <v>120</v>
       </c>
       <c r="AT8">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU8">
         <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AW8">
-        <v>6.2</v>
+        <v>70</v>
       </c>
       <c r="AX8">
+        <v>9.4</v>
+      </c>
+      <c r="AY8">
+        <v>10</v>
+      </c>
+      <c r="AZ8">
+        <v>23</v>
+      </c>
+      <c r="BA8">
+        <v>40</v>
+      </c>
+      <c r="BB8">
+        <v>21</v>
+      </c>
+      <c r="BC8">
+        <v>24</v>
+      </c>
+      <c r="BD8">
+        <v>50</v>
+      </c>
+      <c r="BE8">
+        <v>70</v>
+      </c>
+      <c r="BF8">
+        <v>21</v>
+      </c>
+      <c r="BG8">
+        <v>70</v>
+      </c>
+      <c r="BH8">
+        <v>2.86</v>
+      </c>
+      <c r="BI8">
+        <v>2.52</v>
+      </c>
+      <c r="BJ8">
+        <v>12</v>
+      </c>
+      <c r="BK8">
+        <v>5.8</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>11</v>
+      </c>
+      <c r="BN8">
+        <v>4.6</v>
+      </c>
+      <c r="BO8">
+        <v>3.85</v>
+      </c>
+      <c r="BP8">
+        <v>16.5</v>
+      </c>
+      <c r="BQ8">
+        <v>6.6</v>
+      </c>
+      <c r="BR8">
+        <v>42</v>
+      </c>
+      <c r="BS8">
         <v>9</v>
       </c>
-      <c r="AY8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ8">
-        <v>16.5</v>
-      </c>
-      <c r="BA8">
+      <c r="BT8">
+        <v>8.4</v>
+      </c>
+      <c r="BU8">
         <v>6.4</v>
       </c>
-      <c r="BB8">
-        <v>16.5</v>
-      </c>
-      <c r="BC8">
-        <v>16</v>
-      </c>
-      <c r="BD8">
-        <v>18</v>
-      </c>
-      <c r="BE8">
-        <v>6.4</v>
-      </c>
-      <c r="BF8">
-        <v>10.5</v>
-      </c>
-      <c r="BG8">
-        <v>6.4</v>
-      </c>
-      <c r="BH8">
-        <v>3.45</v>
-      </c>
-      <c r="BI8">
-        <v>2.78</v>
-      </c>
-      <c r="BJ8">
-        <v>10.5</v>
-      </c>
-      <c r="BK8">
-        <v>5.5</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>10.5</v>
-      </c>
-      <c r="BN8">
-        <v>4.7</v>
-      </c>
-      <c r="BO8">
-        <v>3.65</v>
-      </c>
-      <c r="BP8">
-        <v>14</v>
-      </c>
-      <c r="BQ8">
-        <v>6.2</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
-      <c r="BS8">
-        <v>8.4</v>
-      </c>
-      <c r="BT8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU8">
-        <v>4.8</v>
-      </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW8">
+        <v>9.4</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>10</v>
+      </c>
+      <c r="BZ8">
+        <v>42</v>
+      </c>
+      <c r="CA8">
         <v>9</v>
       </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>9.4</v>
-      </c>
-      <c r="BZ8">
-        <v>1000</v>
-      </c>
-      <c r="CA8">
-        <v>8</v>
-      </c>
       <c r="CB8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:80">
-      <c r="A9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F9">
-        <v>2.56</v>
-      </c>
-      <c r="G9">
-        <v>2.64</v>
-      </c>
-      <c r="H9">
-        <v>3.55</v>
-      </c>
-      <c r="I9">
-        <v>3.7</v>
-      </c>
-      <c r="J9">
-        <v>2.94</v>
-      </c>
-      <c r="K9">
-        <v>2.98</v>
-      </c>
-      <c r="L9">
-        <v>1.61</v>
-      </c>
-      <c r="M9">
-        <v>1.15</v>
-      </c>
-      <c r="N9">
-        <v>2.48</v>
-      </c>
-      <c r="O9">
-        <v>1.62</v>
-      </c>
-      <c r="P9">
-        <v>1.48</v>
-      </c>
-      <c r="Q9">
-        <v>2.88</v>
-      </c>
-      <c r="R9">
-        <v>1.17</v>
-      </c>
-      <c r="S9">
-        <v>6.2</v>
-      </c>
-      <c r="T9">
-        <v>2.24</v>
-      </c>
-      <c r="U9">
-        <v>1.75</v>
-      </c>
-      <c r="V9">
-        <v>1.37</v>
-      </c>
-      <c r="W9">
-        <v>1.61</v>
-      </c>
-      <c r="X9">
-        <v>7.4</v>
-      </c>
-      <c r="Y9">
-        <v>9.6</v>
-      </c>
-      <c r="Z9">
-        <v>23</v>
-      </c>
-      <c r="AA9">
-        <v>160</v>
-      </c>
-      <c r="AB9">
-        <v>7.4</v>
-      </c>
-      <c r="AC9">
-        <v>7</v>
-      </c>
-      <c r="AD9">
-        <v>17.5</v>
-      </c>
-      <c r="AE9">
-        <v>65</v>
-      </c>
-      <c r="AF9">
-        <v>15</v>
-      </c>
-      <c r="AG9">
-        <v>14</v>
-      </c>
-      <c r="AH9">
-        <v>24</v>
-      </c>
-      <c r="AI9">
-        <v>200</v>
-      </c>
-      <c r="AJ9">
-        <v>44</v>
-      </c>
-      <c r="AK9">
-        <v>42</v>
-      </c>
-      <c r="AL9">
-        <v>75</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>48</v>
-      </c>
-      <c r="AO9">
-        <v>220</v>
-      </c>
-      <c r="AP9">
-        <v>6.6</v>
-      </c>
-      <c r="AQ9">
-        <v>8.4</v>
-      </c>
-      <c r="AR9">
-        <v>19</v>
-      </c>
-      <c r="AS9">
-        <v>32</v>
-      </c>
-      <c r="AT9">
-        <v>6.8</v>
-      </c>
-      <c r="AU9">
-        <v>6.2</v>
-      </c>
-      <c r="AV9">
-        <v>15</v>
-      </c>
-      <c r="AW9">
-        <v>30</v>
-      </c>
-      <c r="AX9">
-        <v>13</v>
-      </c>
-      <c r="AY9">
-        <v>12</v>
-      </c>
-      <c r="AZ9">
-        <v>21</v>
-      </c>
-      <c r="BA9">
-        <v>38</v>
-      </c>
-      <c r="BB9">
-        <v>32</v>
-      </c>
-      <c r="BC9">
-        <v>24</v>
-      </c>
-      <c r="BD9">
-        <v>34</v>
-      </c>
-      <c r="BE9">
-        <v>70</v>
-      </c>
-      <c r="BF9">
-        <v>36</v>
-      </c>
-      <c r="BG9">
-        <v>36</v>
-      </c>
-      <c r="BH9">
-        <v>2.68</v>
-      </c>
-      <c r="BI9">
-        <v>2.14</v>
-      </c>
-      <c r="BJ9">
-        <v>12</v>
-      </c>
-      <c r="BK9">
-        <v>8.6</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>10.5</v>
-      </c>
-      <c r="BN9">
-        <v>5.4</v>
-      </c>
-      <c r="BO9">
-        <v>4</v>
-      </c>
-      <c r="BP9">
-        <v>25</v>
-      </c>
-      <c r="BQ9">
-        <v>7.6</v>
-      </c>
-      <c r="BR9">
-        <v>55</v>
-      </c>
-      <c r="BS9">
-        <v>9</v>
-      </c>
-      <c r="BT9">
-        <v>6.8</v>
-      </c>
-      <c r="BU9">
-        <v>5.5</v>
-      </c>
-      <c r="BV9">
-        <v>38</v>
-      </c>
-      <c r="BW9">
-        <v>8.4</v>
-      </c>
-      <c r="BX9">
-        <v>65</v>
-      </c>
-      <c r="BY9">
-        <v>9.4</v>
-      </c>
-      <c r="BZ9">
-        <v>60</v>
-      </c>
-      <c r="CA9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:80">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10">
-        <v>2.28</v>
-      </c>
-      <c r="G10">
-        <v>2.38</v>
-      </c>
-      <c r="H10">
-        <v>4</v>
-      </c>
-      <c r="I10">
-        <v>4.3</v>
-      </c>
-      <c r="J10">
-        <v>2.98</v>
-      </c>
-      <c r="K10">
-        <v>3.05</v>
-      </c>
-      <c r="L10">
-        <v>1.67</v>
-      </c>
-      <c r="M10">
-        <v>1.16</v>
-      </c>
-      <c r="N10">
-        <v>2.36</v>
-      </c>
-      <c r="O10">
-        <v>1.68</v>
-      </c>
-      <c r="P10">
-        <v>1.43</v>
-      </c>
-      <c r="Q10">
-        <v>3.05</v>
-      </c>
-      <c r="R10">
-        <v>1.15</v>
-      </c>
-      <c r="S10">
-        <v>6.8</v>
-      </c>
-      <c r="T10">
-        <v>2.38</v>
-      </c>
-      <c r="U10">
-        <v>1.65</v>
-      </c>
-      <c r="V10">
-        <v>1.3</v>
-      </c>
-      <c r="W10">
-        <v>1.72</v>
-      </c>
-      <c r="X10">
-        <v>7.6</v>
-      </c>
-      <c r="Y10">
-        <v>10</v>
-      </c>
-      <c r="Z10">
-        <v>27</v>
-      </c>
-      <c r="AA10">
-        <v>490</v>
-      </c>
-      <c r="AB10">
-        <v>6.6</v>
-      </c>
-      <c r="AC10">
-        <v>7.8</v>
-      </c>
-      <c r="AD10">
-        <v>23</v>
-      </c>
-      <c r="AE10">
-        <v>180</v>
-      </c>
-      <c r="AF10">
-        <v>12.5</v>
-      </c>
-      <c r="AG10">
-        <v>15</v>
-      </c>
-      <c r="AH10">
-        <v>34</v>
-      </c>
-      <c r="AI10">
-        <v>490</v>
-      </c>
-      <c r="AJ10">
-        <v>42</v>
-      </c>
-      <c r="AK10">
-        <v>44</v>
-      </c>
-      <c r="AL10">
-        <v>200</v>
-      </c>
-      <c r="AM10">
-        <v>500</v>
-      </c>
-      <c r="AN10">
-        <v>50</v>
-      </c>
-      <c r="AO10">
-        <v>490</v>
-      </c>
-      <c r="AP10">
-        <v>6.4</v>
-      </c>
-      <c r="AQ10">
-        <v>9</v>
-      </c>
-      <c r="AR10">
-        <v>20</v>
-      </c>
-      <c r="AS10">
-        <v>36</v>
-      </c>
-      <c r="AT10">
-        <v>5.8</v>
-      </c>
-      <c r="AU10">
-        <v>6.6</v>
-      </c>
-      <c r="AV10">
-        <v>17</v>
-      </c>
-      <c r="AW10">
-        <v>34</v>
-      </c>
-      <c r="AX10">
-        <v>11</v>
-      </c>
-      <c r="AY10">
-        <v>11.5</v>
-      </c>
-      <c r="AZ10">
-        <v>20</v>
-      </c>
-      <c r="BA10">
-        <v>42</v>
-      </c>
-      <c r="BB10">
-        <v>21</v>
-      </c>
-      <c r="BC10">
-        <v>22</v>
-      </c>
-      <c r="BD10">
-        <v>36</v>
-      </c>
-      <c r="BE10">
-        <v>100</v>
-      </c>
-      <c r="BF10">
-        <v>24</v>
-      </c>
-      <c r="BG10">
-        <v>40</v>
-      </c>
-      <c r="BH10">
-        <v>2.48</v>
-      </c>
-      <c r="BI10">
-        <v>2.16</v>
-      </c>
-      <c r="BJ10">
-        <v>12.5</v>
-      </c>
-      <c r="BK10">
-        <v>7.2</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>16.5</v>
-      </c>
-      <c r="BN10">
-        <v>4.9</v>
-      </c>
-      <c r="BO10">
-        <v>3.8</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>13</v>
-      </c>
-      <c r="BT10">
-        <v>7.2</v>
-      </c>
-      <c r="BU10">
-        <v>5.4</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>12.5</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>14</v>
-      </c>
-      <c r="BZ10">
-        <v>1000</v>
-      </c>
-      <c r="CA10">
-        <v>10.5</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:80">
-      <c r="A11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F11">
-        <v>1.98</v>
-      </c>
-      <c r="G11">
-        <v>1.99</v>
-      </c>
-      <c r="H11">
-        <v>4.9</v>
-      </c>
-      <c r="I11">
-        <v>5.1</v>
-      </c>
-      <c r="J11">
-        <v>3.35</v>
-      </c>
-      <c r="K11">
-        <v>3.4</v>
-      </c>
-      <c r="L11">
-        <v>1.57</v>
-      </c>
-      <c r="M11">
-        <v>1.12</v>
-      </c>
-      <c r="N11">
-        <v>2.74</v>
-      </c>
-      <c r="O11">
-        <v>1.54</v>
-      </c>
-      <c r="P11">
-        <v>1.58</v>
-      </c>
-      <c r="Q11">
-        <v>2.62</v>
-      </c>
-      <c r="R11">
-        <v>1.21</v>
-      </c>
-      <c r="S11">
-        <v>5.5</v>
-      </c>
-      <c r="T11">
-        <v>2.28</v>
-      </c>
-      <c r="U11">
-        <v>1.73</v>
-      </c>
-      <c r="V11">
-        <v>1.25</v>
-      </c>
-      <c r="W11">
-        <v>2</v>
-      </c>
-      <c r="X11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Y11">
-        <v>12.5</v>
-      </c>
-      <c r="Z11">
-        <v>34</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>6.6</v>
-      </c>
-      <c r="AC11">
-        <v>7.8</v>
-      </c>
-      <c r="AD11">
-        <v>22</v>
-      </c>
-      <c r="AE11">
-        <v>90</v>
-      </c>
-      <c r="AF11">
-        <v>10.5</v>
-      </c>
-      <c r="AG11">
-        <v>11</v>
-      </c>
-      <c r="AH11">
-        <v>27</v>
-      </c>
-      <c r="AI11">
-        <v>120</v>
-      </c>
-      <c r="AJ11">
-        <v>23</v>
-      </c>
-      <c r="AK11">
-        <v>27</v>
-      </c>
-      <c r="AL11">
-        <v>60</v>
-      </c>
-      <c r="AM11">
-        <v>220</v>
-      </c>
-      <c r="AN11">
-        <v>23</v>
-      </c>
-      <c r="AO11">
-        <v>690</v>
-      </c>
-      <c r="AP11">
-        <v>8</v>
-      </c>
-      <c r="AQ11">
-        <v>11.5</v>
-      </c>
-      <c r="AR11">
-        <v>30</v>
-      </c>
-      <c r="AS11">
-        <v>40</v>
-      </c>
-      <c r="AT11">
-        <v>6</v>
-      </c>
-      <c r="AU11">
-        <v>7.4</v>
-      </c>
-      <c r="AV11">
-        <v>19</v>
-      </c>
-      <c r="AW11">
-        <v>70</v>
-      </c>
-      <c r="AX11">
-        <v>9.4</v>
-      </c>
-      <c r="AY11">
-        <v>10</v>
-      </c>
-      <c r="AZ11">
-        <v>23</v>
-      </c>
-      <c r="BA11">
-        <v>40</v>
-      </c>
-      <c r="BB11">
-        <v>21</v>
-      </c>
-      <c r="BC11">
-        <v>24</v>
-      </c>
-      <c r="BD11">
-        <v>50</v>
-      </c>
-      <c r="BE11">
-        <v>70</v>
-      </c>
-      <c r="BF11">
-        <v>20</v>
-      </c>
-      <c r="BG11">
-        <v>42</v>
-      </c>
-      <c r="BH11">
-        <v>2.84</v>
-      </c>
-      <c r="BI11">
-        <v>2.34</v>
-      </c>
-      <c r="BJ11">
-        <v>12</v>
-      </c>
-      <c r="BK11">
-        <v>6</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>11.5</v>
-      </c>
-      <c r="BN11">
-        <v>4.6</v>
-      </c>
-      <c r="BO11">
-        <v>3.6</v>
-      </c>
-      <c r="BP11">
-        <v>16.5</v>
-      </c>
-      <c r="BQ11">
-        <v>7</v>
-      </c>
-      <c r="BR11">
-        <v>42</v>
-      </c>
-      <c r="BS11">
-        <v>9.4</v>
-      </c>
-      <c r="BT11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU11">
-        <v>4.9</v>
-      </c>
-      <c r="BV11">
-        <v>55</v>
-      </c>
-      <c r="BW11">
-        <v>10</v>
-      </c>
-      <c r="BX11">
-        <v>75</v>
-      </c>
-      <c r="BY11">
-        <v>10.5</v>
-      </c>
-      <c r="BZ11">
-        <v>42</v>
-      </c>
-      <c r="CA11">
-        <v>9.4</v>
-      </c>
-      <c r="CB11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -328,7 +328,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-30 00:42:57</t>
+    <t>2026-07-30 02:52:20</t>
   </si>
 </sst>
 </file>
@@ -922,46 +922,46 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I2">
         <v>2.38</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M2">
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="R2">
         <v>1.19</v>
       </c>
       <c r="S2">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T2">
         <v>2.08</v>
@@ -973,7 +973,7 @@
         <v>1.73</v>
       </c>
       <c r="W2">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X2">
         <v>9</v>
@@ -1012,7 +1012,7 @@
         <v>65</v>
       </c>
       <c r="AJ2">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AK2">
         <v>85</v>
@@ -1030,7 +1030,7 @@
         <v>34</v>
       </c>
       <c r="AP2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2">
         <v>6.4</v>
@@ -1039,7 +1039,7 @@
         <v>11</v>
       </c>
       <c r="AS2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT2">
         <v>9</v>
@@ -1051,10 +1051,10 @@
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY2">
         <v>14.5</v>
@@ -1063,79 +1063,79 @@
         <v>19</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
         <v>9.4</v>
       </c>
       <c r="BC2">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BD2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF2">
         <v>9.4</v>
-      </c>
-      <c r="BE2">
-        <v>10</v>
-      </c>
-      <c r="BF2">
-        <v>9.6</v>
       </c>
       <c r="BG2">
         <v>21</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1164,46 +1164,46 @@
         <v>98</v>
       </c>
       <c r="F3">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G3">
         <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I3">
         <v>18</v>
       </c>
       <c r="J3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="K3">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
         <v>1.1</v>
       </c>
       <c r="O3">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="P3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q3">
-        <v>1.44</v>
+        <v>2.28</v>
       </c>
       <c r="R3">
         <v>1.05</v>
       </c>
       <c r="S3">
-        <v>1.92</v>
+        <v>1.05</v>
       </c>
       <c r="T3">
         <v>1.11</v>
@@ -1245,7 +1245,7 @@
         <v>500</v>
       </c>
       <c r="AG3">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="AH3">
         <v>950</v>
@@ -1263,7 +1263,7 @@
         <v>500</v>
       </c>
       <c r="AM3">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3">
         <v>500</v>
@@ -1272,52 +1272,52 @@
         <v>500</v>
       </c>
       <c r="AP3">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AQ3">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AR3">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AS3">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AT3">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AU3">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AV3">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AW3">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="AX3">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AY3">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AZ3">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="BA3">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="BB3">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="BC3">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="BD3">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="BE3">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="BF3">
         <v>1.55</v>
@@ -1406,46 +1406,46 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="G4">
-        <v>990</v>
+        <v>4.4</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="I4">
         <v>990</v>
       </c>
       <c r="J4">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
         <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1454,118 +1454,118 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1648,46 +1648,46 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H5">
         <v>4.4</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q5">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T5">
         <v>1.84</v>
@@ -1696,16 +1696,16 @@
         <v>2</v>
       </c>
       <c r="V5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
         <v>2</v>
       </c>
       <c r="X5">
+        <v>14</v>
+      </c>
+      <c r="Y5">
         <v>16</v>
-      </c>
-      <c r="Y5">
-        <v>17</v>
       </c>
       <c r="Z5">
         <v>95</v>
@@ -1717,16 +1717,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD5">
         <v>22</v>
       </c>
       <c r="AE5">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AF5">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
@@ -1750,10 +1750,10 @@
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO5">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AP5">
         <v>10.5</v>
@@ -1765,7 +1765,7 @@
         <v>14.5</v>
       </c>
       <c r="AS5">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5">
         <v>7.4</v>
@@ -1777,7 +1777,7 @@
         <v>15.5</v>
       </c>
       <c r="AW5">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX5">
         <v>9</v>
@@ -1789,7 +1789,7 @@
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB5">
         <v>16.5</v>
@@ -1801,13 +1801,13 @@
         <v>18</v>
       </c>
       <c r="BE5">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5">
         <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH5">
         <v>3.45</v>
@@ -1825,7 +1825,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN5">
         <v>4.7</v>
@@ -1837,7 +1837,7 @@
         <v>14</v>
       </c>
       <c r="BQ5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -1855,13 +1855,13 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G6">
         <v>2.66</v>
@@ -1899,43 +1899,43 @@
         <v>3.5</v>
       </c>
       <c r="I6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J6">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K6">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="L6">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M6">
         <v>1.15</v>
       </c>
       <c r="N6">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
         <v>1.6</v>
       </c>
       <c r="P6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q6">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S6">
         <v>6.2</v>
       </c>
       <c r="T6">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U6">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V6">
         <v>1.37</v>
@@ -1944,10 +1944,10 @@
         <v>1.6</v>
       </c>
       <c r="X6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6">
         <v>23</v>
@@ -1974,7 +1974,7 @@
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6">
         <v>200</v>
@@ -1992,13 +1992,13 @@
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO6">
         <v>220</v>
       </c>
       <c r="AP6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ6">
         <v>8.6</v>
@@ -2010,7 +2010,7 @@
         <v>32</v>
       </c>
       <c r="AT6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU6">
         <v>6</v>
@@ -2040,22 +2040,22 @@
         <v>32</v>
       </c>
       <c r="BD6">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BE6">
         <v>70</v>
       </c>
       <c r="BF6">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BG6">
         <v>36</v>
       </c>
       <c r="BH6">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BI6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ6">
         <v>12</v>
@@ -2067,10 +2067,10 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO6">
         <v>4</v>
@@ -2079,37 +2079,37 @@
         <v>25</v>
       </c>
       <c r="BQ6">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6">
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6">
         <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV6">
         <v>36</v>
       </c>
       <c r="BW6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX6">
         <v>65</v>
       </c>
       <c r="BY6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ6">
         <v>60</v>
       </c>
       <c r="CA6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="s">
         <v>104</v>
@@ -2132,7 +2132,7 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G7">
         <v>2.38</v>
@@ -2141,46 +2141,46 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J7">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <v>3.05</v>
       </c>
       <c r="L7">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="M7">
         <v>1.16</v>
       </c>
       <c r="N7">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O7">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q7">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="T7">
         <v>2.38</v>
       </c>
       <c r="U7">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
         <v>1.72</v>
@@ -2189,7 +2189,7 @@
         <v>7.6</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7">
         <v>27</v>
@@ -2243,7 +2243,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7">
         <v>20</v>
@@ -2258,10 +2258,10 @@
         <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX7">
         <v>11</v>
@@ -2270,7 +2270,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA7">
         <v>42</v>
@@ -2279,16 +2279,16 @@
         <v>21</v>
       </c>
       <c r="BC7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD7">
         <v>36</v>
       </c>
       <c r="BE7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BG7">
         <v>40</v>
@@ -2297,22 +2297,22 @@
         <v>2.48</v>
       </c>
       <c r="BI7">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ7">
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>16.5</v>
+        <v>3.5</v>
       </c>
       <c r="BN7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO7">
         <v>3.8</v>
@@ -2321,13 +2321,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BT7">
         <v>7.2</v>
@@ -2339,19 +2339,19 @@
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="CB7" t="s">
         <v>104</v>
@@ -2392,28 +2392,28 @@
         <v>3.4</v>
       </c>
       <c r="L8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M8">
         <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
         <v>1.54</v>
       </c>
       <c r="P8">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q8">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S8">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T8">
         <v>2.24</v>
@@ -2428,13 +2428,13 @@
         <v>2</v>
       </c>
       <c r="X8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2446,10 +2446,10 @@
         <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF8">
         <v>10.5</v>
@@ -2461,10 +2461,10 @@
         <v>27</v>
       </c>
       <c r="AI8">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AJ8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK8">
         <v>27</v>
@@ -2473,7 +2473,7 @@
         <v>60</v>
       </c>
       <c r="AM8">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AN8">
         <v>24</v>
@@ -2482,16 +2482,16 @@
         <v>690</v>
       </c>
       <c r="AP8">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
         <v>30</v>
       </c>
       <c r="AS8">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AT8">
         <v>6.2</v>
@@ -2500,13 +2500,13 @@
         <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AX8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY8">
         <v>10</v>
@@ -2515,7 +2515,7 @@
         <v>23</v>
       </c>
       <c r="BA8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB8">
         <v>21</v>
@@ -2533,7 +2533,7 @@
         <v>21</v>
       </c>
       <c r="BG8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH8">
         <v>2.86</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -328,7 +328,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-30 02:52:20</t>
+    <t>2026-07-30 05:02:17</t>
   </si>
 </sst>
 </file>
@@ -922,7 +922,7 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G2">
         <v>4.1</v>
@@ -934,34 +934,34 @@
         <v>2.38</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M2">
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="O2">
         <v>1.53</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q2">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="T2">
         <v>2.08</v>
@@ -973,7 +973,7 @@
         <v>1.73</v>
       </c>
       <c r="W2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X2">
         <v>9</v>
@@ -1009,7 +1009,7 @@
         <v>24</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ2">
         <v>900</v>
@@ -1024,13 +1024,13 @@
         <v>500</v>
       </c>
       <c r="AN2">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AO2">
         <v>34</v>
       </c>
       <c r="AP2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2">
         <v>6.4</v>
@@ -1063,22 +1063,22 @@
         <v>19</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BB2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC2">
         <v>42</v>
       </c>
       <c r="BD2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG2">
         <v>21</v>
@@ -1087,37 +1087,37 @@
         <v>2.78</v>
       </c>
       <c r="BI2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO2">
         <v>5.5</v>
       </c>
       <c r="BP2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>5</v>
@@ -1129,13 +1129,13 @@
         <v>21</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX2">
         <v>44</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1164,13 +1164,13 @@
         <v>98</v>
       </c>
       <c r="F3">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G3">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="H3">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="I3">
         <v>18</v>
@@ -1179,7 +1179,7 @@
         <v>2.66</v>
       </c>
       <c r="K3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1191,19 +1191,19 @@
         <v>1.1</v>
       </c>
       <c r="O3">
-        <v>1.45</v>
+        <v>1.07</v>
       </c>
       <c r="P3">
         <v>1.07</v>
       </c>
       <c r="Q3">
-        <v>2.28</v>
+        <v>1.47</v>
       </c>
       <c r="R3">
         <v>1.05</v>
       </c>
       <c r="S3">
-        <v>1.05</v>
+        <v>1.76</v>
       </c>
       <c r="T3">
         <v>1.11</v>
@@ -1406,7 +1406,7 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="G4">
         <v>4.4</v>
@@ -1427,10 +1427,10 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="O4">
         <v>1.39</v>
@@ -1454,10 +1454,10 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W4">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X4">
         <v>950</v>
@@ -1648,13 +1648,13 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G5">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I5">
         <v>5.1</v>
@@ -1699,7 +1699,7 @@
         <v>1.25</v>
       </c>
       <c r="W5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X5">
         <v>14</v>
@@ -1825,7 +1825,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
         <v>4.7</v>
@@ -1837,7 +1837,7 @@
         <v>14</v>
       </c>
       <c r="BQ5">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -1855,13 +1855,13 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
@@ -1890,19 +1890,19 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G6">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I6">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J6">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K6">
         <v>2.96</v>
@@ -1911,37 +1911,37 @@
         <v>1.63</v>
       </c>
       <c r="M6">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P6">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q6">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="R6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U6">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1950,19 +1950,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA6">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AB6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC6">
         <v>7</v>
       </c>
       <c r="AD6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE6">
         <v>65</v>
@@ -1974,7 +1974,7 @@
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI6">
         <v>200</v>
@@ -1983,7 +1983,7 @@
         <v>44</v>
       </c>
       <c r="AK6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL6">
         <v>75</v>
@@ -1992,7 +1992,7 @@
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO6">
         <v>220</v>
@@ -2004,7 +2004,7 @@
         <v>8.6</v>
       </c>
       <c r="AR6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS6">
         <v>32</v>
@@ -2016,22 +2016,22 @@
         <v>6</v>
       </c>
       <c r="AV6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ6">
         <v>20</v>
       </c>
       <c r="BA6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB6">
         <v>32</v>
@@ -2049,7 +2049,7 @@
         <v>38</v>
       </c>
       <c r="BG6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH6">
         <v>2.66</v>
@@ -2085,7 +2085,7 @@
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT6">
         <v>6.6</v>
@@ -2097,10 +2097,10 @@
         <v>36</v>
       </c>
       <c r="BW6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY6">
         <v>10</v>
@@ -2132,7 +2132,7 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G7">
         <v>2.38</v>
@@ -2156,28 +2156,28 @@
         <v>1.16</v>
       </c>
       <c r="N7">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O7">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R7">
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="T7">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="U7">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V7">
         <v>1.31</v>
@@ -2189,7 +2189,7 @@
         <v>7.6</v>
       </c>
       <c r="Y7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z7">
         <v>27</v>
@@ -2243,10 +2243,10 @@
         <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AS7">
         <v>36</v>
@@ -2258,7 +2258,7 @@
         <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW7">
         <v>38</v>
@@ -2279,13 +2279,13 @@
         <v>21</v>
       </c>
       <c r="BC7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD7">
         <v>36</v>
       </c>
       <c r="BE7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BF7">
         <v>24</v>
@@ -2297,25 +2297,25 @@
         <v>2.48</v>
       </c>
       <c r="BI7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ7">
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BN7">
         <v>4.8</v>
       </c>
       <c r="BO7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP7">
         <v>1000</v>
@@ -2327,7 +2327,7 @@
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>14</v>
+        <v>3.6</v>
       </c>
       <c r="BT7">
         <v>7.2</v>
@@ -2345,7 +2345,7 @@
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
@@ -2374,16 +2374,16 @@
         <v>103</v>
       </c>
       <c r="F8">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H8">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J8">
         <v>3.35</v>
@@ -2398,34 +2398,34 @@
         <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O8">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q8">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S8">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U8">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -2443,7 +2443,7 @@
         <v>6.6</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD8">
         <v>20</v>
@@ -2458,7 +2458,7 @@
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI8">
         <v>240</v>
@@ -2473,7 +2473,7 @@
         <v>60</v>
       </c>
       <c r="AM8">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
         <v>24</v>
@@ -2488,7 +2488,7 @@
         <v>11.5</v>
       </c>
       <c r="AR8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AS8">
         <v>110</v>
@@ -2500,10 +2500,10 @@
         <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AX8">
         <v>9.6</v>
@@ -2515,7 +2515,7 @@
         <v>23</v>
       </c>
       <c r="BA8">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BB8">
         <v>21</v>
@@ -2563,7 +2563,7 @@
         <v>16.5</v>
       </c>
       <c r="BQ8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR8">
         <v>42</v>
@@ -2584,7 +2584,7 @@
         <v>9.4</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY8">
         <v>10</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -328,7 +328,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-30 05:02:17</t>
+    <t>2026-07-30 07:11:59</t>
   </si>
 </sst>
 </file>
@@ -934,40 +934,40 @@
         <v>2.38</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
         <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M2">
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O2">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P2">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
         <v>5.2</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="V2">
         <v>1.73</v>
@@ -976,7 +976,7 @@
         <v>1.32</v>
       </c>
       <c r="X2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Y2">
         <v>7.6</v>
@@ -1006,16 +1006,16 @@
         <v>17.5</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2">
         <v>75</v>
       </c>
       <c r="AJ2">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK2">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AL2">
         <v>200</v>
@@ -1030,7 +1030,7 @@
         <v>34</v>
       </c>
       <c r="AP2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2">
         <v>6.4</v>
@@ -1066,7 +1066,7 @@
         <v>38</v>
       </c>
       <c r="BB2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC2">
         <v>42</v>
@@ -1078,7 +1078,7 @@
         <v>10</v>
       </c>
       <c r="BF2">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BG2">
         <v>21</v>
@@ -1087,19 +1087,19 @@
         <v>2.78</v>
       </c>
       <c r="BI2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN2">
         <v>7.2</v>
@@ -1108,34 +1108,34 @@
         <v>5.5</v>
       </c>
       <c r="BP2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT2">
         <v>5</v>
       </c>
       <c r="BU2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1164,226 +1164,226 @@
         <v>98</v>
       </c>
       <c r="F3">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="G3">
-        <v>7.4</v>
+        <v>2.38</v>
       </c>
       <c r="H3">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="I3">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="J3">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="O3">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="Q3">
-        <v>1.47</v>
+        <v>2.72</v>
       </c>
       <c r="R3">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>1.76</v>
+        <v>5.7</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="Y3">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AC3">
-        <v>500</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="AE3">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AF3">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AG3">
-        <v>110</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI3">
         <v>500</v>
       </c>
       <c r="AJ3">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AK3">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AL3">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AM3">
         <v>580</v>
       </c>
       <c r="AN3">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP3">
-        <v>1.31</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3">
-        <v>1.4</v>
+        <v>9</v>
       </c>
       <c r="AR3">
-        <v>1.41</v>
+        <v>19</v>
       </c>
       <c r="AS3">
-        <v>1.42</v>
+        <v>9.4</v>
       </c>
       <c r="AT3">
-        <v>1.38</v>
+        <v>6</v>
       </c>
       <c r="AU3">
-        <v>1.38</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>1.4</v>
+        <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>1.42</v>
+        <v>46</v>
       </c>
       <c r="AX3">
-        <v>1.39</v>
+        <v>11</v>
       </c>
       <c r="AY3">
-        <v>1.29</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>1.39</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>1.42</v>
+        <v>9.4</v>
       </c>
       <c r="BB3">
-        <v>1.41</v>
+        <v>23</v>
       </c>
       <c r="BC3">
-        <v>1.39</v>
+        <v>23</v>
       </c>
       <c r="BD3">
-        <v>1.42</v>
+        <v>42</v>
       </c>
       <c r="BE3">
-        <v>1.42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3">
-        <v>1.55</v>
+        <v>23</v>
       </c>
       <c r="BG3">
-        <v>1.55</v>
+        <v>9.6</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>104</v>
@@ -1406,64 +1406,64 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="G4">
-        <v>4.4</v>
+        <v>2.14</v>
       </c>
       <c r="H4">
+        <v>4.3</v>
+      </c>
+      <c r="I4">
+        <v>4.9</v>
+      </c>
+      <c r="J4">
+        <v>3.1</v>
+      </c>
+      <c r="K4">
+        <v>3.4</v>
+      </c>
+      <c r="L4">
+        <v>1.58</v>
+      </c>
+      <c r="M4">
+        <v>1.13</v>
+      </c>
+      <c r="N4">
+        <v>2.64</v>
+      </c>
+      <c r="O4">
+        <v>1.54</v>
+      </c>
+      <c r="P4">
+        <v>1.53</v>
+      </c>
+      <c r="Q4">
         <v>2.66</v>
       </c>
-      <c r="I4">
-        <v>990</v>
-      </c>
-      <c r="J4">
-        <v>2.96</v>
-      </c>
-      <c r="K4">
-        <v>7</v>
-      </c>
-      <c r="L4">
-        <v>1.01</v>
-      </c>
-      <c r="M4">
-        <v>1.08</v>
-      </c>
-      <c r="N4">
-        <v>1.24</v>
-      </c>
-      <c r="O4">
-        <v>1.39</v>
-      </c>
-      <c r="P4">
+      <c r="R4">
+        <v>1.19</v>
+      </c>
+      <c r="S4">
+        <v>5.5</v>
+      </c>
+      <c r="T4">
+        <v>2.22</v>
+      </c>
+      <c r="U4">
+        <v>1.7</v>
+      </c>
+      <c r="V4">
         <v>1.25</v>
       </c>
-      <c r="Q4">
-        <v>1.39</v>
-      </c>
-      <c r="R4">
-        <v>1.18</v>
-      </c>
-      <c r="S4">
-        <v>1.39</v>
-      </c>
-      <c r="T4">
-        <v>1.11</v>
-      </c>
-      <c r="U4">
-        <v>1.11</v>
-      </c>
-      <c r="V4">
-        <v>1.08</v>
-      </c>
       <c r="W4">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="X4">
-        <v>950</v>
+        <v>8.6</v>
       </c>
       <c r="Y4">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="Z4">
         <v>500</v>
@@ -1472,160 +1472,160 @@
         <v>900</v>
       </c>
       <c r="AB4">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="AC4">
-        <v>500</v>
+        <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE4">
         <v>500</v>
       </c>
       <c r="AF4">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AG4">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI4">
         <v>500</v>
       </c>
       <c r="AJ4">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="AK4">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL4">
         <v>500</v>
       </c>
       <c r="AM4">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN4">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4">
-        <v>1.25</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4">
-        <v>1.24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4">
-        <v>1.24</v>
+        <v>10.5</v>
       </c>
       <c r="AS4">
-        <v>1.25</v>
+        <v>9.4</v>
       </c>
       <c r="AT4">
-        <v>1.21</v>
+        <v>5.8</v>
       </c>
       <c r="AU4">
-        <v>1.22</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>1.24</v>
+        <v>17</v>
       </c>
       <c r="AW4">
-        <v>1.25</v>
+        <v>9</v>
       </c>
       <c r="AX4">
-        <v>1.21</v>
+        <v>9.6</v>
       </c>
       <c r="AY4">
-        <v>1.21</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>1.23</v>
+        <v>7.4</v>
       </c>
       <c r="BA4">
-        <v>1.25</v>
+        <v>9.4</v>
       </c>
       <c r="BB4">
-        <v>1.24</v>
+        <v>7.6</v>
       </c>
       <c r="BC4">
-        <v>1.23</v>
+        <v>23</v>
       </c>
       <c r="BD4">
-        <v>1.24</v>
+        <v>8.6</v>
       </c>
       <c r="BE4">
-        <v>1.25</v>
+        <v>9.6</v>
       </c>
       <c r="BF4">
-        <v>1.55</v>
+        <v>9.4</v>
       </c>
       <c r="BG4">
-        <v>1.55</v>
+        <v>9.4</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>104</v>
@@ -1648,16 +1648,16 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G5">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H5">
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J5">
         <v>3.6</v>
@@ -1672,7 +1672,7 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
         <v>1.33</v>
@@ -1684,13 +1684,13 @@
         <v>2.02</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T5">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
         <v>2</v>
@@ -1717,7 +1717,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
         <v>22</v>
@@ -1750,7 +1750,7 @@
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO5">
         <v>500</v>
@@ -1810,22 +1810,22 @@
         <v>8.4</v>
       </c>
       <c r="BH5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI5">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN5">
         <v>4.7</v>
@@ -1837,37 +1837,37 @@
         <v>14</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU5">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="s">
         <v>104</v>
@@ -1890,22 +1890,22 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="G6">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="H6">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I6">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>1.63</v>
@@ -1917,7 +1917,7 @@
         <v>2.62</v>
       </c>
       <c r="O6">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P6">
         <v>1.53</v>
@@ -1935,37 +1935,37 @@
         <v>2.22</v>
       </c>
       <c r="U6">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X6">
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA6">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AB6">
         <v>7.8</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AD6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF6">
         <v>15</v>
@@ -1977,7 +1977,7 @@
         <v>24</v>
       </c>
       <c r="AI6">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AJ6">
         <v>44</v>
@@ -1986,52 +1986,52 @@
         <v>42</v>
       </c>
       <c r="AL6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN6">
         <v>48</v>
       </c>
       <c r="AO6">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="AP6">
         <v>7.2</v>
       </c>
       <c r="AQ6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS6">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AT6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV6">
         <v>14</v>
       </c>
       <c r="AW6">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AX6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY6">
         <v>12</v>
       </c>
       <c r="AZ6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA6">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BB6">
         <v>32</v>
@@ -2040,7 +2040,7 @@
         <v>32</v>
       </c>
       <c r="BD6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BE6">
         <v>70</v>
@@ -2049,13 +2049,13 @@
         <v>38</v>
       </c>
       <c r="BG6">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BH6">
         <v>2.66</v>
       </c>
       <c r="BI6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6">
         <v>12</v>
@@ -2067,22 +2067,22 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN6">
         <v>5.4</v>
       </c>
       <c r="BO6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP6">
         <v>25</v>
       </c>
       <c r="BQ6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS6">
         <v>10</v>
@@ -2097,19 +2097,19 @@
         <v>36</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX6">
         <v>60</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>60</v>
       </c>
       <c r="CA6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="s">
         <v>104</v>
@@ -2132,7 +2132,7 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G7">
         <v>2.38</v>
@@ -2150,7 +2150,7 @@
         <v>3.05</v>
       </c>
       <c r="L7">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M7">
         <v>1.16</v>
@@ -2162,7 +2162,7 @@
         <v>1.68</v>
       </c>
       <c r="P7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q7">
         <v>3.15</v>
@@ -2174,7 +2174,7 @@
         <v>7.2</v>
       </c>
       <c r="T7">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="U7">
         <v>1.65</v>
@@ -2189,7 +2189,7 @@
         <v>7.6</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7">
         <v>27</v>
@@ -2204,7 +2204,7 @@
         <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE7">
         <v>180</v>
@@ -2243,10 +2243,10 @@
         <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS7">
         <v>36</v>
@@ -2261,7 +2261,7 @@
         <v>17</v>
       </c>
       <c r="AW7">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AX7">
         <v>11</v>
@@ -2273,13 +2273,13 @@
         <v>22</v>
       </c>
       <c r="BA7">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BB7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC7">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BD7">
         <v>36</v>
@@ -2288,10 +2288,10 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG7">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BH7">
         <v>2.48</v>
@@ -2309,7 +2309,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BN7">
         <v>4.8</v>
@@ -2377,13 +2377,13 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H8">
         <v>4.7</v>
       </c>
       <c r="I8">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J8">
         <v>3.35</v>
@@ -2401,7 +2401,7 @@
         <v>2.82</v>
       </c>
       <c r="O8">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P8">
         <v>1.6</v>
@@ -2422,10 +2422,10 @@
         <v>1.77</v>
       </c>
       <c r="V8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -2440,7 +2440,7 @@
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC8">
         <v>7.6</v>
@@ -2461,10 +2461,10 @@
         <v>26</v>
       </c>
       <c r="AI8">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AJ8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK8">
         <v>27</v>
@@ -2479,7 +2479,7 @@
         <v>24</v>
       </c>
       <c r="AO8">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="AP8">
         <v>8.4</v>
@@ -2488,13 +2488,13 @@
         <v>11.5</v>
       </c>
       <c r="AR8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS8">
         <v>110</v>
       </c>
       <c r="AT8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU8">
         <v>7.2</v>
@@ -2515,7 +2515,7 @@
         <v>23</v>
       </c>
       <c r="BA8">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BB8">
         <v>21</v>
@@ -2533,7 +2533,7 @@
         <v>21</v>
       </c>
       <c r="BG8">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BH8">
         <v>2.86</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -328,7 +328,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-30 07:11:59</t>
+    <t>2026-07-30 09:23:23</t>
   </si>
 </sst>
 </file>
@@ -922,16 +922,16 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="G2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H2">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="I2">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J2">
         <v>3.05</v>
@@ -946,49 +946,49 @@
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O2">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="V2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X2">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC2">
         <v>7.6</v>
@@ -1000,25 +1000,25 @@
         <v>34</v>
       </c>
       <c r="AF2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>75</v>
       </c>
       <c r="AJ2">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AK2">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AL2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AM2">
         <v>500</v>
@@ -1030,19 +1030,19 @@
         <v>34</v>
       </c>
       <c r="AP2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR2">
         <v>11</v>
       </c>
       <c r="AS2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU2">
         <v>6.2</v>
@@ -1051,13 +1051,13 @@
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX2">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ2">
         <v>19</v>
@@ -1066,7 +1066,7 @@
         <v>38</v>
       </c>
       <c r="BB2">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BC2">
         <v>42</v>
@@ -1078,7 +1078,7 @@
         <v>10</v>
       </c>
       <c r="BF2">
-        <v>28</v>
+        <v>9.6</v>
       </c>
       <c r="BG2">
         <v>21</v>
@@ -1093,49 +1093,49 @@
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BP2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BQ2">
         <v>10</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
         <v>11</v>
       </c>
       <c r="BT2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU2">
         <v>3.95</v>
       </c>
       <c r="BV2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX2">
         <v>42</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>2.2</v>
       </c>
       <c r="G3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
         <v>3.85</v>
@@ -1176,46 +1176,46 @@
         <v>4.4</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
         <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="O3">
         <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q3">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X3">
         <v>8.4</v>
@@ -1266,13 +1266,13 @@
         <v>580</v>
       </c>
       <c r="AN3">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AO3">
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
         <v>9</v>
@@ -1281,49 +1281,49 @@
         <v>19</v>
       </c>
       <c r="AS3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
         <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC3">
         <v>23</v>
       </c>
       <c r="BD3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="BE3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF3">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH3">
         <v>2.72</v>
@@ -1335,7 +1335,7 @@
         <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1406,16 +1406,16 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G4">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J4">
         <v>3.1</v>
@@ -1424,34 +1424,34 @@
         <v>3.4</v>
       </c>
       <c r="L4">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O4">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P4">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Q4">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="R4">
         <v>1.19</v>
       </c>
       <c r="S4">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T4">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V4">
         <v>1.25</v>
@@ -1460,7 +1460,7 @@
         <v>1.87</v>
       </c>
       <c r="X4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>13</v>
@@ -1484,7 +1484,7 @@
         <v>500</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
         <v>12</v>
@@ -1499,34 +1499,34 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AL4">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM4">
         <v>580</v>
       </c>
       <c r="AN4">
-        <v>600</v>
+        <v>28</v>
       </c>
       <c r="AO4">
         <v>600</v>
       </c>
       <c r="AP4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR4">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU4">
         <v>6.6</v>
@@ -1535,97 +1535,97 @@
         <v>17</v>
       </c>
       <c r="AW4">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BA4">
+        <v>10</v>
+      </c>
+      <c r="BB4">
+        <v>12.5</v>
+      </c>
+      <c r="BC4">
+        <v>12.5</v>
+      </c>
+      <c r="BD4">
         <v>9.4</v>
       </c>
-      <c r="BB4">
-        <v>7.6</v>
-      </c>
-      <c r="BC4">
-        <v>23</v>
-      </c>
-      <c r="BD4">
-        <v>8.6</v>
-      </c>
       <c r="BE4">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH4">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BI4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO4">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BP4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ4">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BT4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
         <v>104</v>
@@ -1648,16 +1648,16 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G5">
         <v>1.97</v>
       </c>
       <c r="H5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>3.6</v>
@@ -1672,7 +1672,7 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
         <v>1.33</v>
@@ -1684,25 +1684,25 @@
         <v>2.02</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
         <v>3.6</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
         <v>2.02</v>
       </c>
       <c r="X5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y5">
         <v>16</v>
@@ -1714,7 +1714,7 @@
         <v>900</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>8.4</v>
@@ -1723,7 +1723,7 @@
         <v>22</v>
       </c>
       <c r="AE5">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AF5">
         <v>12</v>
@@ -1732,10 +1732,10 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AI5">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AJ5">
         <v>23</v>
@@ -1744,130 +1744,130 @@
         <v>22</v>
       </c>
       <c r="AL5">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM5">
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AR5">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU5">
         <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW5">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BB5">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="BC5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BD5">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BE5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG5">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5">
         <v>3.4</v>
       </c>
       <c r="BI5">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP5">
         <v>14</v>
       </c>
       <c r="BQ5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
         <v>8</v>
       </c>
       <c r="BU5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB5" t="s">
         <v>104</v>
@@ -1890,10 +1890,10 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G6">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H6">
         <v>3.35</v>
@@ -1908,34 +1908,34 @@
         <v>3</v>
       </c>
       <c r="L6">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M6">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N6">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P6">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q6">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T6">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U6">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V6">
         <v>1.41</v>
@@ -1944,16 +1944,16 @@
         <v>1.57</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y6">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6">
         <v>21</v>
       </c>
       <c r="AA6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB6">
         <v>7.8</v>
@@ -1962,13 +1962,13 @@
         <v>6.6</v>
       </c>
       <c r="AD6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE6">
         <v>60</v>
       </c>
       <c r="AF6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG6">
         <v>13.5</v>
@@ -1977,7 +1977,7 @@
         <v>24</v>
       </c>
       <c r="AI6">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ6">
         <v>44</v>
@@ -1986,31 +1986,31 @@
         <v>42</v>
       </c>
       <c r="AL6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM6">
         <v>220</v>
       </c>
       <c r="AN6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO6">
         <v>85</v>
       </c>
       <c r="AP6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR6">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AT6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU6">
         <v>6.2</v>
@@ -2019,40 +2019,40 @@
         <v>14</v>
       </c>
       <c r="AW6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX6">
         <v>13.5</v>
       </c>
       <c r="AY6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA6">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BB6">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BC6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD6">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BE6">
         <v>70</v>
       </c>
       <c r="BF6">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BG6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH6">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI6">
         <v>2.2</v>
@@ -2067,7 +2067,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN6">
         <v>5.4</v>
@@ -2079,16 +2079,16 @@
         <v>25</v>
       </c>
       <c r="BQ6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU6">
         <v>5.4</v>
@@ -2097,19 +2097,19 @@
         <v>36</v>
       </c>
       <c r="BW6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX6">
         <v>60</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
         <v>60</v>
       </c>
       <c r="CA6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB6" t="s">
         <v>104</v>
@@ -2132,22 +2132,22 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="G7">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L7">
         <v>1.68</v>
@@ -2159,7 +2159,7 @@
         <v>2.4</v>
       </c>
       <c r="O7">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P7">
         <v>1.44</v>
@@ -2171,61 +2171,61 @@
         <v>1.15</v>
       </c>
       <c r="S7">
+        <v>7</v>
+      </c>
+      <c r="T7">
+        <v>2.46</v>
+      </c>
+      <c r="U7">
+        <v>1.64</v>
+      </c>
+      <c r="V7">
+        <v>1.29</v>
+      </c>
+      <c r="W7">
+        <v>1.79</v>
+      </c>
+      <c r="X7">
         <v>7.2</v>
       </c>
-      <c r="T7">
-        <v>2.52</v>
-      </c>
-      <c r="U7">
-        <v>1.65</v>
-      </c>
-      <c r="V7">
-        <v>1.31</v>
-      </c>
-      <c r="W7">
-        <v>1.72</v>
-      </c>
-      <c r="X7">
+      <c r="Y7">
+        <v>10.5</v>
+      </c>
+      <c r="Z7">
+        <v>29</v>
+      </c>
+      <c r="AA7">
+        <v>130</v>
+      </c>
+      <c r="AB7">
+        <v>6.2</v>
+      </c>
+      <c r="AC7">
         <v>7.6</v>
       </c>
-      <c r="Y7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z7">
-        <v>27</v>
-      </c>
-      <c r="AA7">
-        <v>490</v>
-      </c>
-      <c r="AB7">
-        <v>6.6</v>
-      </c>
-      <c r="AC7">
-        <v>7.8</v>
-      </c>
       <c r="AD7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE7">
         <v>180</v>
       </c>
       <c r="AF7">
+        <v>12</v>
+      </c>
+      <c r="AG7">
         <v>12.5</v>
       </c>
-      <c r="AG7">
-        <v>13.5</v>
-      </c>
       <c r="AH7">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI7">
         <v>490</v>
       </c>
       <c r="AJ7">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AK7">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AL7">
         <v>200</v>
@@ -2234,70 +2234,70 @@
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AO7">
-        <v>490</v>
+        <v>160</v>
       </c>
       <c r="AP7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AS7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT7">
         <v>5.8</v>
       </c>
       <c r="AU7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW7">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AX7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY7">
         <v>11.5</v>
       </c>
       <c r="AZ7">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BA7">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BB7">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BC7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BD7">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BG7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BH7">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BI7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ7">
         <v>12.5</v>
@@ -2309,49 +2309,49 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>3.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ7">
         <v>10</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS7">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="BT7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU7">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA7">
-        <v>3.6</v>
+        <v>15</v>
       </c>
       <c r="CB7" t="s">
         <v>104</v>
@@ -2377,13 +2377,13 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H8">
         <v>4.7</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J8">
         <v>3.35</v>
@@ -2392,7 +2392,7 @@
         <v>3.4</v>
       </c>
       <c r="L8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M8">
         <v>1.12</v>
@@ -2401,16 +2401,16 @@
         <v>2.82</v>
       </c>
       <c r="O8">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P8">
         <v>1.6</v>
       </c>
       <c r="Q8">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R8">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S8">
         <v>5.4</v>
@@ -2419,13 +2419,13 @@
         <v>2.22</v>
       </c>
       <c r="U8">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -2434,16 +2434,16 @@
         <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
         <v>20</v>
@@ -2452,31 +2452,31 @@
         <v>85</v>
       </c>
       <c r="AF8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG8">
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI8">
         <v>110</v>
       </c>
       <c r="AJ8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL8">
         <v>60</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO8">
         <v>140</v>
@@ -2488,22 +2488,22 @@
         <v>11.5</v>
       </c>
       <c r="AR8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS8">
         <v>110</v>
       </c>
       <c r="AT8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU8">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV8">
         <v>18</v>
       </c>
       <c r="AW8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AX8">
         <v>9.6</v>
@@ -2515,10 +2515,10 @@
         <v>23</v>
       </c>
       <c r="BA8">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC8">
         <v>24</v>
@@ -2530,70 +2530,70 @@
         <v>70</v>
       </c>
       <c r="BF8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG8">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="BH8">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="BI8">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM8">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BN8">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO8">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP8">
         <v>16.5</v>
       </c>
       <c r="BQ8">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BR8">
         <v>42</v>
       </c>
       <c r="BS8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BT8">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BU8">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV8">
         <v>55</v>
       </c>
       <c r="BW8">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BX8">
         <v>75</v>
       </c>
       <c r="BY8">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BZ8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CA8">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="CB8" t="s">
         <v>104</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -328,7 +328,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-30 09:23:23</t>
+    <t>2026-07-30 11:36:10</t>
   </si>
 </sst>
 </file>
@@ -925,31 +925,31 @@
         <v>3.9</v>
       </c>
       <c r="G2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H2">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J2">
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
         <v>1.56</v>
       </c>
       <c r="M2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N2">
         <v>2.74</v>
       </c>
       <c r="O2">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P2">
         <v>1.55</v>
@@ -958,37 +958,37 @@
         <v>2.62</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
         <v>5.3</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA2">
         <v>34</v>
       </c>
       <c r="AB2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC2">
         <v>7.6</v>
@@ -1000,10 +1000,10 @@
         <v>34</v>
       </c>
       <c r="AF2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -1012,16 +1012,16 @@
         <v>75</v>
       </c>
       <c r="AJ2">
-        <v>290</v>
+        <v>170</v>
       </c>
       <c r="AK2">
         <v>85</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AM2">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN2">
         <v>600</v>
@@ -1030,34 +1030,34 @@
         <v>34</v>
       </c>
       <c r="AP2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AZ2">
         <v>19</v>
@@ -1066,13 +1066,13 @@
         <v>38</v>
       </c>
       <c r="BB2">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BC2">
         <v>42</v>
       </c>
       <c r="BD2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE2">
         <v>10</v>
@@ -1093,31 +1093,31 @@
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT2">
         <v>4.9</v>
@@ -1129,13 +1129,13 @@
         <v>19.5</v>
       </c>
       <c r="BW2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
         <v>42</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>2.4</v>
       </c>
       <c r="H3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I3">
         <v>4.4</v>
@@ -1191,10 +1191,10 @@
         <v>2.52</v>
       </c>
       <c r="O3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P3">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q3">
         <v>2.74</v>
@@ -1224,7 +1224,7 @@
         <v>11</v>
       </c>
       <c r="Z3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA3">
         <v>900</v>
@@ -1239,7 +1239,7 @@
         <v>19</v>
       </c>
       <c r="AE3">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="AF3">
         <v>13.5</v>
@@ -1260,10 +1260,10 @@
         <v>36</v>
       </c>
       <c r="AL3">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AM3">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN3">
         <v>38</v>
@@ -1323,7 +1323,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH3">
         <v>2.72</v>
@@ -1406,10 +1406,10 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="G4">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H4">
         <v>4.4</v>
@@ -1424,22 +1424,22 @@
         <v>3.4</v>
       </c>
       <c r="L4">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M4">
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O4">
         <v>1.53</v>
       </c>
       <c r="P4">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="Q4">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R4">
         <v>1.19</v>
@@ -1457,7 +1457,7 @@
         <v>1.25</v>
       </c>
       <c r="W4">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1466,7 +1466,7 @@
         <v>13</v>
       </c>
       <c r="Z4">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AA4">
         <v>900</v>
@@ -1490,16 +1490,16 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI4">
         <v>500</v>
       </c>
       <c r="AJ4">
+        <v>40</v>
+      </c>
+      <c r="AK4">
         <v>48</v>
-      </c>
-      <c r="AK4">
-        <v>65</v>
       </c>
       <c r="AL4">
         <v>150</v>
@@ -1508,7 +1508,7 @@
         <v>580</v>
       </c>
       <c r="AN4">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AO4">
         <v>600</v>
@@ -1520,7 +1520,7 @@
         <v>10</v>
       </c>
       <c r="AR4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS4">
         <v>10</v>
@@ -1535,7 +1535,7 @@
         <v>17</v>
       </c>
       <c r="AW4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX4">
         <v>9.4</v>
@@ -1562,13 +1562,13 @@
         <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG4">
         <v>10</v>
       </c>
       <c r="BH4">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI4">
         <v>2.32</v>
@@ -1589,10 +1589,10 @@
         <v>4.7</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BP4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ4">
         <v>7</v>
@@ -1607,7 +1607,7 @@
         <v>8</v>
       </c>
       <c r="BU4">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1651,19 +1651,19 @@
         <v>1.88</v>
       </c>
       <c r="G5">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.43</v>
@@ -1672,16 +1672,16 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
         <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q5">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R5">
         <v>1.34</v>
@@ -1690,16 +1690,16 @@
         <v>3.6</v>
       </c>
       <c r="T5">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U5">
         <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X5">
         <v>14.5</v>
@@ -1714,7 +1714,7 @@
         <v>900</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
         <v>8.4</v>
@@ -1723,7 +1723,7 @@
         <v>22</v>
       </c>
       <c r="AE5">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AF5">
         <v>12</v>
@@ -1732,10 +1732,10 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI5">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AJ5">
         <v>23</v>
@@ -1744,7 +1744,7 @@
         <v>22</v>
       </c>
       <c r="AL5">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM5">
         <v>580</v>
@@ -1756,13 +1756,13 @@
         <v>600</v>
       </c>
       <c r="AP5">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ5">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR5">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS5">
         <v>10</v>
@@ -1777,37 +1777,37 @@
         <v>16</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="AX5">
         <v>10</v>
       </c>
       <c r="AY5">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC5">
         <v>11</v>
       </c>
       <c r="BD5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH5">
         <v>3.4</v>
@@ -1896,7 +1896,7 @@
         <v>2.74</v>
       </c>
       <c r="H6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I6">
         <v>3.4</v>
@@ -1905,7 +1905,7 @@
         <v>2.96</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L6">
         <v>1.64</v>
@@ -1914,10 +1914,10 @@
         <v>1.15</v>
       </c>
       <c r="N6">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O6">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P6">
         <v>1.49</v>
@@ -1932,7 +1932,7 @@
         <v>6.4</v>
       </c>
       <c r="T6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U6">
         <v>1.75</v>
@@ -1944,10 +1944,10 @@
         <v>1.57</v>
       </c>
       <c r="X6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z6">
         <v>21</v>
@@ -1956,10 +1956,10 @@
         <v>70</v>
       </c>
       <c r="AB6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AD6">
         <v>15.5</v>
@@ -1974,7 +1974,7 @@
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI6">
         <v>95</v>
@@ -2001,19 +2001,19 @@
         <v>7</v>
       </c>
       <c r="AQ6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6">
         <v>18.5</v>
       </c>
       <c r="AS6">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AT6">
         <v>7</v>
       </c>
       <c r="AU6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV6">
         <v>14</v>
@@ -2049,7 +2049,7 @@
         <v>44</v>
       </c>
       <c r="BG6">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BH6">
         <v>2.64</v>
@@ -2132,22 +2132,22 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="G7">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="H7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="J7">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="L7">
         <v>1.68</v>
@@ -2156,13 +2156,13 @@
         <v>1.16</v>
       </c>
       <c r="N7">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O7">
         <v>1.69</v>
       </c>
       <c r="P7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q7">
         <v>3.15</v>
@@ -2174,184 +2174,184 @@
         <v>7</v>
       </c>
       <c r="T7">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="U7">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="W7">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="X7">
         <v>7.2</v>
       </c>
       <c r="Y7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA7">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AB7">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AC7">
         <v>7.6</v>
       </c>
       <c r="AD7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE7">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="AF7">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI7">
-        <v>490</v>
+        <v>160</v>
       </c>
       <c r="AJ7">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL7">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AM7">
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AO7">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AP7">
         <v>6.6</v>
       </c>
       <c r="AQ7">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AS7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT7">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AU7">
         <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW7">
         <v>75</v>
       </c>
       <c r="AX7">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
         <v>26</v>
       </c>
       <c r="BA7">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="BB7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BE7">
         <v>110</v>
       </c>
       <c r="BF7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BG7">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BH7">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BI7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>18.5</v>
+        <v>2.2</v>
       </c>
       <c r="BN7">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BO7">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP7">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BQ7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BR7">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BS7">
-        <v>14</v>
+        <v>2.12</v>
       </c>
       <c r="BT7">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BU7">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV7">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BW7">
-        <v>14</v>
+        <v>2.14</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BZ7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="CA7">
-        <v>15</v>
+        <v>2.12</v>
       </c>
       <c r="CB7" t="s">
         <v>104</v>
@@ -2374,7 +2374,7 @@
         <v>103</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G8">
         <v>2.04</v>
@@ -2383,7 +2383,7 @@
         <v>4.7</v>
       </c>
       <c r="I8">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J8">
         <v>3.35</v>
@@ -2392,34 +2392,34 @@
         <v>3.4</v>
       </c>
       <c r="L8">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M8">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N8">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="O8">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="P8">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q8">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="R8">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S8">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="T8">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="U8">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="V8">
         <v>1.26</v>
@@ -2428,19 +2428,19 @@
         <v>1.96</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z8">
         <v>34</v>
       </c>
       <c r="AA8">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC8">
         <v>7.4</v>
@@ -2449,16 +2449,16 @@
         <v>20</v>
       </c>
       <c r="AE8">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI8">
         <v>110</v>
@@ -2467,40 +2467,40 @@
         <v>25</v>
       </c>
       <c r="AK8">
+        <v>28</v>
+      </c>
+      <c r="AL8">
+        <v>65</v>
+      </c>
+      <c r="AM8">
+        <v>230</v>
+      </c>
+      <c r="AN8">
         <v>26</v>
       </c>
-      <c r="AL8">
-        <v>60</v>
-      </c>
-      <c r="AM8">
-        <v>210</v>
-      </c>
-      <c r="AN8">
-        <v>25</v>
-      </c>
       <c r="AO8">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR8">
         <v>30</v>
       </c>
       <c r="AS8">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AT8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU8">
         <v>7</v>
       </c>
       <c r="AV8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW8">
         <v>75</v>
@@ -2509,19 +2509,19 @@
         <v>9.6</v>
       </c>
       <c r="AY8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
+        <v>25</v>
+      </c>
+      <c r="BA8">
+        <v>95</v>
+      </c>
+      <c r="BB8">
         <v>23</v>
       </c>
-      <c r="BA8">
-        <v>90</v>
-      </c>
-      <c r="BB8">
-        <v>22</v>
-      </c>
       <c r="BC8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD8">
         <v>50</v>
@@ -2530,25 +2530,25 @@
         <v>70</v>
       </c>
       <c r="BF8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BH8">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BI8">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BL8">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="BM8">
         <v>15.5</v>
@@ -2557,16 +2557,16 @@
         <v>4.4</v>
       </c>
       <c r="BO8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BR8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS8">
         <v>12</v>
@@ -2575,25 +2575,25 @@
         <v>8</v>
       </c>
       <c r="BU8">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV8">
         <v>55</v>
       </c>
       <c r="BW8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX8">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY8">
         <v>13.5</v>
       </c>
       <c r="BZ8">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="CA8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="s">
         <v>104</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -328,7 +328,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-30 11:36:10</t>
+    <t>2026-07-30 13:50:57</t>
   </si>
 </sst>
 </file>
@@ -922,10 +922,10 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H2">
         <v>2.26</v>
@@ -934,7 +934,7 @@
         <v>2.36</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>3.15</v>
@@ -946,13 +946,13 @@
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q2">
         <v>2.62</v>
@@ -1012,7 +1012,7 @@
         <v>75</v>
       </c>
       <c r="AJ2">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="AK2">
         <v>85</v>
@@ -1042,7 +1042,7 @@
         <v>23</v>
       </c>
       <c r="AT2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1066,7 +1066,7 @@
         <v>38</v>
       </c>
       <c r="BB2">
-        <v>40</v>
+        <v>9.6</v>
       </c>
       <c r="BC2">
         <v>42</v>
@@ -1164,22 +1164,22 @@
         <v>98</v>
       </c>
       <c r="F3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.61</v>
@@ -1188,10 +1188,10 @@
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O3">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="P3">
         <v>1.5</v>
@@ -1203,19 +1203,19 @@
         <v>1.17</v>
       </c>
       <c r="S3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V3">
         <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X3">
         <v>8.4</v>
@@ -1272,7 +1272,7 @@
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3">
         <v>9</v>
@@ -1281,7 +1281,7 @@
         <v>19</v>
       </c>
       <c r="AS3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT3">
         <v>5.9</v>
@@ -1305,7 +1305,7 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB3">
         <v>21</v>
@@ -1314,10 +1314,10 @@
         <v>23</v>
       </c>
       <c r="BD3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3">
         <v>8.199999999999999</v>
@@ -1326,16 +1326,16 @@
         <v>9.6</v>
       </c>
       <c r="BH3">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BI3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK3">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1344,10 +1344,10 @@
         <v>10.5</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP3">
         <v>21</v>
@@ -1359,13 +1359,13 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
         <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
@@ -1406,13 +1406,13 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G4">
         <v>2.12</v>
       </c>
       <c r="H4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I4">
         <v>5.1</v>
@@ -1430,13 +1430,13 @@
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O4">
         <v>1.53</v>
       </c>
       <c r="P4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q4">
         <v>2.62</v>
@@ -1451,13 +1451,13 @@
         <v>2.2</v>
       </c>
       <c r="U4">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V4">
         <v>1.25</v>
       </c>
       <c r="W4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1466,7 +1466,7 @@
         <v>13</v>
       </c>
       <c r="Z4">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AA4">
         <v>900</v>
@@ -1508,7 +1508,7 @@
         <v>580</v>
       </c>
       <c r="AN4">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AO4">
         <v>600</v>
@@ -1520,7 +1520,7 @@
         <v>10</v>
       </c>
       <c r="AR4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS4">
         <v>10</v>
@@ -1562,7 +1562,7 @@
         <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
         <v>10</v>
@@ -1648,10 +1648,10 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G5">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H5">
         <v>4.6</v>
@@ -1699,7 +1699,7 @@
         <v>1.25</v>
       </c>
       <c r="W5">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X5">
         <v>14.5</v>
@@ -1890,19 +1890,19 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G6">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H6">
         <v>3.3</v>
       </c>
       <c r="I6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J6">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K6">
         <v>3.05</v>
@@ -1920,7 +1920,7 @@
         <v>1.64</v>
       </c>
       <c r="P6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q6">
         <v>2.96</v>
@@ -1938,7 +1938,7 @@
         <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
         <v>1.57</v>
@@ -2007,10 +2007,10 @@
         <v>18.5</v>
       </c>
       <c r="AS6">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AT6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU6">
         <v>6.4</v>
@@ -2046,7 +2046,7 @@
         <v>70</v>
       </c>
       <c r="BF6">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BG6">
         <v>55</v>
@@ -2135,10 +2135,10 @@
         <v>2.04</v>
       </c>
       <c r="G7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I7">
         <v>5.2</v>
@@ -2147,7 +2147,7 @@
         <v>3.15</v>
       </c>
       <c r="K7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L7">
         <v>1.68</v>
@@ -2162,7 +2162,7 @@
         <v>1.69</v>
       </c>
       <c r="P7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q7">
         <v>3.15</v>
@@ -2171,22 +2171,22 @@
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T7">
         <v>2.52</v>
       </c>
       <c r="U7">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W7">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y7">
         <v>11.5</v>
@@ -2195,13 +2195,13 @@
         <v>34</v>
       </c>
       <c r="AA7">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB7">
         <v>5.8</v>
       </c>
       <c r="AC7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
         <v>24</v>
@@ -2222,7 +2222,7 @@
         <v>160</v>
       </c>
       <c r="AJ7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK7">
         <v>34</v>
@@ -2243,13 +2243,13 @@
         <v>6.6</v>
       </c>
       <c r="AQ7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR7">
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AT7">
         <v>5.4</v>
@@ -2261,19 +2261,19 @@
         <v>20</v>
       </c>
       <c r="AW7">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AX7">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7">
         <v>11</v>
       </c>
       <c r="AZ7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BA7">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="BB7">
         <v>23</v>
@@ -2288,10 +2288,10 @@
         <v>110</v>
       </c>
       <c r="BF7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG7">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="BH7">
         <v>2.48</v>
@@ -2383,7 +2383,7 @@
         <v>4.7</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J8">
         <v>3.35</v>
@@ -2392,7 +2392,7 @@
         <v>3.4</v>
       </c>
       <c r="L8">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M8">
         <v>1.13</v>
@@ -2401,16 +2401,16 @@
         <v>2.68</v>
       </c>
       <c r="O8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P8">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q8">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R8">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S8">
         <v>5.9</v>
@@ -2452,7 +2452,7 @@
         <v>90</v>
       </c>
       <c r="AF8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG8">
         <v>11</v>
@@ -2476,10 +2476,10 @@
         <v>230</v>
       </c>
       <c r="AN8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO8">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AP8">
         <v>8.199999999999999</v>
@@ -2488,7 +2488,7 @@
         <v>11</v>
       </c>
       <c r="AR8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS8">
         <v>95</v>
@@ -2497,7 +2497,7 @@
         <v>6</v>
       </c>
       <c r="AU8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
         <v>18.5</v>
@@ -2506,13 +2506,13 @@
         <v>75</v>
       </c>
       <c r="AX8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8">
         <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8">
         <v>95</v>
@@ -2530,28 +2530,28 @@
         <v>70</v>
       </c>
       <c r="BF8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG8">
         <v>100</v>
       </c>
       <c r="BH8">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BI8">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BL8">
         <v>250</v>
       </c>
       <c r="BM8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN8">
         <v>4.4</v>
@@ -2563,37 +2563,37 @@
         <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8">
         <v>44</v>
       </c>
       <c r="BS8">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BT8">
         <v>8</v>
       </c>
       <c r="BU8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV8">
         <v>55</v>
       </c>
       <c r="BW8">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BX8">
         <v>80</v>
       </c>
       <c r="BY8">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ8">
         <v>48</v>
       </c>
       <c r="CA8">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="CB8" t="s">
         <v>104</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -328,7 +328,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-30 13:50:57</t>
+    <t>2026-07-30 16:05:48</t>
   </si>
 </sst>
 </file>
@@ -922,220 +922,220 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="G2">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H2">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="I2">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="O2">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="P2">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="Q2">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="R2">
         <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>1.06</v>
       </c>
       <c r="U2">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V2">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z2">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AF2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AG2">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2">
+        <v>55</v>
+      </c>
+      <c r="AJ2">
+        <v>110</v>
+      </c>
+      <c r="AK2">
         <v>75</v>
       </c>
-      <c r="AJ2">
-        <v>290</v>
-      </c>
-      <c r="AK2">
-        <v>85</v>
-      </c>
       <c r="AL2">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AO2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AP2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
         <v>6.6</v>
       </c>
       <c r="AR2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AS2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT2">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="AY2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BB2">
-        <v>9.6</v>
+        <v>90</v>
       </c>
       <c r="BC2">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BD2">
-        <v>9.6</v>
+        <v>65</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="BF2">
-        <v>9.6</v>
+        <v>80</v>
       </c>
       <c r="BG2">
         <v>21</v>
       </c>
       <c r="BH2">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BI2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>3.9</v>
       </c>
       <c r="BN2">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BO2">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BP2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>3.9</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>3.9</v>
       </c>
       <c r="BT2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BV2">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BX2">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1167,19 +1167,19 @@
         <v>2.22</v>
       </c>
       <c r="G3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I3">
         <v>4.3</v>
       </c>
       <c r="J3">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
         <v>1.61</v>
@@ -1188,37 +1188,37 @@
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="O3">
         <v>1.55</v>
       </c>
       <c r="P3">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T3">
         <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y3">
         <v>11</v>
@@ -1236,7 +1236,7 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE3">
         <v>230</v>
@@ -1248,10 +1248,10 @@
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AJ3">
         <v>36</v>
@@ -1260,40 +1260,40 @@
         <v>36</v>
       </c>
       <c r="AL3">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO3">
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR3">
         <v>19</v>
       </c>
       <c r="AS3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
         <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1305,7 +1305,7 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB3">
         <v>21</v>
@@ -1314,13 +1314,13 @@
         <v>23</v>
       </c>
       <c r="BD3">
-        <v>9.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BE3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG3">
         <v>9.6</v>
@@ -1406,7 +1406,7 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>2.12</v>
@@ -1421,10 +1421,10 @@
         <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M4">
         <v>1.12</v>
@@ -1442,7 +1442,7 @@
         <v>2.62</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
         <v>5.3</v>
@@ -1457,7 +1457,7 @@
         <v>1.25</v>
       </c>
       <c r="W4">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1466,19 +1466,19 @@
         <v>13</v>
       </c>
       <c r="Z4">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA4">
         <v>900</v>
       </c>
       <c r="AB4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE4">
         <v>500</v>
@@ -1490,16 +1490,16 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AI4">
         <v>500</v>
       </c>
       <c r="AJ4">
+        <v>27</v>
+      </c>
+      <c r="AK4">
         <v>40</v>
-      </c>
-      <c r="AK4">
-        <v>48</v>
       </c>
       <c r="AL4">
         <v>150</v>
@@ -1508,124 +1508,124 @@
         <v>580</v>
       </c>
       <c r="AN4">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AO4">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="AP4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ4">
+        <v>10.5</v>
+      </c>
+      <c r="AR4">
+        <v>15</v>
+      </c>
+      <c r="AS4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT4">
+        <v>5.9</v>
+      </c>
+      <c r="AU4">
+        <v>6.8</v>
+      </c>
+      <c r="AV4">
+        <v>13.5</v>
+      </c>
+      <c r="AW4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY4">
         <v>10</v>
       </c>
-      <c r="AR4">
-        <v>14.5</v>
-      </c>
-      <c r="AS4">
-        <v>10</v>
-      </c>
-      <c r="AT4">
-        <v>5.7</v>
-      </c>
-      <c r="AU4">
-        <v>6.6</v>
-      </c>
-      <c r="AV4">
-        <v>17</v>
-      </c>
-      <c r="AW4">
-        <v>10</v>
-      </c>
-      <c r="AX4">
+      <c r="AZ4">
+        <v>22</v>
+      </c>
+      <c r="BA4">
+        <v>9</v>
+      </c>
+      <c r="BB4">
+        <v>21</v>
+      </c>
+      <c r="BC4">
+        <v>19</v>
+      </c>
+      <c r="BD4">
+        <v>32</v>
+      </c>
+      <c r="BE4">
         <v>9.4</v>
       </c>
-      <c r="AY4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ4">
+      <c r="BF4">
         <v>21</v>
       </c>
-      <c r="BA4">
-        <v>10</v>
-      </c>
-      <c r="BB4">
-        <v>12.5</v>
-      </c>
-      <c r="BC4">
-        <v>12.5</v>
-      </c>
-      <c r="BD4">
-        <v>9.4</v>
-      </c>
-      <c r="BE4">
-        <v>10.5</v>
-      </c>
-      <c r="BF4">
-        <v>7.8</v>
-      </c>
       <c r="BG4">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>104</v>
@@ -1648,13 +1648,13 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G5">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -1678,7 +1678,7 @@
         <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         <v>3.6</v>
       </c>
       <c r="T5">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U5">
         <v>2.02</v>
@@ -1699,13 +1699,13 @@
         <v>1.25</v>
       </c>
       <c r="W5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z5">
         <v>95</v>
@@ -1738,10 +1738,10 @@
         <v>320</v>
       </c>
       <c r="AJ5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK5">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AL5">
         <v>85</v>
@@ -1750,7 +1750,7 @@
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO5">
         <v>600</v>
@@ -1765,7 +1765,7 @@
         <v>14.5</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT5">
         <v>7.6</v>
@@ -1774,7 +1774,7 @@
         <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW5">
         <v>23</v>
@@ -1783,7 +1783,7 @@
         <v>10</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
@@ -1792,7 +1792,7 @@
         <v>29</v>
       </c>
       <c r="BB5">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BC5">
         <v>11</v>
@@ -1831,7 +1831,7 @@
         <v>4.6</v>
       </c>
       <c r="BO5">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
         <v>14</v>
@@ -1890,25 +1890,25 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G6">
         <v>2.76</v>
       </c>
       <c r="H6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I6">
         <v>3.35</v>
       </c>
       <c r="J6">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M6">
         <v>1.15</v>
@@ -1920,7 +1920,7 @@
         <v>1.64</v>
       </c>
       <c r="P6">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q6">
         <v>2.96</v>
@@ -1932,7 +1932,7 @@
         <v>6.4</v>
       </c>
       <c r="T6">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U6">
         <v>1.75</v>
@@ -1947,7 +1947,7 @@
         <v>7.6</v>
       </c>
       <c r="Y6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z6">
         <v>21</v>
@@ -1959,13 +1959,13 @@
         <v>7.6</v>
       </c>
       <c r="AC6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD6">
         <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF6">
         <v>15.5</v>
@@ -1974,16 +1974,16 @@
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI6">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ6">
         <v>44</v>
       </c>
       <c r="AK6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL6">
         <v>75</v>
@@ -1995,13 +1995,13 @@
         <v>50</v>
       </c>
       <c r="AO6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP6">
         <v>7</v>
       </c>
       <c r="AQ6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR6">
         <v>18.5</v>
@@ -2010,7 +2010,7 @@
         <v>50</v>
       </c>
       <c r="AT6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU6">
         <v>6.4</v>
@@ -2019,10 +2019,10 @@
         <v>14</v>
       </c>
       <c r="AW6">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AX6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY6">
         <v>12.5</v>
@@ -2031,13 +2031,13 @@
         <v>23</v>
       </c>
       <c r="BA6">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BB6">
+        <v>40</v>
+      </c>
+      <c r="BC6">
         <v>38</v>
-      </c>
-      <c r="BC6">
-        <v>36</v>
       </c>
       <c r="BD6">
         <v>60</v>
@@ -2046,70 +2046,70 @@
         <v>70</v>
       </c>
       <c r="BF6">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BG6">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BH6">
         <v>2.64</v>
       </c>
       <c r="BI6">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="BJ6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BM6">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BQ6">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BR6">
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6">
         <v>6.4</v>
       </c>
       <c r="BU6">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
         <v>36</v>
       </c>
       <c r="BW6">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CA6">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="s">
         <v>104</v>
@@ -2132,7 +2132,7 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G7">
         <v>2.06</v>
@@ -2150,19 +2150,19 @@
         <v>3.2</v>
       </c>
       <c r="L7">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M7">
         <v>1.16</v>
       </c>
       <c r="N7">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O7">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q7">
         <v>3.15</v>
@@ -2174,16 +2174,16 @@
         <v>7.2</v>
       </c>
       <c r="T7">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U7">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V7">
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X7">
         <v>7.4</v>
@@ -2216,7 +2216,7 @@
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI7">
         <v>160</v>
@@ -2240,7 +2240,7 @@
         <v>210</v>
       </c>
       <c r="AP7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7">
         <v>10.5</v>
@@ -2249,19 +2249,19 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AT7">
         <v>5.4</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV7">
         <v>20</v>
       </c>
       <c r="AW7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AX7">
         <v>9.199999999999999</v>
@@ -2297,7 +2297,7 @@
         <v>2.48</v>
       </c>
       <c r="BI7">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BJ7">
         <v>13</v>
@@ -2309,13 +2309,13 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.2</v>
+        <v>19.5</v>
       </c>
       <c r="BN7">
         <v>4.4</v>
       </c>
       <c r="BO7">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BP7">
         <v>17.5</v>
@@ -2339,7 +2339,7 @@
         <v>65</v>
       </c>
       <c r="BW7">
-        <v>2.14</v>
+        <v>15.5</v>
       </c>
       <c r="BX7">
         <v>100</v>
@@ -2374,16 +2374,16 @@
         <v>103</v>
       </c>
       <c r="F8">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G8">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H8">
+        <v>4.6</v>
+      </c>
+      <c r="I8">
         <v>4.7</v>
-      </c>
-      <c r="I8">
-        <v>4.8</v>
       </c>
       <c r="J8">
         <v>3.35</v>
@@ -2392,40 +2392,40 @@
         <v>3.4</v>
       </c>
       <c r="L8">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M8">
         <v>1.13</v>
       </c>
       <c r="N8">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="O8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P8">
         <v>1.55</v>
       </c>
       <c r="Q8">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R8">
         <v>1.19</v>
       </c>
       <c r="S8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U8">
         <v>1.73</v>
       </c>
       <c r="V8">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W8">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X8">
         <v>8.6</v>
@@ -2443,7 +2443,7 @@
         <v>6.4</v>
       </c>
       <c r="AC8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD8">
         <v>20</v>
@@ -2452,7 +2452,7 @@
         <v>90</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
         <v>11</v>
@@ -2473,22 +2473,22 @@
         <v>65</v>
       </c>
       <c r="AM8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AN8">
         <v>27</v>
       </c>
       <c r="AO8">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP8">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS8">
         <v>95</v>
@@ -2497,7 +2497,7 @@
         <v>6</v>
       </c>
       <c r="AU8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV8">
         <v>18.5</v>
@@ -2530,70 +2530,70 @@
         <v>70</v>
       </c>
       <c r="BF8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG8">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="BH8">
         <v>2.62</v>
       </c>
       <c r="BI8">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BL8">
         <v>250</v>
       </c>
       <c r="BM8">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN8">
         <v>4.4</v>
       </c>
       <c r="BO8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP8">
         <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8">
         <v>44</v>
       </c>
       <c r="BS8">
+        <v>12.5</v>
+      </c>
+      <c r="BT8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU8">
+        <v>6.2</v>
+      </c>
+      <c r="BV8">
+        <v>60</v>
+      </c>
+      <c r="BW8">
         <v>13.5</v>
-      </c>
-      <c r="BT8">
-        <v>8</v>
-      </c>
-      <c r="BU8">
-        <v>5.6</v>
-      </c>
-      <c r="BV8">
-        <v>55</v>
-      </c>
-      <c r="BW8">
-        <v>14.5</v>
       </c>
       <c r="BX8">
         <v>80</v>
       </c>
       <c r="BY8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ8">
         <v>48</v>
       </c>
       <c r="CA8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CB8" t="s">
         <v>104</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
   <si>
     <t>League</t>
   </si>
@@ -256,12 +256,12 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
-    <t>Ecuadorian Serie B</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -271,9 +271,6 @@
     <t>2026-07-30</t>
   </si>
   <si>
-    <t>19:00:00</t>
-  </si>
-  <si>
     <t>20:30:00</t>
   </si>
   <si>
@@ -286,9 +283,6 @@
     <t>22:30:00</t>
   </si>
   <si>
-    <t>Sportivo San Lorenzo</t>
-  </si>
-  <si>
     <t>Cumbaya FC</t>
   </si>
   <si>
@@ -307,9 +301,6 @@
     <t>Corinthians</t>
   </si>
   <si>
-    <t>Guarani (Par)</t>
-  </si>
-  <si>
     <t>CD Cuenca Juniors</t>
   </si>
   <si>
@@ -328,7 +319,7 @@
     <t>Athletico-PR</t>
   </si>
   <si>
-    <t>2026-07-30 16:05:48</t>
+    <t>2026-07-30 18:21:09</t>
   </si>
 </sst>
 </file>
@@ -660,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -916,477 +907,477 @@
         <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>4.2</v>
+        <v>2.82</v>
       </c>
       <c r="G2">
+        <v>3.15</v>
+      </c>
+      <c r="H2">
+        <v>4.4</v>
+      </c>
+      <c r="I2">
+        <v>4.9</v>
+      </c>
+      <c r="J2">
+        <v>2.22</v>
+      </c>
+      <c r="K2">
+        <v>2.3</v>
+      </c>
+      <c r="L2">
+        <v>12</v>
+      </c>
+      <c r="M2">
+        <v>1.46</v>
+      </c>
+      <c r="N2">
+        <v>1.42</v>
+      </c>
+      <c r="O2">
+        <v>3.2</v>
+      </c>
+      <c r="P2">
+        <v>1.11</v>
+      </c>
+      <c r="Q2">
+        <v>9.6</v>
+      </c>
+      <c r="R2">
+        <v>1.02</v>
+      </c>
+      <c r="S2">
+        <v>36</v>
+      </c>
+      <c r="T2">
         <v>4.6</v>
       </c>
-      <c r="H2">
-        <v>2.12</v>
-      </c>
-      <c r="I2">
-        <v>2.24</v>
-      </c>
-      <c r="J2">
-        <v>3.1</v>
-      </c>
-      <c r="K2">
-        <v>3.3</v>
-      </c>
-      <c r="L2">
-        <v>1.53</v>
-      </c>
-      <c r="M2">
-        <v>1.12</v>
-      </c>
-      <c r="N2">
-        <v>2.88</v>
-      </c>
-      <c r="O2">
-        <v>1.5</v>
-      </c>
-      <c r="P2">
-        <v>1.64</v>
-      </c>
-      <c r="Q2">
-        <v>2.56</v>
-      </c>
-      <c r="R2">
-        <v>1.2</v>
-      </c>
-      <c r="S2">
-        <v>4.5</v>
-      </c>
-      <c r="T2">
-        <v>1.06</v>
-      </c>
       <c r="U2">
-        <v>1.84</v>
+        <v>1.22</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="Y2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="Z2">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="AA2">
-        <v>27</v>
+        <v>290</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>4.9</v>
       </c>
       <c r="AC2">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="AE2">
-        <v>28</v>
+        <v>390</v>
       </c>
       <c r="AF2">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AG2">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
         <v>110</v>
       </c>
       <c r="AK2">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>110</v>
+        <v>410</v>
       </c>
       <c r="AO2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR2">
+        <v>28</v>
+      </c>
+      <c r="AS2">
+        <v>140</v>
+      </c>
+      <c r="AT2">
+        <v>4.5</v>
+      </c>
+      <c r="AU2">
+        <v>8.4</v>
+      </c>
+      <c r="AV2">
+        <v>36</v>
+      </c>
+      <c r="AW2">
+        <v>210</v>
+      </c>
+      <c r="AX2">
+        <v>15</v>
+      </c>
+      <c r="AY2">
+        <v>27</v>
+      </c>
+      <c r="AZ2">
+        <v>85</v>
+      </c>
+      <c r="BA2">
+        <v>380</v>
+      </c>
+      <c r="BB2">
+        <v>60</v>
+      </c>
+      <c r="BC2">
+        <v>120</v>
+      </c>
+      <c r="BD2">
+        <v>380</v>
+      </c>
+      <c r="BE2">
+        <v>450</v>
+      </c>
+      <c r="BF2">
+        <v>190</v>
+      </c>
+      <c r="BG2">
+        <v>320</v>
+      </c>
+      <c r="BH2">
+        <v>1.12</v>
+      </c>
+      <c r="BI2">
+        <v>1.08</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>12.5</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>4.5</v>
+      </c>
+      <c r="BN2">
+        <v>65</v>
+      </c>
+      <c r="BO2">
+        <v>7.8</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>7.2</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>4.5</v>
+      </c>
+      <c r="BT2">
+        <v>80</v>
+      </c>
+      <c r="BU2">
         <v>10</v>
       </c>
-      <c r="AS2">
-        <v>22</v>
-      </c>
-      <c r="AT2">
-        <v>12</v>
-      </c>
-      <c r="AU2">
-        <v>6.6</v>
-      </c>
-      <c r="AV2">
-        <v>10</v>
-      </c>
-      <c r="AW2">
-        <v>24</v>
-      </c>
-      <c r="AX2">
-        <v>28</v>
-      </c>
-      <c r="AY2">
-        <v>18</v>
-      </c>
-      <c r="AZ2">
-        <v>20</v>
-      </c>
-      <c r="BA2">
-        <v>44</v>
-      </c>
-      <c r="BB2">
-        <v>90</v>
-      </c>
-      <c r="BC2">
-        <v>60</v>
-      </c>
-      <c r="BD2">
-        <v>65</v>
-      </c>
-      <c r="BE2">
-        <v>90</v>
-      </c>
-      <c r="BF2">
-        <v>80</v>
-      </c>
-      <c r="BG2">
-        <v>21</v>
-      </c>
-      <c r="BH2">
-        <v>2.9</v>
-      </c>
-      <c r="BI2">
-        <v>2.38</v>
-      </c>
-      <c r="BJ2">
-        <v>12</v>
-      </c>
-      <c r="BK2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>3.9</v>
-      </c>
-      <c r="BN2">
-        <v>8.6</v>
-      </c>
-      <c r="BO2">
-        <v>6.2</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>3.9</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>3.9</v>
-      </c>
-      <c r="BT2">
-        <v>5</v>
-      </c>
-      <c r="BU2">
-        <v>3.9</v>
-      </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BZ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:80">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
         <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F3">
-        <v>2.22</v>
+        <v>1.33</v>
       </c>
       <c r="G3">
-        <v>2.36</v>
+        <v>1.35</v>
       </c>
       <c r="H3">
-        <v>3.8</v>
+        <v>15.5</v>
       </c>
       <c r="I3">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="L3">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="O3">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S3">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
         <v>1.77</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="W3">
-        <v>1.73</v>
+        <v>3.7</v>
       </c>
       <c r="X3">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>4.1</v>
+      </c>
+      <c r="AC3">
+        <v>6.6</v>
+      </c>
+      <c r="AD3">
+        <v>25</v>
+      </c>
+      <c r="AE3">
+        <v>190</v>
+      </c>
+      <c r="AF3">
+        <v>5.3</v>
+      </c>
+      <c r="AG3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AH3">
+        <v>32</v>
+      </c>
+      <c r="AI3">
+        <v>210</v>
+      </c>
+      <c r="AJ3">
+        <v>14.5</v>
+      </c>
+      <c r="AK3">
+        <v>27</v>
+      </c>
+      <c r="AL3">
+        <v>100</v>
+      </c>
+      <c r="AM3">
+        <v>530</v>
+      </c>
+      <c r="AN3">
+        <v>32</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>10.5</v>
+      </c>
+      <c r="AQ3">
+        <v>10.5</v>
+      </c>
+      <c r="AR3">
+        <v>10.5</v>
+      </c>
+      <c r="AS3">
+        <v>10.5</v>
+      </c>
+      <c r="AT3">
+        <v>3.8</v>
+      </c>
+      <c r="AU3">
+        <v>6.2</v>
+      </c>
+      <c r="AV3">
+        <v>20</v>
+      </c>
+      <c r="AW3">
+        <v>85</v>
+      </c>
+      <c r="AX3">
+        <v>4.9</v>
+      </c>
+      <c r="AY3">
+        <v>7.4</v>
+      </c>
+      <c r="AZ3">
+        <v>25</v>
+      </c>
+      <c r="BA3">
+        <v>110</v>
+      </c>
+      <c r="BB3">
+        <v>12.5</v>
+      </c>
+      <c r="BC3">
+        <v>21</v>
+      </c>
+      <c r="BD3">
+        <v>65</v>
+      </c>
+      <c r="BE3">
         <v>46</v>
       </c>
-      <c r="AA3">
-        <v>900</v>
-      </c>
-      <c r="AB3">
-        <v>7.2</v>
-      </c>
-      <c r="AC3">
-        <v>7.6</v>
-      </c>
-      <c r="AD3">
-        <v>18.5</v>
-      </c>
-      <c r="AE3">
-        <v>230</v>
-      </c>
-      <c r="AF3">
-        <v>13.5</v>
-      </c>
-      <c r="AG3">
-        <v>12.5</v>
-      </c>
-      <c r="AH3">
-        <v>25</v>
-      </c>
-      <c r="AI3">
-        <v>230</v>
-      </c>
-      <c r="AJ3">
-        <v>36</v>
-      </c>
-      <c r="AK3">
-        <v>36</v>
-      </c>
-      <c r="AL3">
-        <v>190</v>
-      </c>
-      <c r="AM3">
-        <v>500</v>
-      </c>
-      <c r="AN3">
-        <v>36</v>
-      </c>
-      <c r="AO3">
-        <v>600</v>
-      </c>
-      <c r="AP3">
-        <v>7.4</v>
-      </c>
-      <c r="AQ3">
-        <v>9.4</v>
-      </c>
-      <c r="AR3">
-        <v>19</v>
-      </c>
-      <c r="AS3">
-        <v>9.6</v>
-      </c>
-      <c r="AT3">
-        <v>6.2</v>
-      </c>
-      <c r="AU3">
-        <v>6.4</v>
-      </c>
-      <c r="AV3">
-        <v>15.5</v>
-      </c>
-      <c r="AW3">
-        <v>9.6</v>
-      </c>
-      <c r="AX3">
-        <v>10.5</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
-        <v>21</v>
-      </c>
-      <c r="BA3">
-        <v>9.6</v>
-      </c>
-      <c r="BB3">
-        <v>21</v>
-      </c>
-      <c r="BC3">
-        <v>23</v>
-      </c>
-      <c r="BD3">
-        <v>44</v>
-      </c>
-      <c r="BE3">
-        <v>10</v>
-      </c>
       <c r="BF3">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="BG3">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="BH3">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.26</v>
+        <v>1.25</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="BK3">
-        <v>9</v>
+        <v>1.25</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>1.25</v>
       </c>
       <c r="BN3">
-        <v>5.1</v>
+        <v>1.17</v>
       </c>
       <c r="BO3">
-        <v>3.9</v>
+        <v>1.07</v>
       </c>
       <c r="BP3">
-        <v>21</v>
+        <v>880</v>
       </c>
       <c r="BQ3">
-        <v>7.2</v>
+        <v>1.25</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.4</v>
+        <v>1.25</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9.199999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="CB3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1400,240 +1391,240 @@
         <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F4">
+        <v>1.78</v>
+      </c>
+      <c r="G4">
+        <v>1.81</v>
+      </c>
+      <c r="H4">
+        <v>5.4</v>
+      </c>
+      <c r="I4">
+        <v>5.6</v>
+      </c>
+      <c r="J4">
+        <v>3.7</v>
+      </c>
+      <c r="K4">
+        <v>3.85</v>
+      </c>
+      <c r="L4">
+        <v>1.43</v>
+      </c>
+      <c r="M4">
+        <v>1.08</v>
+      </c>
+      <c r="N4">
+        <v>3.75</v>
+      </c>
+      <c r="O4">
+        <v>1.35</v>
+      </c>
+      <c r="P4">
+        <v>1.92</v>
+      </c>
+      <c r="Q4">
+        <v>2.04</v>
+      </c>
+      <c r="R4">
+        <v>1.35</v>
+      </c>
+      <c r="S4">
+        <v>3.75</v>
+      </c>
+      <c r="T4">
+        <v>1.92</v>
+      </c>
+      <c r="U4">
         <v>2</v>
       </c>
-      <c r="G4">
-        <v>2.12</v>
-      </c>
-      <c r="H4">
-        <v>4.5</v>
-      </c>
-      <c r="I4">
-        <v>5.1</v>
-      </c>
-      <c r="J4">
-        <v>3.1</v>
-      </c>
-      <c r="K4">
-        <v>3.45</v>
-      </c>
-      <c r="L4">
-        <v>1.57</v>
-      </c>
-      <c r="M4">
-        <v>1.12</v>
-      </c>
-      <c r="N4">
-        <v>2.74</v>
-      </c>
-      <c r="O4">
-        <v>1.53</v>
-      </c>
-      <c r="P4">
-        <v>1.56</v>
-      </c>
-      <c r="Q4">
-        <v>2.62</v>
-      </c>
-      <c r="R4">
-        <v>1.2</v>
-      </c>
-      <c r="S4">
-        <v>5.3</v>
-      </c>
-      <c r="T4">
-        <v>2.2</v>
-      </c>
-      <c r="U4">
-        <v>1.72</v>
-      </c>
       <c r="V4">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z4">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA4">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>8</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE4">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AI4">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AJ4">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AK4">
+        <v>19.5</v>
+      </c>
+      <c r="AL4">
         <v>40</v>
       </c>
-      <c r="AL4">
-        <v>150</v>
-      </c>
       <c r="AM4">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN4">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AP4">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AR4">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AS4">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="AT4">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW4">
-        <v>8.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="AX4">
         <v>9.199999999999999</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA4">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="BB4">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BC4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE4">
+        <v>29</v>
+      </c>
+      <c r="BF4">
+        <v>11</v>
+      </c>
+      <c r="BG4">
+        <v>75</v>
+      </c>
+      <c r="BH4">
+        <v>3.45</v>
+      </c>
+      <c r="BI4">
+        <v>3.05</v>
+      </c>
+      <c r="BJ4">
+        <v>10.5</v>
+      </c>
+      <c r="BK4">
+        <v>6.4</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>13.5</v>
+      </c>
+      <c r="BN4">
+        <v>4.4</v>
+      </c>
+      <c r="BO4">
+        <v>3.9</v>
+      </c>
+      <c r="BP4">
+        <v>12.5</v>
+      </c>
+      <c r="BQ4">
+        <v>7.2</v>
+      </c>
+      <c r="BR4">
+        <v>28</v>
+      </c>
+      <c r="BS4">
+        <v>9.6</v>
+      </c>
+      <c r="BT4">
+        <v>8.6</v>
+      </c>
+      <c r="BU4">
+        <v>5.8</v>
+      </c>
+      <c r="BV4">
+        <v>46</v>
+      </c>
+      <c r="BW4">
+        <v>11</v>
+      </c>
+      <c r="BX4">
+        <v>55</v>
+      </c>
+      <c r="BY4">
+        <v>11.5</v>
+      </c>
+      <c r="BZ4">
+        <v>24</v>
+      </c>
+      <c r="CA4">
         <v>9.4</v>
       </c>
-      <c r="BF4">
-        <v>21</v>
-      </c>
-      <c r="BG4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>1.04</v>
-      </c>
-      <c r="BJ4">
-        <v>1000</v>
-      </c>
-      <c r="BK4">
-        <v>1.04</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.04</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>1.04</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.04</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.04</v>
-      </c>
-      <c r="BT4">
-        <v>1000</v>
-      </c>
-      <c r="BU4">
-        <v>1.04</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>1.04</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>1.04</v>
-      </c>
-      <c r="BZ4">
-        <v>1000</v>
-      </c>
-      <c r="CA4">
-        <v>1.04</v>
-      </c>
       <c r="CB4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
         <v>84</v>
@@ -1642,235 +1633,235 @@
         <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F5">
-        <v>1.88</v>
+        <v>2.88</v>
       </c>
       <c r="G5">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="J5">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="P5">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="S5">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="T5">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>2.06</v>
+        <v>1.52</v>
       </c>
       <c r="X5">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="Y5">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="Z5">
-        <v>95</v>
+        <v>18.5</v>
       </c>
       <c r="AA5">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC5">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AD5">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI5">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AK5">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AL5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM5">
-        <v>580</v>
+        <v>230</v>
       </c>
       <c r="AN5">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AO5">
-        <v>600</v>
+        <v>75</v>
       </c>
       <c r="AP5">
         <v>7</v>
       </c>
       <c r="AQ5">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR5">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS5">
+        <v>50</v>
+      </c>
+      <c r="AT5">
+        <v>7.2</v>
+      </c>
+      <c r="AU5">
+        <v>6.4</v>
+      </c>
+      <c r="AV5">
+        <v>13.5</v>
+      </c>
+      <c r="AW5">
+        <v>46</v>
+      </c>
+      <c r="AX5">
+        <v>15</v>
+      </c>
+      <c r="AY5">
+        <v>12.5</v>
+      </c>
+      <c r="AZ5">
+        <v>24</v>
+      </c>
+      <c r="BA5">
+        <v>65</v>
+      </c>
+      <c r="BB5">
+        <v>46</v>
+      </c>
+      <c r="BC5">
+        <v>42</v>
+      </c>
+      <c r="BD5">
+        <v>65</v>
+      </c>
+      <c r="BE5">
+        <v>70</v>
+      </c>
+      <c r="BF5">
+        <v>50</v>
+      </c>
+      <c r="BG5">
+        <v>60</v>
+      </c>
+      <c r="BH5">
+        <v>2.56</v>
+      </c>
+      <c r="BI5">
+        <v>2.34</v>
+      </c>
+      <c r="BJ5">
+        <v>12.5</v>
+      </c>
+      <c r="BK5">
         <v>10.5</v>
       </c>
-      <c r="AT5">
-        <v>7.6</v>
-      </c>
-      <c r="AU5">
-        <v>7.2</v>
-      </c>
-      <c r="AV5">
-        <v>15.5</v>
-      </c>
-      <c r="AW5">
-        <v>23</v>
-      </c>
-      <c r="AX5">
-        <v>10</v>
-      </c>
-      <c r="AY5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ5">
-        <v>16.5</v>
-      </c>
-      <c r="BA5">
-        <v>29</v>
-      </c>
-      <c r="BB5">
-        <v>18</v>
-      </c>
-      <c r="BC5">
+      <c r="BL5">
+        <v>250</v>
+      </c>
+      <c r="BM5">
+        <v>13</v>
+      </c>
+      <c r="BN5">
+        <v>5.6</v>
+      </c>
+      <c r="BO5">
+        <v>5.1</v>
+      </c>
+      <c r="BP5">
+        <v>30</v>
+      </c>
+      <c r="BQ5">
+        <v>19</v>
+      </c>
+      <c r="BR5">
+        <v>55</v>
+      </c>
+      <c r="BS5">
         <v>11</v>
       </c>
-      <c r="BD5">
-        <v>18</v>
-      </c>
-      <c r="BE5">
-        <v>10.5</v>
-      </c>
-      <c r="BF5">
-        <v>12</v>
-      </c>
-      <c r="BG5">
-        <v>10</v>
-      </c>
-      <c r="BH5">
-        <v>3.4</v>
-      </c>
-      <c r="BI5">
-        <v>2.8</v>
-      </c>
-      <c r="BJ5">
-        <v>10.5</v>
-      </c>
-      <c r="BK5">
-        <v>5.9</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>12.5</v>
-      </c>
-      <c r="BN5">
-        <v>4.6</v>
-      </c>
-      <c r="BO5">
-        <v>4.1</v>
-      </c>
-      <c r="BP5">
-        <v>14</v>
-      </c>
-      <c r="BQ5">
-        <v>6.8</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>9.4</v>
-      </c>
       <c r="BT5">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA5">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="CB5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1881,243 +1872,243 @@
         <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F6">
-        <v>2.72</v>
+        <v>1.92</v>
       </c>
       <c r="G6">
-        <v>2.76</v>
+        <v>1.94</v>
       </c>
       <c r="H6">
+        <v>5.6</v>
+      </c>
+      <c r="I6">
+        <v>5.7</v>
+      </c>
+      <c r="J6">
         <v>3.25</v>
       </c>
-      <c r="I6">
-        <v>3.35</v>
-      </c>
-      <c r="J6">
-        <v>2.96</v>
-      </c>
       <c r="K6">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M6">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="O6">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="P6">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Q6">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="R6">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S6">
+        <v>7.6</v>
+      </c>
+      <c r="T6">
+        <v>2.66</v>
+      </c>
+      <c r="U6">
+        <v>1.56</v>
+      </c>
+      <c r="V6">
+        <v>1.21</v>
+      </c>
+      <c r="W6">
+        <v>2.06</v>
+      </c>
+      <c r="X6">
+        <v>7.2</v>
+      </c>
+      <c r="Y6">
+        <v>12</v>
+      </c>
+      <c r="Z6">
+        <v>44</v>
+      </c>
+      <c r="AA6">
+        <v>230</v>
+      </c>
+      <c r="AB6">
+        <v>5.3</v>
+      </c>
+      <c r="AC6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD6">
+        <v>27</v>
+      </c>
+      <c r="AE6">
+        <v>150</v>
+      </c>
+      <c r="AF6">
+        <v>9.4</v>
+      </c>
+      <c r="AG6">
+        <v>12</v>
+      </c>
+      <c r="AH6">
+        <v>38</v>
+      </c>
+      <c r="AI6">
+        <v>500</v>
+      </c>
+      <c r="AJ6">
+        <v>24</v>
+      </c>
+      <c r="AK6">
+        <v>34</v>
+      </c>
+      <c r="AL6">
+        <v>90</v>
+      </c>
+      <c r="AM6">
+        <v>480</v>
+      </c>
+      <c r="AN6">
+        <v>32</v>
+      </c>
+      <c r="AO6">
+        <v>350</v>
+      </c>
+      <c r="AP6">
         <v>6.4</v>
       </c>
-      <c r="T6">
+      <c r="AQ6">
+        <v>11</v>
+      </c>
+      <c r="AR6">
+        <v>36</v>
+      </c>
+      <c r="AS6">
+        <v>180</v>
+      </c>
+      <c r="AT6">
+        <v>5</v>
+      </c>
+      <c r="AU6">
+        <v>7.4</v>
+      </c>
+      <c r="AV6">
+        <v>23</v>
+      </c>
+      <c r="AW6">
+        <v>75</v>
+      </c>
+      <c r="AX6">
+        <v>8.4</v>
+      </c>
+      <c r="AY6">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6">
+        <v>32</v>
+      </c>
+      <c r="BA6">
+        <v>60</v>
+      </c>
+      <c r="BB6">
+        <v>21</v>
+      </c>
+      <c r="BC6">
+        <v>29</v>
+      </c>
+      <c r="BD6">
+        <v>70</v>
+      </c>
+      <c r="BE6">
+        <v>110</v>
+      </c>
+      <c r="BF6">
+        <v>27</v>
+      </c>
+      <c r="BG6">
+        <v>48</v>
+      </c>
+      <c r="BH6">
+        <v>2.44</v>
+      </c>
+      <c r="BI6">
         <v>2.26</v>
       </c>
-      <c r="U6">
-        <v>1.75</v>
-      </c>
-      <c r="V6">
-        <v>1.42</v>
-      </c>
-      <c r="W6">
-        <v>1.57</v>
-      </c>
-      <c r="X6">
-        <v>7.6</v>
-      </c>
-      <c r="Y6">
-        <v>8.4</v>
-      </c>
-      <c r="Z6">
-        <v>21</v>
-      </c>
-      <c r="AA6">
-        <v>70</v>
-      </c>
-      <c r="AB6">
-        <v>7.6</v>
-      </c>
-      <c r="AC6">
-        <v>7</v>
-      </c>
-      <c r="AD6">
-        <v>15.5</v>
-      </c>
-      <c r="AE6">
-        <v>55</v>
-      </c>
-      <c r="AF6">
-        <v>15.5</v>
-      </c>
-      <c r="AG6">
-        <v>13.5</v>
-      </c>
-      <c r="AH6">
-        <v>27</v>
-      </c>
-      <c r="AI6">
-        <v>85</v>
-      </c>
-      <c r="AJ6">
-        <v>44</v>
-      </c>
-      <c r="AK6">
-        <v>44</v>
-      </c>
-      <c r="AL6">
-        <v>75</v>
-      </c>
-      <c r="AM6">
-        <v>220</v>
-      </c>
-      <c r="AN6">
-        <v>50</v>
-      </c>
-      <c r="AO6">
-        <v>80</v>
-      </c>
-      <c r="AP6">
-        <v>7</v>
-      </c>
-      <c r="AQ6">
+      <c r="BJ6">
+        <v>14</v>
+      </c>
+      <c r="BK6">
         <v>8</v>
       </c>
-      <c r="AR6">
-        <v>18.5</v>
-      </c>
-      <c r="AS6">
-        <v>50</v>
-      </c>
-      <c r="AT6">
-        <v>7</v>
-      </c>
-      <c r="AU6">
-        <v>6.4</v>
-      </c>
-      <c r="AV6">
-        <v>14</v>
-      </c>
-      <c r="AW6">
-        <v>44</v>
-      </c>
-      <c r="AX6">
-        <v>14</v>
-      </c>
-      <c r="AY6">
-        <v>12.5</v>
-      </c>
-      <c r="AZ6">
-        <v>23</v>
-      </c>
-      <c r="BA6">
-        <v>65</v>
-      </c>
-      <c r="BB6">
-        <v>40</v>
-      </c>
-      <c r="BC6">
-        <v>38</v>
-      </c>
-      <c r="BD6">
-        <v>60</v>
-      </c>
-      <c r="BE6">
-        <v>70</v>
-      </c>
-      <c r="BF6">
-        <v>44</v>
-      </c>
-      <c r="BG6">
-        <v>34</v>
-      </c>
-      <c r="BH6">
-        <v>2.64</v>
-      </c>
-      <c r="BI6">
-        <v>2.12</v>
-      </c>
-      <c r="BJ6">
-        <v>12.5</v>
-      </c>
-      <c r="BK6">
-        <v>5.9</v>
-      </c>
       <c r="BL6">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN6">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BO6">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BP6">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="BQ6">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6">
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BT6">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BU6">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV6">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="BW6">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BX6">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="BY6">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="BZ6">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="CA6">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="CB6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
         <v>84</v>
@@ -2126,477 +2117,235 @@
         <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
         <v>2.02</v>
       </c>
-      <c r="G7">
-        <v>2.06</v>
-      </c>
       <c r="H7">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I7">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="L7">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="M7">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="O7">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="P7">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Q7">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="R7">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="T7">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="U7">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="V7">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="X7">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z7">
         <v>34</v>
       </c>
       <c r="AA7">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB7">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE7">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AF7">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH7">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI7">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AJ7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL7">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AM7">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AN7">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO7">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AP7">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AQ7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR7">
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AT7">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW7">
         <v>75</v>
       </c>
       <c r="AX7">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BA7">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="BB7">
         <v>23</v>
       </c>
       <c r="BC7">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BD7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BE7">
         <v>110</v>
       </c>
       <c r="BF7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BG7">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="BH7">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="BI7">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="BM7">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BN7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP7">
         <v>17.5</v>
       </c>
       <c r="BQ7">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BR7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS7">
-        <v>2.12</v>
+        <v>29</v>
       </c>
       <c r="BT7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BU7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BV7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW7">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BX7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BY7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BZ7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="CA7">
-        <v>2.12</v>
+        <v>24</v>
       </c>
       <c r="CB7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:80">
-      <c r="A8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8">
-        <v>2.04</v>
-      </c>
-      <c r="G8">
-        <v>2.06</v>
-      </c>
-      <c r="H8">
-        <v>4.6</v>
-      </c>
-      <c r="I8">
-        <v>4.7</v>
-      </c>
-      <c r="J8">
-        <v>3.35</v>
-      </c>
-      <c r="K8">
-        <v>3.4</v>
-      </c>
-      <c r="L8">
-        <v>1.63</v>
-      </c>
-      <c r="M8">
-        <v>1.13</v>
-      </c>
-      <c r="N8">
-        <v>2.62</v>
-      </c>
-      <c r="O8">
-        <v>1.6</v>
-      </c>
-      <c r="P8">
-        <v>1.55</v>
-      </c>
-      <c r="Q8">
-        <v>2.8</v>
-      </c>
-      <c r="R8">
-        <v>1.19</v>
-      </c>
-      <c r="S8">
-        <v>6</v>
-      </c>
-      <c r="T8">
-        <v>2.34</v>
-      </c>
-      <c r="U8">
-        <v>1.73</v>
-      </c>
-      <c r="V8">
-        <v>1.27</v>
-      </c>
-      <c r="W8">
-        <v>1.94</v>
-      </c>
-      <c r="X8">
-        <v>8.6</v>
-      </c>
-      <c r="Y8">
-        <v>11.5</v>
-      </c>
-      <c r="Z8">
-        <v>34</v>
-      </c>
-      <c r="AA8">
-        <v>130</v>
-      </c>
-      <c r="AB8">
-        <v>6.4</v>
-      </c>
-      <c r="AC8">
-        <v>7.6</v>
-      </c>
-      <c r="AD8">
-        <v>20</v>
-      </c>
-      <c r="AE8">
-        <v>90</v>
-      </c>
-      <c r="AF8">
-        <v>10.5</v>
-      </c>
-      <c r="AG8">
-        <v>11</v>
-      </c>
-      <c r="AH8">
-        <v>28</v>
-      </c>
-      <c r="AI8">
-        <v>110</v>
-      </c>
-      <c r="AJ8">
-        <v>25</v>
-      </c>
-      <c r="AK8">
-        <v>28</v>
-      </c>
-      <c r="AL8">
-        <v>65</v>
-      </c>
-      <c r="AM8">
-        <v>240</v>
-      </c>
-      <c r="AN8">
-        <v>27</v>
-      </c>
-      <c r="AO8">
-        <v>160</v>
-      </c>
-      <c r="AP8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ8">
-        <v>10.5</v>
-      </c>
-      <c r="AR8">
-        <v>30</v>
-      </c>
-      <c r="AS8">
-        <v>95</v>
-      </c>
-      <c r="AT8">
-        <v>6</v>
-      </c>
-      <c r="AU8">
-        <v>7.4</v>
-      </c>
-      <c r="AV8">
-        <v>18.5</v>
-      </c>
-      <c r="AW8">
-        <v>75</v>
-      </c>
-      <c r="AX8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY8">
-        <v>10.5</v>
-      </c>
-      <c r="AZ8">
-        <v>26</v>
-      </c>
-      <c r="BA8">
-        <v>95</v>
-      </c>
-      <c r="BB8">
-        <v>23</v>
-      </c>
-      <c r="BC8">
-        <v>26</v>
-      </c>
-      <c r="BD8">
-        <v>50</v>
-      </c>
-      <c r="BE8">
-        <v>70</v>
-      </c>
-      <c r="BF8">
-        <v>25</v>
-      </c>
-      <c r="BG8">
-        <v>120</v>
-      </c>
-      <c r="BH8">
-        <v>2.62</v>
-      </c>
-      <c r="BI8">
-        <v>2.5</v>
-      </c>
-      <c r="BJ8">
-        <v>12.5</v>
-      </c>
-      <c r="BK8">
-        <v>7.2</v>
-      </c>
-      <c r="BL8">
-        <v>250</v>
-      </c>
-      <c r="BM8">
-        <v>16.5</v>
-      </c>
-      <c r="BN8">
-        <v>4.4</v>
-      </c>
-      <c r="BO8">
-        <v>4</v>
-      </c>
-      <c r="BP8">
-        <v>17.5</v>
-      </c>
-      <c r="BQ8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR8">
-        <v>44</v>
-      </c>
-      <c r="BS8">
-        <v>12.5</v>
-      </c>
-      <c r="BT8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU8">
-        <v>6.2</v>
-      </c>
-      <c r="BV8">
-        <v>60</v>
-      </c>
-      <c r="BW8">
-        <v>13.5</v>
-      </c>
-      <c r="BX8">
-        <v>80</v>
-      </c>
-      <c r="BY8">
-        <v>14.5</v>
-      </c>
-      <c r="BZ8">
-        <v>48</v>
-      </c>
-      <c r="CA8">
-        <v>13</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
